--- a/App/TestCases_App/User_admin.xlsx
+++ b/App/TestCases_App/User_admin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06AE3776-1949-4681-88CD-8C0BE65BDA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0525236B-4AFE-478C-8C8E-FF16DD61A4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="202">
   <si>
     <t>Num</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>Views of tables</t>
-  </si>
-  <si>
-    <t>Tickets' history</t>
   </si>
   <si>
     <t>Take order</t>
@@ -141,9 +138,6 @@
     <t>OK</t>
   </si>
   <si>
-    <t>No se puede buscar por fechas</t>
-  </si>
-  <si>
     <t>Se ha introducido un número desorbitado de comensales, y al ir a pagar, se ha cerrado la aplicación.</t>
   </si>
   <si>
@@ -337,9 +331,6 @@
     <t>USERADM023</t>
   </si>
   <si>
-    <t>El botón "MODO TPV" pisotea la barra superior. Waiter001.jpg</t>
-  </si>
-  <si>
     <t>Cash closing page</t>
   </si>
   <si>
@@ -444,6 +435,260 @@
   <si>
     <t>1. The user clicks "Automático"
 2. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>El botón "MODO TPV" pisotea la barra superior. Waiter001.jpg
+Alerta erronea: alerta.jpg
+al no haber scroll lateral ,no se intuye que hay opciones debajo de "Cartas"</t>
+  </si>
+  <si>
+    <t>Tables's map</t>
+  </si>
+  <si>
+    <t>Users</t>
+  </si>
+  <si>
+    <t>Categories</t>
+  </si>
+  <si>
+    <t>Modifiers</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>Promotions</t>
+  </si>
+  <si>
+    <t>Printers</t>
+  </si>
+  <si>
+    <t>Request</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>Backups</t>
+  </si>
+  <si>
+    <t>Upgrade to PRO version</t>
+  </si>
+  <si>
+    <t>USERADM031</t>
+  </si>
+  <si>
+    <t>USERADM032</t>
+  </si>
+  <si>
+    <t>USERADM033</t>
+  </si>
+  <si>
+    <t>USERADM034</t>
+  </si>
+  <si>
+    <t>USERADM035</t>
+  </si>
+  <si>
+    <t>USERADM036</t>
+  </si>
+  <si>
+    <t>USERADM037</t>
+  </si>
+  <si>
+    <t>USERADM038</t>
+  </si>
+  <si>
+    <t>USERADM039</t>
+  </si>
+  <si>
+    <t>USERADM040</t>
+  </si>
+  <si>
+    <t>USERADM041</t>
+  </si>
+  <si>
+    <t>USERADM042</t>
+  </si>
+  <si>
+    <t>USERADM043</t>
+  </si>
+  <si>
+    <t>USERADM044</t>
+  </si>
+  <si>
+    <t>USERADM045</t>
+  </si>
+  <si>
+    <t>USERADM046</t>
+  </si>
+  <si>
+    <t>USERADM047</t>
+  </si>
+  <si>
+    <t>USERADM048</t>
+  </si>
+  <si>
+    <t>USERADM049</t>
+  </si>
+  <si>
+    <t>USERADM050</t>
+  </si>
+  <si>
+    <t>USERADM051</t>
+  </si>
+  <si>
+    <t>USERADM052</t>
+  </si>
+  <si>
+    <t>USERADM053</t>
+  </si>
+  <si>
+    <t>USERADM054</t>
+  </si>
+  <si>
+    <t>USERADM055</t>
+  </si>
+  <si>
+    <t>USERADM056</t>
+  </si>
+  <si>
+    <t>USERADM057</t>
+  </si>
+  <si>
+    <t>USERADM058</t>
+  </si>
+  <si>
+    <t>USERADM059</t>
+  </si>
+  <si>
+    <t>USERADM060</t>
+  </si>
+  <si>
+    <t>USERADM061</t>
+  </si>
+  <si>
+    <t>USERADM062</t>
+  </si>
+  <si>
+    <t>USERADM063</t>
+  </si>
+  <si>
+    <t>1. The operation is cancelled.</t>
+  </si>
+  <si>
+    <t>1. The user sees tickets' history page</t>
+  </si>
+  <si>
+    <t>1. The tickets' history page is shown.</t>
+  </si>
+  <si>
+    <t>Tickets' history: find</t>
+  </si>
+  <si>
+    <t>Funciona "Buscar tickets" , pero no "Rango de fechas"</t>
+  </si>
+  <si>
+    <t>Tickets' history: information</t>
+  </si>
+  <si>
+    <t>Tickets' history: information, re-print</t>
+  </si>
+  <si>
+    <t>Tickets' history: information, close</t>
+  </si>
+  <si>
+    <t>No se puede "reimprimir ticket"</t>
+  </si>
+  <si>
+    <t>Se puede cerrar con la opción cerrar y con el aspa</t>
+  </si>
+  <si>
+    <t>Tickets' history: information, print</t>
+  </si>
+  <si>
+    <t>No se puede "imprimir" desde el icono impresora</t>
+  </si>
+  <si>
+    <t>1. The user sees Invoicing page</t>
+  </si>
+  <si>
+    <t>1. The user sees menus page</t>
+  </si>
+  <si>
+    <t>1. The user sees Tables's map page</t>
+  </si>
+  <si>
+    <t>1. The user users page</t>
+  </si>
+  <si>
+    <t>1. The user sees categories page</t>
+  </si>
+  <si>
+    <t>1. The user sees modifiers page</t>
+  </si>
+  <si>
+    <t>1. The user sees products page</t>
+  </si>
+  <si>
+    <t>1. The user sees promotions page</t>
+  </si>
+  <si>
+    <t>1. The user sees printers page</t>
+  </si>
+  <si>
+    <t>1. The user sees settings page</t>
+  </si>
+  <si>
+    <t>1. The user sees backups page</t>
+  </si>
+  <si>
+    <t>1. The user sees Upgrade to PRO version page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invoicing: </t>
+  </si>
+  <si>
+    <t>Invoicing: Invoicers list</t>
+  </si>
+  <si>
+    <t>No sirve para nada la etiqueta "# Numeración actual"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>La operación "Nueva factura" aparece dos veces.</t>
+  </si>
+  <si>
+    <t>Invoicing: Add, mandatory fields</t>
+  </si>
+  <si>
+    <t>Invoicing: Add, all fields</t>
+  </si>
+  <si>
+    <t>Aparece un mensaje de que "seleccione una serie de facturación" que no viene por ningún sitio</t>
+  </si>
+  <si>
+    <t>Invoicing: Add, all fields, cancel</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nueva factura"
+2. Clicks a ticket and "Generar factura"
+3. Fills the all fields
+4. Clicks back arrow</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nueva factura"
+2. Clicks a ticket and "Generar factura"
+3. Fills the all fields
+4. Clicks "Confirmar y emitir factura"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nueva factura"
+2. Clicks a ticket and "Generar factura"
+3. Fills the mandatory fields
+4. Clicks "Confirmar y emitir factura"</t>
   </si>
 </sst>
 </file>
@@ -525,7 +770,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -548,42 +793,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6565"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -918,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -957,292 +1174,288 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>82</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
       <c r="G3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="2" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>121</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>122</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>96</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>100</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="G13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1250,383 +1463,1139 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="G15" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="1"/>
+        <v>112</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="F16" s="1"/>
       <c r="G16" s="2" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="1"/>
+        <v>113</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="F17" s="1"/>
       <c r="G17" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="1"/>
+        <v>116</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>118</v>
+      </c>
       <c r="F18" s="1"/>
       <c r="G18" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="1"/>
+        <v>117</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>119</v>
+      </c>
       <c r="F19" s="1"/>
       <c r="G19" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="G20" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="1"/>
+        <v>92</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="F21" s="1"/>
       <c r="G21" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>37</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F23" s="1"/>
       <c r="G23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>42</v>
+        <v>193</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" s="1"/>
+        <v>168</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>168</v>
+      </c>
       <c r="G24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>47</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>48</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>109</v>
-      </c>
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
-        <v>69</v>
+        <v>171</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
-      <c r="G26" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="G26" s="2"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C27" s="1"/>
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1" t="s">
+        <v>172</v>
+      </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="3"/>
+      <c r="G27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>111</v>
-      </c>
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H28" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C29" s="1"/>
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1" t="s">
+        <v>176</v>
+      </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="3"/>
-    </row>
-    <row r="30" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="G29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>75</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
       <c r="G30" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>79</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>26</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>26</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>26</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H34" s="3"/>
+    </row>
+    <row r="35" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>26</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>26</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H36" s="3"/>
+    </row>
+    <row r="37" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>27</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>28</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>29</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>30</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>31</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>32</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>33</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
         <v>34</v>
       </c>
-      <c r="H31" s="3"/>
+      <c r="B44" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>35</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H45" s="3"/>
+    </row>
+    <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>36</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H46" s="3"/>
+    </row>
+    <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>37</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H47" s="3"/>
+    </row>
+    <row r="48" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>38</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H48" s="3"/>
+    </row>
+    <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>39</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>40</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H50" s="3"/>
+    </row>
+    <row r="51" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>41</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>42</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H52" s="3"/>
+    </row>
+    <row r="53" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>43</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>44</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H54" s="3"/>
+    </row>
+    <row r="55" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>45</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H55" s="3"/>
+    </row>
+    <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>46</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H56" s="3"/>
+    </row>
+    <row r="57" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>47</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H57" s="3"/>
+    </row>
+    <row r="58" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>48</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H58" s="3"/>
+    </row>
+    <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>49</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>50</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H60" s="3"/>
+    </row>
+    <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>51</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H61" s="3"/>
+    </row>
+    <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>52</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H62" s="3"/>
+    </row>
+    <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>53</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H63" s="3"/>
+    </row>
+    <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>54</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H64" s="3"/>
+    </row>
+    <row r="65" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>55</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H65" s="3"/>
+    </row>
+    <row r="66" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>56</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H66" s="3"/>
+    </row>
+    <row r="67" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>57</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H67" s="3"/>
+    </row>
+    <row r="68" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>58</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H68" s="3"/>
+    </row>
+    <row r="69" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>59</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H69" s="3"/>
+    </row>
+    <row r="70" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>60</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H70" s="3"/>
+    </row>
+    <row r="71" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>61</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>62</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F72" s="1"/>
+      <c r="G72" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H72" s="3"/>
+    </row>
+    <row r="73" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>63</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H73" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G29">
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="PTE">
+  <conditionalFormatting sqref="G2:G73">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="BL">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="KO">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G30:G31">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
-      <formula>NOT(ISERROR(SEARCH("PTE",G30)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
-      <formula>NOT(ISERROR(SEARCH("BL",G30)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
-      <formula>NOT(ISERROR(SEARCH("KO",G30)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",G30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/App/TestCases_App/User_admin.xlsx
+++ b/App/TestCases_App/User_admin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0525236B-4AFE-478C-8C8E-FF16DD61A4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF318592-CAFE-41C3-833F-03AEBB295B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="220">
   <si>
     <t>Num</t>
   </si>
@@ -658,16 +658,10 @@
     <t xml:space="preserve">  </t>
   </si>
   <si>
-    <t>La operación "Nueva factura" aparece dos veces.</t>
-  </si>
-  <si>
     <t>Invoicing: Add, mandatory fields</t>
   </si>
   <si>
     <t>Invoicing: Add, all fields</t>
-  </si>
-  <si>
-    <t>Aparece un mensaje de que "seleccione una serie de facturación" que no viene por ningún sitio</t>
   </si>
   <si>
     <t>Invoicing: Add, all fields, cancel</t>
@@ -689,6 +683,76 @@
 2. Clicks a ticket and "Generar factura"
 3. Fills the mandatory fields
 4. Clicks "Confirmar y emitir factura"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invoicing: Settings, new </t>
+  </si>
+  <si>
+    <t>1. The user clicks "Configuración"
+2. Clicks "Series de facturación"
+3. Añadir  "nueva serie"
+4. Clicks "Crear serie"</t>
+  </si>
+  <si>
+    <t>1. The serie is created</t>
+  </si>
+  <si>
+    <t>Invoicing: Settings, new with fields</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Configuración"
+2. Clicks "Series de facturación"
+3. Añadir  "nueva serie" with fields modified
+4. Clicks "Crear serie"</t>
+  </si>
+  <si>
+    <t>Invoicing: Settings,tax data</t>
+  </si>
+  <si>
+    <t>Invoicing: Settings,taxes</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Configuración"
+2. Clicks "Datos fiscales"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Configuración"
+2. Clicks "Impuestos"</t>
+  </si>
+  <si>
+    <t>Invoicing: Settings, general options</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Configuración"
+2. Clicks "Opciones generales"</t>
+  </si>
+  <si>
+    <t>Invoicing: Settings, verifactu</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Configuración"
+2. Clicks "Verifactu"</t>
+  </si>
+  <si>
+    <t>Traducir, verifactu y  añadir funcionalidad</t>
+  </si>
+  <si>
+    <t>Sale vacio, añadir funcionalidad</t>
+  </si>
+  <si>
+    <t>No hace nada, se queda cargando, añadir funcionalidad</t>
+  </si>
+  <si>
+    <t>Aparece un mensaje de que "seleccione una serie de facturación" que no viene por ningún sitio: FAC002.jpg</t>
+  </si>
+  <si>
+    <t>La operación "Nueva factura" aparece dos veces: FAC001.jpg</t>
+  </si>
+  <si>
+    <t>Aparece un mensaje de que "seleccione una serie de facturación" que no viene por ningún sitio FAC002.jpg</t>
+  </si>
+  <si>
+    <t>Ha permitido meter el año 20266: FAC003.jpg</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +1199,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -1791,7 +1855,7 @@
         <v>10</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1811,7 +1875,7 @@
         <v>32</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1822,10 +1886,10 @@
         <v>107</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -1833,7 +1897,7 @@
         <v>10</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1844,10 +1908,10 @@
         <v>107</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -1855,7 +1919,7 @@
         <v>10</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1866,10 +1930,10 @@
         <v>107</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>166</v>
@@ -1882,7 +1946,7 @@
       </c>
       <c r="H34" s="3"/>
     </row>
-    <row r="35" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>26</v>
       </c>
@@ -1890,17 +1954,21 @@
         <v>107</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
+        <v>200</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="F35" s="1"/>
       <c r="G35" s="2" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>26</v>
       </c>
@@ -1908,96 +1976,120 @@
         <v>107</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="F36" s="1"/>
       <c r="G36" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H36" s="3"/>
-    </row>
-    <row r="37" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>69</v>
+        <v>205</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H37" s="3"/>
-    </row>
-    <row r="38" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
+        <v>107</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>208</v>
+      </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H38" s="3"/>
-    </row>
-    <row r="39" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
+        <v>107</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H39" s="3"/>
-    </row>
-    <row r="40" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H40" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C41" s="1"/>
+        <v>107</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>190</v>
+      </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
@@ -2008,13 +2100,17 @@
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
+        <v>108</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>179</v>
+      </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="2" t="s">
@@ -2024,17 +2120,13 @@
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>181</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="2" t="s">
@@ -2044,10 +2136,10 @@
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -2060,13 +2152,17 @@
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
+        <v>111</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>180</v>
+      </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="2" t="s">
@@ -2076,17 +2172,13 @@
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>182</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="2" t="s">
@@ -2096,10 +2188,10 @@
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -2110,15 +2202,19 @@
       </c>
       <c r="H47" s="3"/>
     </row>
-    <row r="48" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
+        <v>135</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>181</v>
+      </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="2" t="s">
@@ -2128,17 +2224,13 @@
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>183</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="2" t="s">
@@ -2148,10 +2240,10 @@
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -2162,15 +2254,19 @@
       </c>
       <c r="H50" s="3"/>
     </row>
-    <row r="51" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
+        <v>138</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>182</v>
+      </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="2" t="s">
@@ -2180,17 +2276,13 @@
     </row>
     <row r="52" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>184</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="2" t="s">
@@ -2198,12 +2290,12 @@
       </c>
       <c r="H52" s="3"/>
     </row>
-    <row r="53" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -2214,15 +2306,19 @@
       </c>
       <c r="H53" s="3"/>
     </row>
-    <row r="54" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
+        <v>141</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>183</v>
+      </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="2" t="s">
@@ -2232,17 +2328,13 @@
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>185</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="2" t="s">
@@ -2250,12 +2342,12 @@
       </c>
       <c r="H55" s="3"/>
     </row>
-    <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -2266,15 +2358,19 @@
       </c>
       <c r="H56" s="3"/>
     </row>
-    <row r="57" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
+        <v>144</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="2" t="s">
@@ -2284,17 +2380,13 @@
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>186</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="2" t="s">
@@ -2302,12 +2394,12 @@
       </c>
       <c r="H58" s="3"/>
     </row>
-    <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -2320,13 +2412,17 @@
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
+        <v>147</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="2" t="s">
@@ -2336,17 +2432,13 @@
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>167</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="2" t="s">
@@ -2354,12 +2446,12 @@
       </c>
       <c r="H61" s="3"/>
     </row>
-    <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -2372,13 +2464,17 @@
     </row>
     <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
+        <v>150</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>186</v>
+      </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="2" t="s">
@@ -2388,17 +2484,13 @@
     </row>
     <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>187</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="2" t="s">
@@ -2408,10 +2500,10 @@
     </row>
     <row r="65" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -2424,13 +2516,17 @@
     </row>
     <row r="66" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
+        <v>153</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>167</v>
+      </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="2" t="s">
@@ -2440,17 +2536,13 @@
     </row>
     <row r="67" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>188</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="2" t="s">
@@ -2460,10 +2552,10 @@
     </row>
     <row r="68" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -2474,18 +2566,18 @@
       </c>
       <c r="H68" s="3"/>
     </row>
-    <row r="69" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
@@ -2494,12 +2586,12 @@
       </c>
       <c r="H69" s="3"/>
     </row>
-    <row r="70" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
@@ -2510,81 +2602,169 @@
       </c>
       <c r="H70" s="3"/>
     </row>
-    <row r="71" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>73</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
       <c r="G71" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="H71" s="3"/>
+    </row>
+    <row r="72" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>77</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="2" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="H72" s="3"/>
     </row>
     <row r="73" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
+        <v>58</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H73" s="3"/>
+    </row>
+    <row r="74" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>59</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H74" s="3"/>
+    </row>
+    <row r="75" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>60</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H75" s="3"/>
+    </row>
+    <row r="76" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>61</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>62</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F77" s="1"/>
+      <c r="G77" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H77" s="3"/>
+    </row>
+    <row r="78" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
         <v>63</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D78" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E78" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="F78" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G73" s="2" t="s">
+      <c r="G78" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H73" s="3"/>
+      <c r="H78" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G73">
+  <conditionalFormatting sqref="G2:G78">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>

--- a/App/TestCases_App/User_admin.xlsx
+++ b/App/TestCases_App/User_admin.xlsx
@@ -8,19 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF318592-CAFE-41C3-833F-03AEBB295B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F083B8DC-4EF7-4922-93D3-9A629ED9484A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="604">
   <si>
     <t>Num</t>
   </si>
@@ -44,12 +58,6 @@
   </si>
   <si>
     <t>Notes</t>
-  </si>
-  <si>
-    <t>Views of tables</t>
-  </si>
-  <si>
-    <t>Take order</t>
   </si>
   <si>
     <t>KO</t>
@@ -66,13 +74,7 @@
 4. Clicks "Cerrar mesa"</t>
   </si>
   <si>
-    <t>Take order: Join table</t>
-  </si>
-  <si>
     <t>Las mesas no se unen.</t>
-  </si>
-  <si>
-    <t>Take order: Fee</t>
   </si>
   <si>
     <t>1. Select numbers of people
@@ -81,24 +83,12 @@
 4. Clicks "Cerrar mesa"</t>
   </si>
   <si>
-    <t>Take order: change type of menu</t>
-  </si>
-  <si>
-    <t>Take order: find a product</t>
-  </si>
-  <si>
     <t>1. Select numbers of people
 2. Select find product
 3. Add product
 4. Clicks "Cerrar mesa"</t>
   </si>
   <si>
-    <t>Take order: Add modifiers</t>
-  </si>
-  <si>
-    <t>Take order: Add modifiers, cancel</t>
-  </si>
-  <si>
     <t>1. Select numbers of people
 2. Select a product
 3. Add a modifier, clicks "Añadir al pedido"
@@ -120,9 +110,6 @@
     <t>Con cada producto añadido, se está añadiendo el suplemento de terraza. Waiter003.jpg</t>
   </si>
   <si>
-    <t>Take order: pay the bill</t>
-  </si>
-  <si>
     <t>1. Select numbers of people
 2. Select products
 3. Clicks "Realizar pago"
@@ -132,22 +119,10 @@
     <t>Se reparte la cuenta entre ocho, se hace un pago en efectivo, se hace un pago con tarjeta, pero al pagar el resto de la cuenta indica, se ha pagado 1/8 cuando han sido 2/8. Waiter004.jpg</t>
   </si>
   <si>
-    <t>El menu sale cortado. Waiter002.jpg</t>
-  </si>
-  <si>
     <t>OK</t>
   </si>
   <si>
-    <t>Se ha introducido un número desorbitado de comensales, y al ir a pagar, se ha cerrado la aplicación.</t>
-  </si>
-  <si>
     <t>BL</t>
-  </si>
-  <si>
-    <t>Take order: Add product</t>
-  </si>
-  <si>
-    <t>Take order: Delete product</t>
   </si>
   <si>
     <t>The product is deleted</t>
@@ -171,9 +146,6 @@
 </t>
   </si>
   <si>
-    <t>Take order: Cancel,add product</t>
-  </si>
-  <si>
     <t>1. Select numbers of people
 2. Select products
 3. Clicks "+"
@@ -256,16 +228,10 @@
     <t>Cash closing's history</t>
   </si>
   <si>
-    <t>Take order: send order</t>
-  </si>
-  <si>
     <t>Invoicing</t>
   </si>
   <si>
     <t>pte</t>
-  </si>
-  <si>
-    <t>Menus</t>
   </si>
   <si>
     <t>Pending tasks</t>
@@ -304,9 +270,6 @@
     <t>1. The operation is done</t>
   </si>
   <si>
-    <t>ok</t>
-  </si>
-  <si>
     <t>USERADM016</t>
   </si>
   <si>
@@ -329,9 +292,6 @@
   </si>
   <si>
     <t>USERADM023</t>
-  </si>
-  <si>
-    <t>Cash closing page</t>
   </si>
   <si>
     <t>Tiene algún sentido hacer un cierre vacio, con todo a 0 ???</t>
@@ -368,15 +328,6 @@
   </si>
   <si>
     <t>Aunque no se puede probar la impresión aparece un mensaje con "Imprimiendo cierre…" y no da error.</t>
-  </si>
-  <si>
-    <t>Normal cash register closing declared</t>
-  </si>
-  <si>
-    <t>Automatic cash register closing</t>
-  </si>
-  <si>
-    <t>Cash register closing: Cancelled</t>
   </si>
   <si>
     <t>USERADM024</t>
@@ -442,30 +393,6 @@
 al no haber scroll lateral ,no se intuye que hay opciones debajo de "Cartas"</t>
   </si>
   <si>
-    <t>Tables's map</t>
-  </si>
-  <si>
-    <t>Users</t>
-  </si>
-  <si>
-    <t>Categories</t>
-  </si>
-  <si>
-    <t>Modifiers</t>
-  </si>
-  <si>
-    <t>Products</t>
-  </si>
-  <si>
-    <t>Promotions</t>
-  </si>
-  <si>
-    <t>Printers</t>
-  </si>
-  <si>
-    <t>Request</t>
-  </si>
-  <si>
     <t>Settings</t>
   </si>
   <si>
@@ -499,24 +426,6 @@
     <t>USERADM038</t>
   </si>
   <si>
-    <t>USERADM039</t>
-  </si>
-  <si>
-    <t>USERADM040</t>
-  </si>
-  <si>
-    <t>USERADM041</t>
-  </si>
-  <si>
-    <t>USERADM042</t>
-  </si>
-  <si>
-    <t>USERADM043</t>
-  </si>
-  <si>
-    <t>USERADM044</t>
-  </si>
-  <si>
     <t>USERADM045</t>
   </si>
   <si>
@@ -541,18 +450,12 @@
     <t>USERADM052</t>
   </si>
   <si>
-    <t>USERADM053</t>
-  </si>
-  <si>
     <t>USERADM054</t>
   </si>
   <si>
     <t>USERADM055</t>
   </si>
   <si>
-    <t>USERADM056</t>
-  </si>
-  <si>
     <t>USERADM057</t>
   </si>
   <si>
@@ -616,21 +519,6 @@
     <t>1. The user sees menus page</t>
   </si>
   <si>
-    <t>1. The user sees Tables's map page</t>
-  </si>
-  <si>
-    <t>1. The user users page</t>
-  </si>
-  <si>
-    <t>1. The user sees categories page</t>
-  </si>
-  <si>
-    <t>1. The user sees modifiers page</t>
-  </si>
-  <si>
-    <t>1. The user sees products page</t>
-  </si>
-  <si>
     <t>1. The user sees promotions page</t>
   </si>
   <si>
@@ -646,16 +534,10 @@
     <t>1. The user sees Upgrade to PRO version page</t>
   </si>
   <si>
-    <t xml:space="preserve">Invoicing: </t>
-  </si>
-  <si>
     <t>Invoicing: Invoicers list</t>
   </si>
   <si>
     <t>No sirve para nada la etiqueta "# Numeración actual"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  </t>
   </si>
   <si>
     <t>Invoicing: Add, mandatory fields</t>
@@ -746,13 +628,1386 @@
     <t>Aparece un mensaje de que "seleccione una serie de facturación" que no viene por ningún sitio: FAC002.jpg</t>
   </si>
   <si>
-    <t>La operación "Nueva factura" aparece dos veces: FAC001.jpg</t>
-  </si>
-  <si>
     <t>Aparece un mensaje de que "seleccione una serie de facturación" que no viene por ningún sitio FAC002.jpg</t>
   </si>
   <si>
     <t>Ha permitido meter el año 20266: FAC003.jpg</t>
+  </si>
+  <si>
+    <t>1. The Upgrade to PRO version page</t>
+  </si>
+  <si>
+    <t>Upgrade to PRO version, change plan</t>
+  </si>
+  <si>
+    <t>1. The user changes the plan</t>
+  </si>
+  <si>
+    <t>1. The plan is changed.</t>
+  </si>
+  <si>
+    <t>No es posible cambiarse de plan, sale el mensaje: "Para contratar el plan XXX, contacta con soporte.</t>
+  </si>
+  <si>
+    <t>Aparece una pantalla con errores, que además no se puede cerrar: sin001.jpg</t>
+  </si>
+  <si>
+    <t>1. The backups page is correctly</t>
+  </si>
+  <si>
+    <t>Backups: create</t>
+  </si>
+  <si>
+    <t>1. The user creates a backup</t>
+  </si>
+  <si>
+    <t>1. The backups is created</t>
+  </si>
+  <si>
+    <t>Se queda pendiente de sincronizar, no se puede garantizar que exista: COPSEG001.jpg</t>
+  </si>
+  <si>
+    <t>Settings: General, principal TPV</t>
+  </si>
+  <si>
+    <t>Settings: General, language</t>
+  </si>
+  <si>
+    <t>Settings: General, delete account</t>
+  </si>
+  <si>
+    <t>Settings: General, close session</t>
+  </si>
+  <si>
+    <t>Settings: Appearance, interfaz</t>
+  </si>
+  <si>
+    <t>Settings: Appearance, mode</t>
+  </si>
+  <si>
+    <t>Settings: Accesibility, size letter</t>
+  </si>
+  <si>
+    <t>Settings: Notifications, confirmation</t>
+  </si>
+  <si>
+    <t>Settings: Notifications, order QR</t>
+  </si>
+  <si>
+    <t>Settings: Taxes,create</t>
+  </si>
+  <si>
+    <t>Settings: Taxes, delete</t>
+  </si>
+  <si>
+    <t>El desplegable para introducir el valor, tapa el botón de "Añadir"</t>
+  </si>
+  <si>
+    <t>Settings: Taxes, delete,cancel</t>
+  </si>
+  <si>
+    <t>Debería confirmar si se desea borrar.</t>
+  </si>
+  <si>
+    <t>1. The user can change the status</t>
+  </si>
+  <si>
+    <t>1. The notificacion is activated/deactivated</t>
+  </si>
+  <si>
+    <t>1. The user can change if the order will be created from QR</t>
+  </si>
+  <si>
+    <t>1. The user can activate/deactived sounds by new orders.</t>
+  </si>
+  <si>
+    <t>Settings: Notifications,sounds' order</t>
+  </si>
+  <si>
+    <t>Settings: Notifications,sounds' pay</t>
+  </si>
+  <si>
+    <t>1. The user can activate/deactived sounds by new pay</t>
+  </si>
+  <si>
+    <t>1. The user can create a new tax.</t>
+  </si>
+  <si>
+    <t>1. The new tax is created.</t>
+  </si>
+  <si>
+    <t>1. The tax is deleted</t>
+  </si>
+  <si>
+    <t>1. The user can delete a tax used.
+2. A message is shown with "El impuesto se va a eliminar, ¿Está seguro?"
+3. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user can delete a tax used.
+2. A message is shown with "El impuesto se va a eliminar, ¿Está seguro?"
+3. Clicks "Eliminar"</t>
+  </si>
+  <si>
+    <t>Al cambiar una vez, se bloquea el botón y no se puede cambiar entre grande, mediana, pequeña. Es necesario cambiar de pestaña
+No se ve cambio en el tamaño de la letra.</t>
+  </si>
+  <si>
+    <t>1. The user changes the size letter (an example is shown)</t>
+  </si>
+  <si>
+    <t>1 .The size letter is changed
+2. The example is shown correctly.</t>
+  </si>
+  <si>
+    <t>1. The user changes between light/dark</t>
+  </si>
+  <si>
+    <t>1. The appaearance is changed</t>
+  </si>
+  <si>
+    <t>Una vez que se cambia la apariencia, el botón se queda bloqueado y es necesario cambiar de pestaña.</t>
+  </si>
+  <si>
+    <t>Una vez que se cambia la apariencia, el botón se queda bloqueado y es necesario cambiar de pestaña. 
+Se debe explicar que es el modo normal, y el modo ciego</t>
+  </si>
+  <si>
+    <t>1. The mode is changed</t>
+  </si>
+  <si>
+    <t>Settings: Appearance, tables' map</t>
+  </si>
+  <si>
+    <t>1. The user changes tables' map between fixed/automatic</t>
+  </si>
+  <si>
+    <t>1. The tables' map is changed.</t>
+  </si>
+  <si>
+    <t>1. The user changes mode between normal/blind</t>
+  </si>
+  <si>
+    <t>1. The option is changed.</t>
+  </si>
+  <si>
+    <t>1. The user can delete the account</t>
+  </si>
+  <si>
+    <t>Aparece un mensaje diciendo que refiere configuración adicional.</t>
+  </si>
+  <si>
+    <t>1. The user can change the language</t>
+  </si>
+  <si>
+    <t>1.The language is changed</t>
+  </si>
+  <si>
+    <t>1.The language is not changed</t>
+  </si>
+  <si>
+    <t>El valor en el campo se cambia, pero la app sigue en español.</t>
+  </si>
+  <si>
+    <t>1. The user can close the session</t>
+  </si>
+  <si>
+    <t>1. The session is closed</t>
+  </si>
+  <si>
+    <t>Con solo un ipad no se puede probar esta funcionalidad.</t>
+  </si>
+  <si>
+    <t>1.The user can enabled/disabled the ipad as Principal</t>
+  </si>
+  <si>
+    <t>1. The ipad is enabled/disabled as principal.</t>
+  </si>
+  <si>
+    <t>1. The settings page is correctly</t>
+  </si>
+  <si>
+    <t>Request page</t>
+  </si>
+  <si>
+    <t>1. The user sees request page.</t>
+  </si>
+  <si>
+    <t>1. The request page is correctly</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nueva petición"
+2. Fills the fields.
+3. Clicks  "Enviar petición"</t>
+  </si>
+  <si>
+    <t>1. The request is sent.</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nueva petición"
+2. Fills the fields.
+3. Clicks  "Cancelar"</t>
+  </si>
+  <si>
+    <t>Request page: create, cancel.</t>
+  </si>
+  <si>
+    <t>Request page: create</t>
+  </si>
+  <si>
+    <t>No se pueden crear peticiones, con lo que no se pueden ver en Todas, abierto, En progreso, Esperando respuesta, Resuelto y Cerrado.</t>
+  </si>
+  <si>
+    <t>Request page, show by the type: all, open,in progress, wait response,resolve, close.</t>
+  </si>
+  <si>
+    <t>1. The printers page is correctly.</t>
+  </si>
+  <si>
+    <t>Printers page</t>
+  </si>
+  <si>
+    <t>Printers page: search type</t>
+  </si>
+  <si>
+    <t>1. The user changes the search type</t>
+  </si>
+  <si>
+    <t>1. The search type is changed.</t>
+  </si>
+  <si>
+    <t>1. The user can upload a logo</t>
+  </si>
+  <si>
+    <t>1. The logo es uploaded.</t>
+  </si>
+  <si>
+    <t>No se  puede comprobar, xq no  hay impresoras configurables, deberia de poder enviarse a un pdf, o algo.</t>
+  </si>
+  <si>
+    <t>1. The user can change the logo</t>
+  </si>
+  <si>
+    <t>1. The logo es changed.</t>
+  </si>
+  <si>
+    <t>Printers page: logo, delete</t>
+  </si>
+  <si>
+    <t>Printers page: logo, change</t>
+  </si>
+  <si>
+    <t>Printers page: logo, uoload</t>
+  </si>
+  <si>
+    <t>1. The user can delete the logo</t>
+  </si>
+  <si>
+    <t>1. The logo es deleted.</t>
+  </si>
+  <si>
+    <t>Printers page: configuration size</t>
+  </si>
+  <si>
+    <t>1. The size of the paper is configured.</t>
+  </si>
+  <si>
+    <t>Printers page: Titles</t>
+  </si>
+  <si>
+    <t>1. The user can configure the title and the footer</t>
+  </si>
+  <si>
+    <t>1. The tittle and the footer is configurated.</t>
+  </si>
+  <si>
+    <t>Printers page: QR</t>
+  </si>
+  <si>
+    <t>1. The user can configure a QR</t>
+  </si>
+  <si>
+    <t>1. The QR is configurated.</t>
+  </si>
+  <si>
+    <t>No se  puede comprobar, xq no  hay impresoras configurables</t>
+  </si>
+  <si>
+    <t>Printers page: test of the article</t>
+  </si>
+  <si>
+    <t>1. The user can define a test of the article</t>
+  </si>
+  <si>
+    <t>1. The test o f the article is created.</t>
+  </si>
+  <si>
+    <t>1. The user can define the search type: wifi, usb, manual, all search</t>
+  </si>
+  <si>
+    <t>The type of the seache is created.</t>
+  </si>
+  <si>
+    <t>1. The user can configure the size of the paper: 58mm, 80mm..</t>
+  </si>
+  <si>
+    <t>Promotions page</t>
+  </si>
+  <si>
+    <t>1. The promotions page is correctly.</t>
+  </si>
+  <si>
+    <t>Promotions: create, cancel</t>
+  </si>
+  <si>
+    <t>Promotions: modify</t>
+  </si>
+  <si>
+    <t>Promotions: modify, cancel</t>
+  </si>
+  <si>
+    <t>Promotions: delete</t>
+  </si>
+  <si>
+    <t>Promotions: delete, cancel</t>
+  </si>
+  <si>
+    <t>Promotions: search</t>
+  </si>
+  <si>
+    <t>Promotions: create mandatory parameters</t>
+  </si>
+  <si>
+    <t>Promotions: create all parameters</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nueva promoción"
+2. Fills the mandatory fields
+3. Clicks "Crear"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nueva promoción"
+2. Fills the all fields
+3. Clicks "Crear"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nueva promoción"
+2. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user clicks the pencil icon
+2. Modify fields
+3. Clicks "Actualizar"</t>
+  </si>
+  <si>
+    <t>1. The user clicks the pencil icon
+2. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user does a search</t>
+  </si>
+  <si>
+    <t>1. The search is correctly.</t>
+  </si>
+  <si>
+    <t>1. The promotion is created.</t>
+  </si>
+  <si>
+    <t>1. The promotion is modified.</t>
+  </si>
+  <si>
+    <t>El combo para teclear tapa los textos que se escribe y el botón de Crear: PROMO002.jpg</t>
+  </si>
+  <si>
+    <t>1. The promotion is deleted.</t>
+  </si>
+  <si>
+    <t>Products page</t>
+  </si>
+  <si>
+    <t>1. The user sees Products page</t>
+  </si>
+  <si>
+    <t>1. The Products page is correctly.</t>
+  </si>
+  <si>
+    <t>Products: create mandatory parameters</t>
+  </si>
+  <si>
+    <t>Products: create all parameters</t>
+  </si>
+  <si>
+    <t>Products: create, cancel</t>
+  </si>
+  <si>
+    <t>Products: modify</t>
+  </si>
+  <si>
+    <t>Products: modify, cancel</t>
+  </si>
+  <si>
+    <t>Products: delete</t>
+  </si>
+  <si>
+    <t>Products: delete, cancel</t>
+  </si>
+  <si>
+    <t>Products: search</t>
+  </si>
+  <si>
+    <t>El combo para teclear tapa los textos que se escribe y el botón de Actualizar: PROMO003.jpg</t>
+  </si>
+  <si>
+    <t>Products: activate/deactivate</t>
+  </si>
+  <si>
+    <t>1. The user changes the status: activate/deactivated</t>
+  </si>
+  <si>
+    <t>1. The status is changed</t>
+  </si>
+  <si>
+    <t>No aparece en ningún sitio, como activar/desactivar un producto.</t>
+  </si>
+  <si>
+    <t>Products: create with image</t>
+  </si>
+  <si>
+    <t>Products: modify with image</t>
+  </si>
+  <si>
+    <t>1. The user clicks the pencil icon
+2. Modify fields
+3. Clicks "Guardar cambios"</t>
+  </si>
+  <si>
+    <t>No funciona el botón "Subir archivo": PRO007.jpg</t>
+  </si>
+  <si>
+    <t>No funciona el botón "Subir archivo": PRO008.jpg</t>
+  </si>
+  <si>
+    <t>Se busca un número 5, pero la búsqueda no es correcta, para que encuentre el resultado, hay q introducir un espacio delante, algo q no debería ser necesario:PRO005.jpg</t>
+  </si>
+  <si>
+    <t>Modifiers page</t>
+  </si>
+  <si>
+    <t>1. The user sees Modifiers page</t>
+  </si>
+  <si>
+    <t>1. The Modifiers page is correctly.</t>
+  </si>
+  <si>
+    <t>Modifiers: create mandatory parameters</t>
+  </si>
+  <si>
+    <t>Modifiers: create all parameters</t>
+  </si>
+  <si>
+    <t>Modifiers: create, cancel</t>
+  </si>
+  <si>
+    <t>Modifiers: modify</t>
+  </si>
+  <si>
+    <t>Modifiers: modify, cancel</t>
+  </si>
+  <si>
+    <t>Modifiers: delete</t>
+  </si>
+  <si>
+    <t>Modifiers: delete, cancel</t>
+  </si>
+  <si>
+    <t>Modifiers: search</t>
+  </si>
+  <si>
+    <t>1. The modifier is modified.</t>
+  </si>
+  <si>
+    <t>1. The modifier is deleted.</t>
+  </si>
+  <si>
+    <t>Al modificar el modificador, el combo para escribir tapa la opción de "Guardar cambios": MOD003.jpg
+Al modificar el modificador ,se introduce como Selección máxima "11111111111111111" se, guarda, pero luego se ve la selección máxima con el valor de la selección mínima:MOD005_1.jpg y MOD005_2.jpg</t>
+  </si>
+  <si>
+    <t>1. The modifier  is created.</t>
+  </si>
+  <si>
+    <t>1. The Product is modified.</t>
+  </si>
+  <si>
+    <t>1. The Product is deleted.</t>
+  </si>
+  <si>
+    <t>1. The Product is created.</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nueva Product"
+2. Fills the mandatory fields
+3. Clicks "Imagen"
+4. Clicks "Subir archivo"
+3. Clicks "Crear producto"</t>
+  </si>
+  <si>
+    <t>1. The user clicks a Products
+2. Clicks "Imagen"
+3. Clicks "Subir archivo"
+4. Clicks "Guardar cambios"</t>
+  </si>
+  <si>
+    <t>1. The user clicks the garbage icon
+3. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user clicks the garbage icon
+3. Clicks "Eliminar"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nuevo producto"
+2. Fills the mandatory fields
+3. Clicks "Crear producto"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nuevo producto"
+2. Fills the all fields
+3. Clicks "Crear producto"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nuevo producto"
+2. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nuevo grupo"
+2. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The modifier is created.</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nuevo grupo"
+2. Fills the mandatory fields
+3. Clicks "Crear grupo"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nuevo grupo"
+2. Fills the all fields
+3. Clicks "Crear grupo"</t>
+  </si>
+  <si>
+    <t>Al crear el modificador no se tiene en cuenta que la Selección mínima sea menor que la selección máxima: MOD004.jpg</t>
+  </si>
+  <si>
+    <t>Categories page</t>
+  </si>
+  <si>
+    <t>1. The user sees Categories page</t>
+  </si>
+  <si>
+    <t>Categories: create mandatory parameters</t>
+  </si>
+  <si>
+    <t>Categories: create all parameters</t>
+  </si>
+  <si>
+    <t>Categories: create, cancel</t>
+  </si>
+  <si>
+    <t>Categories: modify</t>
+  </si>
+  <si>
+    <t>Categories: modify, cancel</t>
+  </si>
+  <si>
+    <t>Categories: delete</t>
+  </si>
+  <si>
+    <t>Categories: delete, cancel</t>
+  </si>
+  <si>
+    <t>Categories: search</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Añadir categoría"
+2. Fills the mandatory fields
+3. Clicks "Crear"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Añadir categoría"
+2. Fills the all fields
+3. Clicks "Crear"</t>
+  </si>
+  <si>
+    <t>1. The categories page is correctly.</t>
+  </si>
+  <si>
+    <t>1. The categorie  is created.</t>
+  </si>
+  <si>
+    <t>1. The categorie is created.</t>
+  </si>
+  <si>
+    <t>1. The categorie page is correctly.</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Añadir categoría"
+2. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The categorie is modified.</t>
+  </si>
+  <si>
+    <t>1. The categorie is deleted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No se indican los campos obligatorios y al pulsar "Crear" no hace nada. 
+La imagen del teclado impide ver el resto de la funcionalidad: CATEG004.jpg
+</t>
+  </si>
+  <si>
+    <t>Se busca el número 6, pero la búsqueda no es correcta, para que encuentre el resultado, hay q introducir un espacio delante, algo q no debería ser necesario:CATEG005.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los botones "Cancelar" y "Crear" salen cortados: CATEG003.jpg
+</t>
+  </si>
+  <si>
+    <t>Categories:rol, add</t>
+  </si>
+  <si>
+    <t>Categories:rol, delete</t>
+  </si>
+  <si>
+    <t>1. The user writes a name of the rol
+2. Clicks "Crear rol"</t>
+  </si>
+  <si>
+    <t>1. The rol is created.</t>
+  </si>
+  <si>
+    <t>Al crear un nombre muy largo se sale de la pantalla y no sale el icono de editar o borrar: CATEG001.jpg y CATEG002.jpg</t>
+  </si>
+  <si>
+    <t>1. The rol is modified.</t>
+  </si>
+  <si>
+    <t>1. The user clicks the pencil icon of a rol
+2. Modify the description</t>
+  </si>
+  <si>
+    <t>1. The rol is deleted.</t>
+  </si>
+  <si>
+    <t>Los botones "Cancelar" y "Guardar" salen cortados: CATEG006.jpg
+La imagen del teclado impide ver el resto de la funcionalidad: CATEG004.jpg
+En el listado de categorías se debe poner desplazamiento vertical</t>
+  </si>
+  <si>
+    <t>Añadir barra de desplazamiento lateral en el listado de Categorías</t>
+  </si>
+  <si>
+    <t>Añadir barra de desplazamiento lateral en el listado de modificadores</t>
+  </si>
+  <si>
+    <t>Añadir barra de desplazamiento lateral en el listado de productos.</t>
+  </si>
+  <si>
+    <t>Añadir barra de desplazamiento lateral en el listado de promociones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La opción aparece cortada: printer001.jpg
+</t>
+  </si>
+  <si>
+    <t>BLOQUEANTE: No hace nada, al pulsar "Enviar petición"</t>
+  </si>
+  <si>
+    <t>Asegurarse de poner barra lateral en el listado para desplazarse.</t>
+  </si>
+  <si>
+    <t>Categories:rol, modify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks the garbage icon of a rol
+</t>
+  </si>
+  <si>
+    <t>Debería de preguntar si se quiere modificar y permitir cancelar.</t>
+  </si>
+  <si>
+    <t>Debería de preguntar si se quiere borrar y permitir cancelar.</t>
+  </si>
+  <si>
+    <t>Users: create mandatory parameters</t>
+  </si>
+  <si>
+    <t>Users: create all parameters</t>
+  </si>
+  <si>
+    <t>Users: create, cancel</t>
+  </si>
+  <si>
+    <t>Users: modify</t>
+  </si>
+  <si>
+    <t>Users: modify, cancel</t>
+  </si>
+  <si>
+    <t>Users: delete</t>
+  </si>
+  <si>
+    <t>Users: delete, cancel</t>
+  </si>
+  <si>
+    <t>Users: search</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nuevo usuario"
+2. Fills the mandatory fields
+3. Clicks "Crear"</t>
+  </si>
+  <si>
+    <t>1. The user is created.</t>
+  </si>
+  <si>
+    <t>1. The user  is created.</t>
+  </si>
+  <si>
+    <t>1. The user is modified.</t>
+  </si>
+  <si>
+    <t>1. The user is deleted.</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Añadir usuario"
+2. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Añadir usuario"
+2. Fills the all fields
+3. Clicks "Crear"</t>
+  </si>
+  <si>
+    <t>Users: hide/show pin</t>
+  </si>
+  <si>
+    <t>1. The user can hide/show the pin</t>
+  </si>
+  <si>
+    <t>1. The pin is hidden/shown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los nombres largos machacan el campo anexo: USER004.jpg
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No se indican los campos obligatorios y al pulsar "Guardar" no hace nada: USER003.jpg
+La imagen del teclado impide ver el resto de la funcionalidad
+En pin de acceso, pone 4 dígitos pero pueden ser menos. Si se obligatorio 4 hay que indicarlo, sino cambiar leyenda con "Máximo 4 dígitos":USER005.jpg
+</t>
+  </si>
+  <si>
+    <t>Tables' map: place table</t>
+  </si>
+  <si>
+    <t>1 .The user creates a table
+2. Places table</t>
+  </si>
+  <si>
+    <t>1. The table is placed</t>
+  </si>
+  <si>
+    <t>Tables' map: place zoom</t>
+  </si>
+  <si>
+    <t>1.The zoom works perfectly.</t>
+  </si>
+  <si>
+    <t>1.The zoom works perfectly</t>
+  </si>
+  <si>
+    <t>1 .The user can do zoom,  between 50% and 200%</t>
+  </si>
+  <si>
+    <t>Tables's map: zones, create, cancel</t>
+  </si>
+  <si>
+    <t>1. The zone is created.</t>
+  </si>
+  <si>
+    <t>Tables's map: zones, create with mandatory fields</t>
+  </si>
+  <si>
+    <t>Tables's map: zones, create with all fields</t>
+  </si>
+  <si>
+    <t>1. The user creates a zone
+2. Clicks "</t>
+  </si>
+  <si>
+    <t>1. The user creates a zone
+2. Fills all parameters
+3. Clicks "Guardar cambios"</t>
+  </si>
+  <si>
+    <t>1. The user creates a zone
+2. Fils mandatory parameters
+3. Clicks "Guardar cambios"</t>
+  </si>
+  <si>
+    <t>Tables' map: modify size</t>
+  </si>
+  <si>
+    <t>1 .The user selects a table
+2. Modify dimensions</t>
+  </si>
+  <si>
+    <t>1.The table is modified</t>
+  </si>
+  <si>
+    <t>Se han cambiado las medidas de una mesa rectangular y no se actualiza.</t>
+  </si>
+  <si>
+    <t>No están indicados los campos obligatorios, el teclado machaca el resto de la funcionalidad: ZONE001.jpg,ZONE002.jpg</t>
+  </si>
+  <si>
+    <t>BLOQUEANTE: Se ha creado una zona, con tres mesas, una redonda y luego una mesa de 800x1550. Al crear la grande, no se ve ninguna: zone002.jpg, en otros casos solo se ve un trozo: ZONE003.jpg</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Gestionar tarifas"
+2. Clicks "Crear nueva tarifa"
+2. Fills the mandatory fields</t>
+  </si>
+  <si>
+    <t>1.The tax is created</t>
+  </si>
+  <si>
+    <t>Tables' map: manage rates, create with mandatory fields</t>
+  </si>
+  <si>
+    <t>Tables' map: manage rates, create with all fields</t>
+  </si>
+  <si>
+    <t>Tables' map: manage rates, create , cancel</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Gestionar tarifas"
+2. Clicks "Crear nueva tarifa"
+2. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Gestionar tarifas"
+2. Clicks "Crear nueva tarifa"
+2. Fills the all fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No se indican campos obligatorios con el *. </t>
+  </si>
+  <si>
+    <t>Al salir el teclado emergente tapa la funcionalidad: ZONE005.jpg</t>
+  </si>
+  <si>
+    <t>Tables' map: manage rates, modify</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Gestionar tarifas"
+2. Clicks the pencil of a tax
+3. Modify the tax
+4. Clicks "Guardar"</t>
+  </si>
+  <si>
+    <t>1. The tax is modified</t>
+  </si>
+  <si>
+    <t>Tables' map: manage rates, modify, cancel</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Gestionar tarifas"
+2. Clicks the pencil of a tax
+3. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>Tables' map: manage rates, delete</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Gestionar tarifas"
+2. Clicks the pencil of a tax
+3. Clicks "Eliminar"</t>
+  </si>
+  <si>
+    <t>No hay pregunta de confirmación antes de borrar, ni dice si afecta a las mesas abiertas, o ya cerradas..
+Además por uniformidad con el resto de la app, debería haber una papelera para borrar al lado del lapiz, no que este esa operación dentro de la edición</t>
+  </si>
+  <si>
+    <t>Menus: create</t>
+  </si>
+  <si>
+    <t>Menus: page</t>
+  </si>
+  <si>
+    <t>Menus: modify</t>
+  </si>
+  <si>
+    <t>Menus: delete</t>
+  </si>
+  <si>
+    <t>Menus_types: page</t>
+  </si>
+  <si>
+    <t>1. The user sees Menus_types page</t>
+  </si>
+  <si>
+    <t>Menus_types: create</t>
+  </si>
+  <si>
+    <t>Menus_types: modify</t>
+  </si>
+  <si>
+    <t>Menus_types: delete</t>
+  </si>
+  <si>
+    <t>Menus_types: create, Cancel</t>
+  </si>
+  <si>
+    <t>Menus_types: modify, Cancel</t>
+  </si>
+  <si>
+    <t>Menus_types: delete, Cancel</t>
+  </si>
+  <si>
+    <t>Menus: create, cancel</t>
+  </si>
+  <si>
+    <t>Menus: modify, cancel</t>
+  </si>
+  <si>
+    <t>Menus: delete, cancel</t>
+  </si>
+  <si>
+    <t>Menus_types: see</t>
+  </si>
+  <si>
+    <t>Menus_types: see, Cancel</t>
+  </si>
+  <si>
+    <t>Al pulsar en el icono del ojo, se muestra editar.</t>
+  </si>
+  <si>
+    <t>Menus_types: actived</t>
+  </si>
+  <si>
+    <t>Menus_types: deactivated</t>
+  </si>
+  <si>
+    <t>No se puede subir una imagen de una carta: MEN001.jpg</t>
+  </si>
+  <si>
+    <t>No se puede modificar:MEN002.jpg</t>
+  </si>
+  <si>
+    <t>No tiene botón cancelar, como el resto de funcionalidad, solo se puede con el aspa.</t>
+  </si>
+  <si>
+    <t>¿no se puede cambiar el tipo de carta? Solo pone MAESTRA</t>
+  </si>
+  <si>
+    <t>La operación "Nueva factura" aparece dos veces: FAC001.jpg
+funcionalidad desactivada: FAC004.jpg</t>
+  </si>
+  <si>
+    <t>USERADM039</t>
+  </si>
+  <si>
+    <t>USERADM040</t>
+  </si>
+  <si>
+    <t>USERADM041</t>
+  </si>
+  <si>
+    <t>USERADM042</t>
+  </si>
+  <si>
+    <t>USERADM043</t>
+  </si>
+  <si>
+    <t>USERADM044</t>
+  </si>
+  <si>
+    <t>USERADM053</t>
+  </si>
+  <si>
+    <t>USERADM056</t>
+  </si>
+  <si>
+    <t>USERADM064</t>
+  </si>
+  <si>
+    <t>USERADM065</t>
+  </si>
+  <si>
+    <t>USERADM066</t>
+  </si>
+  <si>
+    <t>USERADM067</t>
+  </si>
+  <si>
+    <t>USERADM068</t>
+  </si>
+  <si>
+    <t>USERADM069</t>
+  </si>
+  <si>
+    <t>USERADM070</t>
+  </si>
+  <si>
+    <t>USERADM071</t>
+  </si>
+  <si>
+    <t>USERADM072</t>
+  </si>
+  <si>
+    <t>USERADM073</t>
+  </si>
+  <si>
+    <t>USERADM074</t>
+  </si>
+  <si>
+    <t>USERADM075</t>
+  </si>
+  <si>
+    <t>USERADM076</t>
+  </si>
+  <si>
+    <t>USERADM077</t>
+  </si>
+  <si>
+    <t>USERADM078</t>
+  </si>
+  <si>
+    <t>USERADM079</t>
+  </si>
+  <si>
+    <t>USERADM080</t>
+  </si>
+  <si>
+    <t>USERADM081</t>
+  </si>
+  <si>
+    <t>USERADM082</t>
+  </si>
+  <si>
+    <t>USERADM083</t>
+  </si>
+  <si>
+    <t>USERADM084</t>
+  </si>
+  <si>
+    <t>USERADM085</t>
+  </si>
+  <si>
+    <t>USERADM086</t>
+  </si>
+  <si>
+    <t>USERADM087</t>
+  </si>
+  <si>
+    <t>USERADM088</t>
+  </si>
+  <si>
+    <t>USERADM089</t>
+  </si>
+  <si>
+    <t>USERADM090</t>
+  </si>
+  <si>
+    <t>USERADM091</t>
+  </si>
+  <si>
+    <t>USERADM092</t>
+  </si>
+  <si>
+    <t>USERADM093</t>
+  </si>
+  <si>
+    <t>USERADM094</t>
+  </si>
+  <si>
+    <t>USERADM095</t>
+  </si>
+  <si>
+    <t>USERADM096</t>
+  </si>
+  <si>
+    <t>USERADM097</t>
+  </si>
+  <si>
+    <t>USERADM098</t>
+  </si>
+  <si>
+    <t>USERADM099</t>
+  </si>
+  <si>
+    <t>USERADM100</t>
+  </si>
+  <si>
+    <t>USERADM101</t>
+  </si>
+  <si>
+    <t>USERADM102</t>
+  </si>
+  <si>
+    <t>USERADM103</t>
+  </si>
+  <si>
+    <t>USERADM104</t>
+  </si>
+  <si>
+    <t>USERADM105</t>
+  </si>
+  <si>
+    <t>USERADM106</t>
+  </si>
+  <si>
+    <t>USERADM107</t>
+  </si>
+  <si>
+    <t>USERADM108</t>
+  </si>
+  <si>
+    <t>USERADM109</t>
+  </si>
+  <si>
+    <t>USERADM110</t>
+  </si>
+  <si>
+    <t>USERADM111</t>
+  </si>
+  <si>
+    <t>USERADM112</t>
+  </si>
+  <si>
+    <t>USERADM113</t>
+  </si>
+  <si>
+    <t>USERADM114</t>
+  </si>
+  <si>
+    <t>USERADM115</t>
+  </si>
+  <si>
+    <t>USERADM116</t>
+  </si>
+  <si>
+    <t>USERADM117</t>
+  </si>
+  <si>
+    <t>USERADM118</t>
+  </si>
+  <si>
+    <t>USERADM119</t>
+  </si>
+  <si>
+    <t>USERADM120</t>
+  </si>
+  <si>
+    <t>USERADM121</t>
+  </si>
+  <si>
+    <t>USERADM122</t>
+  </si>
+  <si>
+    <t>USERADM123</t>
+  </si>
+  <si>
+    <t>USERADM124</t>
+  </si>
+  <si>
+    <t>USERADM125</t>
+  </si>
+  <si>
+    <t>USERADM126</t>
+  </si>
+  <si>
+    <t>USERADM127</t>
+  </si>
+  <si>
+    <t>USERADM128</t>
+  </si>
+  <si>
+    <t>USERADM129</t>
+  </si>
+  <si>
+    <t>USERADM130</t>
+  </si>
+  <si>
+    <t>USERADM131</t>
+  </si>
+  <si>
+    <t>USERADM132</t>
+  </si>
+  <si>
+    <t>USERADM133</t>
+  </si>
+  <si>
+    <t>USERADM134</t>
+  </si>
+  <si>
+    <t>USERADM135</t>
+  </si>
+  <si>
+    <t>USERADM136</t>
+  </si>
+  <si>
+    <t>USERADM137</t>
+  </si>
+  <si>
+    <t>USERADM138</t>
+  </si>
+  <si>
+    <t>USERADM139</t>
+  </si>
+  <si>
+    <t>USERADM140</t>
+  </si>
+  <si>
+    <t>USERADM141</t>
+  </si>
+  <si>
+    <t>USERADM142</t>
+  </si>
+  <si>
+    <t>USERADM143</t>
+  </si>
+  <si>
+    <t>USERADM144</t>
+  </si>
+  <si>
+    <t>USERADM145</t>
+  </si>
+  <si>
+    <t>USERADM146</t>
+  </si>
+  <si>
+    <t>USERADM147</t>
+  </si>
+  <si>
+    <t>USERADM148</t>
+  </si>
+  <si>
+    <t>USERADM149</t>
+  </si>
+  <si>
+    <t>USERADM150</t>
+  </si>
+  <si>
+    <t>USERADM151</t>
+  </si>
+  <si>
+    <t>USERADM152</t>
+  </si>
+  <si>
+    <t>USERADM153</t>
+  </si>
+  <si>
+    <t>USERADM154</t>
+  </si>
+  <si>
+    <t>USERADM155</t>
+  </si>
+  <si>
+    <t>USERADM156</t>
+  </si>
+  <si>
+    <t>USERADM157</t>
+  </si>
+  <si>
+    <t>USERADM158</t>
+  </si>
+  <si>
+    <t>USERADM159</t>
+  </si>
+  <si>
+    <t>USERADM160</t>
+  </si>
+  <si>
+    <t>USERADM161</t>
+  </si>
+  <si>
+    <t>Views of tables:Take order: Fee</t>
+  </si>
+  <si>
+    <t>Cash closing: Normal cash register closing declared</t>
+  </si>
+  <si>
+    <t>Cash closing: Automatic cash register closing</t>
+  </si>
+  <si>
+    <t>Cash closing:  Cancelled</t>
+  </si>
+  <si>
+    <t>Tickets' history: Page</t>
+  </si>
+  <si>
+    <t>Cash closing: page</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order, Add modifiers</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order, Add modifiers, cancel</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order, pay the bill</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order, Add product</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order, Delete product</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order, Cancel,add product</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order, send order</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order, change type of menu</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order,find a product</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order, Join table</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order</t>
+  </si>
+  <si>
+    <t>Views of tables: page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user sees the Views of tables page
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+  </si>
+  <si>
+    <t>Se ha introducido un número desorbitado de comensales, y al ir a pagar, se ha cerrado la aplicación.
+El menu sale cortado. Waiter002.jpg</t>
+  </si>
+  <si>
+    <t>1. The user writes a word in the find space</t>
+  </si>
+  <si>
+    <t>1. The search is displayed</t>
+  </si>
+  <si>
+    <t>No hay tickets</t>
   </si>
 </sst>
 </file>
@@ -1199,7 +2454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -1243,23 +2498,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -1267,19 +2522,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1"/>
+        <v>597</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>598</v>
+      </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>31</v>
+        <v>599</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -1287,21 +2544,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>29</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1309,21 +2566,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>595</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1331,21 +2588,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>580</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1353,18 +2610,18 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>593</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="2" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H7" s="3"/>
     </row>
@@ -1373,18 +2630,18 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>594</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H8" s="3"/>
     </row>
@@ -1393,18 +2650,18 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>20</v>
+        <v>586</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H9" s="3"/>
     </row>
@@ -1413,18 +2670,18 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>21</v>
+        <v>587</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H10" s="3"/>
     </row>
@@ -1433,21 +2690,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>26</v>
+        <v>588</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1455,23 +2712,23 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>33</v>
+        <v>589</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1479,22 +2736,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>34</v>
+        <v>590</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H13" s="3"/>
     </row>
@@ -1503,23 +2760,23 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>40</v>
+        <v>591</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1527,23 +2784,23 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>66</v>
+        <v>592</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -1551,23 +2808,23 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>90</v>
+        <v>585</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="2" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -1575,20 +2832,20 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>102</v>
+        <v>581</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H17" s="3"/>
     </row>
@@ -1597,20 +2854,20 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>102</v>
+        <v>581</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H18" s="3"/>
     </row>
@@ -1619,20 +2876,20 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>103</v>
+        <v>582</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H19" s="3"/>
     </row>
@@ -1641,22 +2898,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>104</v>
+        <v>583</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H20" s="3"/>
     </row>
@@ -1665,23 +2922,23 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -1689,20 +2946,20 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H22" s="3"/>
     </row>
@@ -1711,23 +2968,23 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -1735,25 +2992,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>193</v>
+        <v>584</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>192</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1761,1010 +3018,3190 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
+        <v>132</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>602</v>
+      </c>
       <c r="F25" s="1"/>
       <c r="G25" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="C26" s="1" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="3"/>
+      <c r="G26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="C27" s="1" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>174</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="C28" s="1" t="s">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="C29" s="1" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>217</v>
+        <v>473</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="2" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>194</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>194</v>
+        <v>150</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>199</v>
+        <v>155</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>216</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>195</v>
+        <v>151</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>198</v>
+        <v>154</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>218</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>196</v>
+        <v>152</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>197</v>
+        <v>153</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H34" s="3"/>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>200</v>
+        <v>156</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>201</v>
+        <v>157</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H35" s="3"/>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>219</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>205</v>
+        <v>161</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>207</v>
+        <v>163</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>215</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>206</v>
+        <v>162</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>208</v>
+        <v>164</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>214</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>209</v>
+        <v>165</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>214</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>107</v>
+        <v>474</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>211</v>
+        <v>167</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>212</v>
+        <v>168</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>213</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>107</v>
+        <v>475</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D41" s="1"/>
+        <v>453</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>454</v>
+      </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H41" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>472</v>
+      </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>108</v>
+        <v>476</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>179</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H42" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C43" s="1"/>
+        <v>477</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>468</v>
+      </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H43" s="3"/>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C44" s="1"/>
+        <v>478</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>455</v>
+      </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H44" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>469</v>
+      </c>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>111</v>
+        <v>479</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>180</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C46" s="1"/>
+        <v>112</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>465</v>
+      </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H46" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>471</v>
+      </c>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C47" s="1"/>
+        <v>113</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>458</v>
+      </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H47" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>470</v>
+      </c>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>181</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H48" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>470</v>
+      </c>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C49" s="1"/>
+        <v>115</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>459</v>
+      </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H49" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>470</v>
+      </c>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C50" s="1"/>
+        <v>116</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>456</v>
+      </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H50" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>470</v>
+      </c>
     </row>
     <row r="51" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>182</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H51" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>470</v>
+      </c>
     </row>
     <row r="52" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C52" s="1"/>
+        <v>118</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>457</v>
+      </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H52" s="3"/>
-    </row>
-    <row r="53" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C53" s="1"/>
+        <v>119</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>460</v>
+      </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H53" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>470</v>
+      </c>
     </row>
     <row r="54" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>141</v>
+        <v>480</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>125</v>
+        <v>450</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>183</v>
+        <v>142</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H54" s="3"/>
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C55" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>449</v>
+      </c>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H55" s="3"/>
     </row>
-    <row r="56" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C56" s="1"/>
+        <v>121</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>461</v>
+      </c>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H56" s="3"/>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>144</v>
+        <v>481</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>184</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H57" s="3"/>
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C58" s="1"/>
+        <v>122</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>462</v>
+      </c>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H58" s="3"/>
     </row>
-    <row r="59" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C59" s="1"/>
+        <v>123</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>451</v>
+      </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H59" s="3"/>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>185</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H60" s="3"/>
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C61" s="1"/>
+        <v>125</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>452</v>
+      </c>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H61" s="3"/>
     </row>
-    <row r="62" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C62" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>463</v>
+      </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H62" s="3"/>
     </row>
-    <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>128</v>
+        <v>421</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E63" s="1"/>
+        <v>425</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>420</v>
+      </c>
       <c r="F63" s="1"/>
       <c r="G63" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H63" s="3"/>
-    </row>
-    <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>420</v>
+      </c>
       <c r="F64" s="1"/>
       <c r="G64" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H64" s="3"/>
-    </row>
-    <row r="65" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
+        <v>482</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="G65" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H65" s="3"/>
     </row>
-    <row r="66" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>153</v>
+        <v>483</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>129</v>
+        <v>412</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
+        <v>413</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>414</v>
+      </c>
       <c r="G66" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H66" s="3"/>
     </row>
-    <row r="67" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
+        <v>484</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>416</v>
+      </c>
       <c r="G67" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H67" s="3"/>
     </row>
-    <row r="68" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
+        <v>485</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>428</v>
+      </c>
       <c r="F68" s="1"/>
       <c r="G68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
         <v>68</v>
       </c>
-      <c r="H68" s="3"/>
-    </row>
-    <row r="69" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
-        <v>54</v>
-      </c>
       <c r="B69" s="1" t="s">
-        <v>156</v>
+        <v>486</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>130</v>
+        <v>434</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E69" s="1"/>
+        <v>432</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>433</v>
+      </c>
       <c r="F69" s="1"/>
       <c r="G69" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H69" s="3"/>
-    </row>
-    <row r="70" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
+        <v>487</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>433</v>
+      </c>
       <c r="F70" s="1"/>
       <c r="G70" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H70" s="3"/>
-    </row>
-    <row r="71" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
+        <v>488</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="G71" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H71" s="3"/>
     </row>
-    <row r="72" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>159</v>
+        <v>489</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>131</v>
+        <v>441</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
+        <v>442</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>443</v>
+      </c>
       <c r="G72" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H72" s="3"/>
     </row>
-    <row r="73" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
+        <v>490</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="G73" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H73" s="3"/>
     </row>
-    <row r="74" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>161</v>
+        <v>491</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>132</v>
+        <v>446</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E74" s="1"/>
+        <v>447</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>209</v>
+      </c>
       <c r="F74" s="1"/>
       <c r="G74" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H74" s="3"/>
-    </row>
-    <row r="75" spans="1:8" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
+        <v>492</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>401</v>
+      </c>
       <c r="F75" s="1"/>
       <c r="G75" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H75" s="3"/>
-    </row>
-    <row r="76" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="F76" s="1"/>
+      <c r="G76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H77" s="3"/>
+    </row>
+    <row r="78" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H78" s="3"/>
+    </row>
+    <row r="79" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H79" s="3"/>
+    </row>
+    <row r="80" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H80" s="3"/>
+    </row>
+    <row r="81" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H81" s="3"/>
+    </row>
+    <row r="82" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H82" s="3"/>
+    </row>
+    <row r="83" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H83" s="3"/>
+    </row>
+    <row r="84" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F85" s="1"/>
+      <c r="G85" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="F86" s="1"/>
+      <c r="G86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H87" s="3"/>
+    </row>
+    <row r="88" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="F88" s="1"/>
+      <c r="G88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H89" s="3"/>
+    </row>
+    <row r="90" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H90" s="3"/>
+    </row>
+    <row r="91" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H91" s="3"/>
+    </row>
+    <row r="92" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F92" s="1"/>
+      <c r="G92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="F93" s="1"/>
+      <c r="G93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="F94" s="1"/>
+      <c r="G94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="F95" s="1"/>
+      <c r="G95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F97" s="1"/>
+      <c r="G97" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H97" s="3"/>
+    </row>
+    <row r="98" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="F98" s="1"/>
+      <c r="G98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H99" s="3"/>
+    </row>
+    <row r="100" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H101" s="3"/>
+    </row>
+    <row r="102" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H102" s="3"/>
+    </row>
+    <row r="103" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H103" s="3"/>
+    </row>
+    <row r="104" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H104" s="3"/>
+    </row>
+    <row r="105" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H106" s="3"/>
+    </row>
+    <row r="107" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F107" s="1"/>
+      <c r="G107" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H107" s="3"/>
+    </row>
+    <row r="108" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H108" s="3"/>
+    </row>
+    <row r="109" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H109" s="3"/>
+    </row>
+    <row r="110" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H110" s="3"/>
+    </row>
+    <row r="111" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H111" s="3"/>
+    </row>
+    <row r="112" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H112" s="3">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="F114" s="1"/>
+      <c r="G114" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F115" s="1"/>
+      <c r="G115" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F116" s="1"/>
+      <c r="G116" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H118" s="3"/>
+    </row>
+    <row r="119" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H120" s="3"/>
+    </row>
+    <row r="121" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H122" s="3"/>
+    </row>
+    <row r="123" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H123" s="3"/>
+    </row>
+    <row r="124" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H124" s="3"/>
+    </row>
+    <row r="125" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H125" s="3"/>
+    </row>
+    <row r="126" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F126" s="1"/>
+      <c r="G126" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F127" s="1"/>
+      <c r="G127" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F128" s="1"/>
+      <c r="G128" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="F129" s="1"/>
+      <c r="G129" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="F130" s="1"/>
+      <c r="G130" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F131" s="1"/>
+      <c r="G131" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F132" s="1"/>
+      <c r="G132" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F133" s="1"/>
+      <c r="G133" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F134" s="1"/>
+      <c r="G134" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H136" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F137" s="1"/>
+      <c r="G137" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H138" s="3"/>
+    </row>
+    <row r="139" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H140" s="3"/>
+    </row>
+    <row r="141" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F141" s="1"/>
+      <c r="G141" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H142" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H143" s="3"/>
+    </row>
+    <row r="144" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E144" s="1"/>
+      <c r="F144" s="1"/>
+      <c r="G144" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H144" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F145" s="1"/>
+      <c r="G145" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H145" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F146" s="1"/>
+      <c r="G146" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F147" s="1"/>
+      <c r="G147" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F148" s="1"/>
+      <c r="G148" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F149" s="1"/>
+      <c r="G149" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H149" s="3"/>
+    </row>
+    <row r="150" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H150" s="3"/>
+    </row>
+    <row r="151" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H151" s="3"/>
+    </row>
+    <row r="152" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H152" s="3"/>
+    </row>
+    <row r="153" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F153" s="1"/>
+      <c r="G153" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F154" s="1"/>
+      <c r="G154" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H154" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F155" s="1"/>
+      <c r="G155" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H155" s="3"/>
+    </row>
+    <row r="156" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H156" s="3"/>
+    </row>
+    <row r="157" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F157" s="1"/>
+      <c r="G157" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H157" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F158" s="1"/>
+      <c r="G158" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H158" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F159" s="1"/>
+      <c r="G159" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H159" s="3"/>
+    </row>
+    <row r="160" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H160" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E161" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
+      <c r="F161" s="1"/>
+      <c r="G161" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="C162" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F77" s="1"/>
-      <c r="G77" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H77" s="3"/>
-    </row>
-    <row r="78" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
+      <c r="D162" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H78" s="3"/>
+      <c r="E162" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H162" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G78">
+  <conditionalFormatting sqref="G2:G162">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>

--- a/App/TestCases_App/User_admin.xlsx
+++ b/App/TestCases_App/User_admin.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F083B8DC-4EF7-4922-93D3-9A629ED9484A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E1F1D03-483B-4F08-910B-841B9E7DC6E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="649">
   <si>
     <t>Num</t>
   </si>
@@ -84,12 +83,6 @@
   </si>
   <si>
     <t>1. Select numbers of people
-2. Select find product
-3. Add product
-4. Clicks "Cerrar mesa"</t>
-  </si>
-  <si>
-    <t>1. Select numbers of people
 2. Select a product
 3. Add a modifier, clicks "Añadir al pedido"
 4. Clicks "Cerrar mesa"</t>
@@ -486,9 +479,6 @@
     <t>1. The tickets' history page is shown.</t>
   </si>
   <si>
-    <t>Tickets' history: find</t>
-  </si>
-  <si>
     <t>Funciona "Buscar tickets" , pero no "Rango de fechas"</t>
   </si>
   <si>
@@ -609,14 +599,8 @@
 2. Clicks "Opciones generales"</t>
   </si>
   <si>
-    <t>Invoicing: Settings, verifactu</t>
-  </si>
-  <si>
     <t>1. The user clicks "Configuración"
 2. Clicks "Verifactu"</t>
-  </si>
-  <si>
-    <t>Traducir, verifactu y  añadir funcionalidad</t>
   </si>
   <si>
     <t>Sale vacio, añadir funcionalidad</t>
@@ -1444,10 +1428,6 @@
   </si>
   <si>
     <t>1. The user creates a zone
-2. Clicks "</t>
-  </si>
-  <si>
-    <t>1. The user creates a zone
 2. Fills all parameters
 3. Clicks "Guardar cambios"</t>
   </si>
@@ -1559,24 +1539,6 @@
     <t>1. The user sees Menus_types page</t>
   </si>
   <si>
-    <t>Menus_types: create</t>
-  </si>
-  <si>
-    <t>Menus_types: modify</t>
-  </si>
-  <si>
-    <t>Menus_types: delete</t>
-  </si>
-  <si>
-    <t>Menus_types: create, Cancel</t>
-  </si>
-  <si>
-    <t>Menus_types: modify, Cancel</t>
-  </si>
-  <si>
-    <t>Menus_types: delete, Cancel</t>
-  </si>
-  <si>
     <t>Menus: create, cancel</t>
   </si>
   <si>
@@ -1586,15 +1548,6 @@
     <t>Menus: delete, cancel</t>
   </si>
   <si>
-    <t>Menus_types: see</t>
-  </si>
-  <si>
-    <t>Menus_types: see, Cancel</t>
-  </si>
-  <si>
-    <t>Al pulsar en el icono del ojo, se muestra editar.</t>
-  </si>
-  <si>
     <t>Menus_types: actived</t>
   </si>
   <si>
@@ -1607,16 +1560,9 @@
     <t>No se puede modificar:MEN002.jpg</t>
   </si>
   <si>
-    <t>No tiene botón cancelar, como el resto de funcionalidad, solo se puede con el aspa.</t>
-  </si>
-  <si>
     <t>¿no se puede cambiar el tipo de carta? Solo pone MAESTRA</t>
   </si>
   <si>
-    <t>La operación "Nueva factura" aparece dos veces: FAC001.jpg
-funcionalidad desactivada: FAC004.jpg</t>
-  </si>
-  <si>
     <t>USERADM039</t>
   </si>
   <si>
@@ -1975,9 +1921,6 @@
   </si>
   <si>
     <t>Views of tables: Take order, change type of menu</t>
-  </si>
-  <si>
-    <t>Views of tables: Take order,find a product</t>
   </si>
   <si>
     <t>Views of tables: Take order, Join table</t>
@@ -2001,13 +1944,226 @@
 El menu sale cortado. Waiter002.jpg</t>
   </si>
   <si>
-    <t>1. The user writes a word in the find space</t>
-  </si>
-  <si>
     <t>1. The search is displayed</t>
   </si>
   <si>
     <t>No hay tickets</t>
+  </si>
+  <si>
+    <t>1.The user writes a world in the box of the search</t>
+  </si>
+  <si>
+    <t>Menus_types: search</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order,search a product</t>
+  </si>
+  <si>
+    <t>1. Select numbers of people
+2. Select search product
+3. Add product
+4. Clicks "Cerrar mesa"</t>
+  </si>
+  <si>
+    <t>Tickets' history: search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user writes a word in the box of search </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invoicing: Add, mandatory fields
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La operación "Nueva factura" aparece dos veces: FAC001.jpg
+funcionalidad desactivada: FAC004.jpg
+BLOQUEANTE 30/04/26: No se puede crear factura </t>
+  </si>
+  <si>
+    <t>Invoicing: Settings</t>
+  </si>
+  <si>
+    <t>Traducir verifactu y mostrar un mensaje/funcionalidad, cuando se activa/desactiva</t>
+  </si>
+  <si>
+    <t>Sale vacio, añadir funcionalidad
+30/04/26 Sale lo mismo que en Verifactu</t>
+  </si>
+  <si>
+    <t>Invoicing: Taxes book</t>
+  </si>
+  <si>
+    <t>Invoicing: Reports</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Configuración"
+2. Clicks "Libro de facturación"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Configuración"
+2. Clicks "Informes fiscales"</t>
+  </si>
+  <si>
+    <t>La operación está deshabilitada</t>
+  </si>
+  <si>
+    <t>USERADM162</t>
+  </si>
+  <si>
+    <t>USERADM163</t>
+  </si>
+  <si>
+    <t>USERADM164</t>
+  </si>
+  <si>
+    <t>30/04/2026 : Error al eliminar: MOD005.jpg</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nuevo menu"
+2. Fills the fields
+3 Clicks "Crear menu"</t>
+  </si>
+  <si>
+    <t>1. The menu is created.</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nuevo menu"
+2. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The menu is modified.</t>
+  </si>
+  <si>
+    <t>1. The user clicks the pencil icon
+3. Clicks "Guardar cambios"</t>
+  </si>
+  <si>
+    <t>1. The user clicks the garbage icon
+2. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user clicks the garbage icon
+2. Clicks "Eliminar"</t>
+  </si>
+  <si>
+    <t>1. The menu is deleted.</t>
+  </si>
+  <si>
+    <t>1. The user clicks active status</t>
+  </si>
+  <si>
+    <t>1. The menu_type is activated</t>
+  </si>
+  <si>
+    <t>1. The user clicks deactive status</t>
+  </si>
+  <si>
+    <t>1. The menu_type is deactivated</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Añadir carta"
+2. Fills the first fields, clicks "Siguiente"
+3. Fills the second fields, clicks "Siguiente"
+4. Fills the third fields, clicks "Siguiente"
+5. Clicks "Finalizar y Guardar"</t>
+  </si>
+  <si>
+    <t>1.The user clicks eye icon (carta personalizada)</t>
+  </si>
+  <si>
+    <t>1. The user sees the menu_type</t>
+  </si>
+  <si>
+    <t>Se edita la carta, no se ve solo</t>
+  </si>
+  <si>
+    <t>1.The user clicks eye icon (carta personalizada)
+2. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Añadir carta"
+2. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The menu_type is created</t>
+  </si>
+  <si>
+    <t>Menus_types: modify (MAESTRA)</t>
+  </si>
+  <si>
+    <t>Menus_types: delete (MAESTRA)</t>
+  </si>
+  <si>
+    <t>1. The menu_type is shown.</t>
+  </si>
+  <si>
+    <t>Menus_types: modify (personalized)</t>
+  </si>
+  <si>
+    <t>Menus_types: delete (personalized)</t>
+  </si>
+  <si>
+    <t>1. The personalized menu_type is modified</t>
+  </si>
+  <si>
+    <t>Menus_types: create(personalized)</t>
+  </si>
+  <si>
+    <t>Menus_types: create (MAESTRA)</t>
+  </si>
+  <si>
+    <t>Menus_types: see (MAESTRA)</t>
+  </si>
+  <si>
+    <t>Menus_types: see, Cancel (MAESTRA)</t>
+  </si>
+  <si>
+    <t>Menus_types: create, cancel(MAESTRA)</t>
+  </si>
+  <si>
+    <t>Menus_types: create(personalized),cancel</t>
+  </si>
+  <si>
+    <t>Menus_types: modify(personalized),cancel</t>
+  </si>
+  <si>
+    <t>Menus_types: delete(personalized),cancel</t>
+  </si>
+  <si>
+    <t>1. The user clicks pencil icon
+2. Modify fields
+3. Clicks "Finalizar y Guardar"</t>
+  </si>
+  <si>
+    <t>1. The user clicks pencil icon
+2. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user creates a zone
+2. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user clicks garbage icon
+2. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user clicks garbage icon
+2.  Clicks "Eliminar"</t>
+  </si>
+  <si>
+    <t>1. The menu_type is deleted</t>
+  </si>
+  <si>
+    <t>No se puede borrar:MEN002.jpg</t>
+  </si>
+  <si>
+    <t>1. The user clicks garbage icon</t>
+  </si>
+  <si>
+    <t>1. The user clicks pencil icon</t>
+  </si>
+  <si>
+    <t>1. The  menu_type is modified</t>
   </si>
 </sst>
 </file>
@@ -2454,7 +2610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H162"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -2498,23 +2654,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -2522,13 +2678,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>597</v>
+        <v>580</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>598</v>
+        <v>581</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -2536,7 +2692,7 @@
         <v>8</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>599</v>
+        <v>582</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -2544,10 +2700,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>9</v>
@@ -2558,7 +2714,7 @@
         <v>8</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>600</v>
+        <v>583</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -2566,10 +2722,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>595</v>
+        <v>578</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -2588,10 +2744,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>12</v>
@@ -2602,7 +2758,7 @@
         <v>8</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -2610,18 +2766,18 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>593</v>
+        <v>577</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" s="3"/>
     </row>
@@ -2630,18 +2786,18 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>13</v>
+        <v>589</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H8" s="3"/>
     </row>
@@ -2650,18 +2806,18 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>586</v>
+        <v>570</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9" s="3"/>
     </row>
@@ -2670,18 +2826,18 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H10" s="3"/>
     </row>
@@ -2690,13 +2846,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -2704,7 +2860,7 @@
         <v>8</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -2712,23 +2868,23 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>589</v>
+        <v>573</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -2736,22 +2892,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>590</v>
+        <v>574</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H13" s="3"/>
     </row>
@@ -2760,23 +2916,23 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -2784,23 +2940,23 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -2808,23 +2964,23 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -2832,20 +2988,20 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>581</v>
+        <v>565</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H17" s="3"/>
     </row>
@@ -2854,20 +3010,20 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>581</v>
+        <v>565</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H18" s="3"/>
     </row>
@@ -2876,20 +3032,20 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H19" s="3"/>
     </row>
@@ -2898,22 +3054,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>583</v>
+        <v>567</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H20" s="3"/>
     </row>
@@ -2922,23 +3078,23 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -2946,20 +3102,20 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H22" s="3"/>
     </row>
@@ -2968,23 +3124,23 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -2992,25 +3148,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="F24" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3018,23 +3174,23 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>132</v>
+        <v>590</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3042,19 +3198,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>603</v>
+        <v>585</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3062,19 +3218,18 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D27" s="1"/>
+        <v>133</v>
+      </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3082,19 +3237,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3102,33 +3257,33 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -3136,27 +3291,27 @@
         <v>8</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>150</v>
+        <v>592</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3164,21 +3319,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3186,21 +3341,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3208,22 +3363,22 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H34" s="3"/>
     </row>
@@ -3232,20 +3387,20 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H35" s="3"/>
     </row>
@@ -3254,23 +3409,23 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3278,21 +3433,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3300,21 +3455,21 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3322,13 +3477,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -3336,7 +3491,7 @@
         <v>8</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>170</v>
+        <v>596</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3344,13 +3499,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>167</v>
+        <v>594</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
@@ -3358,49 +3513,51 @@
         <v>8</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>453</v>
+        <v>597</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>454</v>
+        <v>599</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="D42" s="1"/>
+        <v>598</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>600</v>
+      </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>466</v>
+        <v>601</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3408,155 +3565,186 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="D43" s="1"/>
+        <v>448</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>449</v>
+      </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H43" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
+        <v>453</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>615</v>
+      </c>
       <c r="G44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>469</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H44" s="3"/>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
+        <v>454</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>617</v>
+      </c>
       <c r="G45" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
+        <v>632</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>624</v>
+      </c>
       <c r="F46" s="1"/>
       <c r="G46" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
+        <v>635</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
+        <v>633</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>620</v>
+      </c>
       <c r="F48" s="1"/>
       <c r="G48" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
+        <v>634</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="F49" s="1"/>
       <c r="G49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>470</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="H49" s="3"/>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
+        <v>625</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>648</v>
+      </c>
       <c r="F50" s="1"/>
       <c r="G50" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
     </row>
     <row r="51" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3564,1378 +3752,1439 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
+        <v>626</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>644</v>
+      </c>
       <c r="F51" s="1"/>
       <c r="G51" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
+        <v>631</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>624</v>
+      </c>
       <c r="F52" s="1"/>
       <c r="G52" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
+        <v>636</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>450</v>
+        <v>628</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E54" s="1"/>
+        <v>639</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>630</v>
+      </c>
       <c r="F54" s="1"/>
       <c r="G54" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H54" s="3"/>
-    </row>
-    <row r="55" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
+        <v>637</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G55" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H55" s="3"/>
     </row>
-    <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
+        <v>629</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>644</v>
+      </c>
       <c r="G56" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H56" s="3"/>
     </row>
-    <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
+        <v>638</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G57" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H57" s="3"/>
     </row>
-    <row r="58" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
+        <v>587</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>627</v>
+      </c>
       <c r="G58" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H58" s="3"/>
+        <v>19</v>
+      </c>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="D59" s="1"/>
+        <v>445</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>140</v>
+      </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H59" s="3"/>
     </row>
-    <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
+        <v>444</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>607</v>
+      </c>
       <c r="G60" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H60" s="3"/>
     </row>
-    <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
+        <v>450</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G61" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H61" s="3"/>
     </row>
-    <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
+        <v>446</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>609</v>
+      </c>
       <c r="G62" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H62" s="3"/>
     </row>
-    <row r="63" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>425</v>
+        <v>287</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="F63" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H63" s="3"/>
+    </row>
+    <row r="64" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>422</v>
+        <v>447</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>424</v>
+        <v>612</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="F64" s="1"/>
+        <v>613</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>613</v>
+      </c>
       <c r="G64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>431</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H64" s="3"/>
     </row>
     <row r="65" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>419</v>
+        <v>452</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>423</v>
+        <v>611</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H65" s="3"/>
     </row>
-    <row r="66" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>414</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="F66" s="1"/>
       <c r="G66" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H66" s="3"/>
-    </row>
-    <row r="67" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="F67" s="1" t="s">
         <v>416</v>
       </c>
+      <c r="F67" s="1"/>
       <c r="G67" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H67" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row r="68" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>427</v>
+        <v>641</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="F68" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G68" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H68" s="3"/>
+    </row>
+    <row r="69" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>432</v>
+        <v>409</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="F69" s="1"/>
+        <v>410</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>410</v>
+      </c>
       <c r="G69" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H69" s="3"/>
+    </row>
+    <row r="70" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="F70" s="1"/>
+        <v>413</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>412</v>
+      </c>
       <c r="G70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H70" s="3"/>
+    </row>
+    <row r="71" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>129</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="F71" s="1"/>
       <c r="G71" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H71" s="3"/>
-    </row>
-    <row r="72" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>443</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="F72" s="1"/>
       <c r="G72" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H72" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>434</v>
+      </c>
     </row>
     <row r="73" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>129</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="F73" s="1"/>
       <c r="G73" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H73" s="3"/>
-    </row>
-    <row r="74" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F74" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G74" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H74" s="3"/>
+    </row>
+    <row r="75" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>392</v>
+        <v>436</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>400</v>
+        <v>437</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="F75" s="1"/>
+        <v>438</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>438</v>
+      </c>
       <c r="G75" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>411</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H75" s="3"/>
     </row>
     <row r="76" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>393</v>
+        <v>439</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>406</v>
+        <v>440</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="F76" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G76" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H76" s="3"/>
+    </row>
+    <row r="77" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>394</v>
+        <v>441</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>405</v>
+        <v>442</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>129</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="F77" s="1"/>
       <c r="G77" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H77" s="3"/>
-    </row>
-    <row r="78" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>290</v>
+        <v>396</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>403</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="F78" s="1"/>
       <c r="G78" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H78" s="3"/>
-    </row>
-    <row r="79" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>291</v>
+        <v>402</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>129</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="F79" s="1"/>
       <c r="G79" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H79" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="80" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>341</v>
+        <v>401</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>404</v>
+        <v>128</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>404</v>
+        <v>128</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H80" s="3"/>
     </row>
-    <row r="81" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>340</v>
+        <v>286</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>129</v>
+        <v>399</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>129</v>
+        <v>399</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H81" s="3"/>
     </row>
-    <row r="82" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>293</v>
+        <v>128</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>293</v>
+        <v>128</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H82" s="3"/>
     </row>
-    <row r="83" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>408</v>
+        <v>337</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H83" s="3"/>
     </row>
-    <row r="84" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>350</v>
+        <v>394</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>362</v>
+        <v>128</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>365</v>
+        <v>128</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H84" s="3"/>
+    </row>
+    <row r="85" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>352</v>
+        <v>395</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>360</v>
+        <v>288</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="F85" s="1"/>
+        <v>289</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="G85" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H85" s="3"/>
+    </row>
+    <row r="86" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>353</v>
+        <v>403</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>361</v>
+        <v>404</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F86" s="1"/>
+        <v>405</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>405</v>
+      </c>
       <c r="G86" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H86" s="3"/>
+    </row>
+    <row r="87" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>129</v>
+        <v>358</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>129</v>
+        <v>361</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H87" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>377</v>
+      </c>
     </row>
     <row r="88" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="F88" s="1"/>
       <c r="G88" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>291</v>
+        <v>357</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>129</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="F89" s="1"/>
       <c r="G89" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H89" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="90" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>368</v>
+        <v>128</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>368</v>
+        <v>128</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H90" s="3"/>
     </row>
-    <row r="91" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>340</v>
+        <v>312</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>129</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="F91" s="1"/>
       <c r="G91" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H91" s="3"/>
-    </row>
-    <row r="92" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="F92" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G92" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>370</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H92" s="3"/>
     </row>
     <row r="93" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>374</v>
+        <v>337</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="F93" s="1"/>
+        <v>364</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>364</v>
+      </c>
       <c r="G93" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>376</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H93" s="3"/>
     </row>
     <row r="94" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>388</v>
+        <v>354</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>378</v>
+        <v>336</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="F94" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G94" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H94" s="3"/>
+    </row>
+    <row r="95" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>389</v>
+        <v>288</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>379</v>
+        <v>289</v>
       </c>
       <c r="F95" s="1"/>
       <c r="G95" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>321</v>
+        <v>370</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>322</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="F96" s="1"/>
       <c r="G96" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>323</v>
+        <v>384</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>347</v>
+        <v>374</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="F97" s="1"/>
       <c r="G97" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H97" s="3"/>
-    </row>
-    <row r="98" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>324</v>
+        <v>369</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>348</v>
+        <v>385</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>334</v>
+        <v>375</v>
       </c>
       <c r="F98" s="1"/>
       <c r="G98" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>345</v>
+        <v>317</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>129</v>
+        <v>318</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>129</v>
+        <v>318</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H99" s="3"/>
-    </row>
-    <row r="100" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>331</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="F100" s="1"/>
       <c r="G100" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H100" s="3"/>
+    </row>
+    <row r="101" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>291</v>
+        <v>344</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>129</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="F101" s="1"/>
       <c r="G101" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H101" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="102" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>341</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>332</v>
+        <v>128</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>332</v>
+        <v>128</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H102" s="3"/>
     </row>
-    <row r="103" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="C103" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H103" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H103" s="3"/>
-    </row>
-    <row r="104" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>293</v>
+        <v>128</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>293</v>
+        <v>128</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H104" s="3"/>
     </row>
-    <row r="105" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>299</v>
+        <v>337</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>337</v>
+        <v>128</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>337</v>
+        <v>128</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H106" s="3"/>
     </row>
-    <row r="107" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>343</v>
+        <v>288</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="F107" s="1"/>
+        <v>289</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="G107" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H107" s="3"/>
     </row>
-    <row r="108" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>344</v>
+        <v>295</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>129</v>
+        <v>296</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>129</v>
+        <v>296</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H108" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>379</v>
+      </c>
     </row>
     <row r="109" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H109" s="3"/>
     </row>
-    <row r="110" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>291</v>
+        <v>339</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>129</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="F110" s="1"/>
       <c r="G110" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H110" s="3"/>
     </row>
@@ -4944,368 +5193,368 @@
         <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>336</v>
+        <v>128</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>336</v>
+        <v>128</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H111" s="3"/>
     </row>
-    <row r="112" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>340</v>
+        <v>312</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>129</v>
+        <v>331</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>129</v>
+        <v>331</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H112" s="3">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H112" s="3"/>
+    </row>
+    <row r="113" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>293</v>
+        <v>128</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>293</v>
+        <v>128</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>319</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H113" s="3"/>
     </row>
     <row r="114" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="F114" s="1"/>
+        <v>332</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>332</v>
+      </c>
       <c r="G114" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H114" s="3"/>
+    </row>
+    <row r="115" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="F115" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G115" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H115" s="3">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>339</v>
+        <v>288</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="F116" s="1"/>
+        <v>289</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="G116" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>278</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="F117" s="1"/>
       <c r="G117" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>287</v>
+        <v>334</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>294</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="F118" s="1"/>
       <c r="G118" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H118" s="3"/>
-    </row>
-    <row r="119" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>288</v>
+        <v>335</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>294</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="F119" s="1"/>
       <c r="G119" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>289</v>
+        <v>141</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>129</v>
+        <v>274</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>129</v>
+        <v>274</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H120" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="121" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D121" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E121" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="F121" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H121" s="3"/>
+    </row>
+    <row r="122" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>129</v>
+        <v>290</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>129</v>
+        <v>290</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H122" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="123" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>341</v>
+        <v>285</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>297</v>
+        <v>128</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>297</v>
+        <v>128</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H123" s="3"/>
     </row>
-    <row r="124" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>340</v>
+        <v>286</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>129</v>
+        <v>291</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>129</v>
+        <v>291</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H124" s="3"/>
-    </row>
-    <row r="125" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>293</v>
+        <v>128</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>293</v>
+        <v>128</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H125" s="3"/>
     </row>
@@ -5314,95 +5563,95 @@
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>144</v>
+        <v>337</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="F126" s="1"/>
+        <v>293</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>293</v>
+      </c>
       <c r="G126" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H126" s="3" t="s">
-        <v>385</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H126" s="3"/>
     </row>
     <row r="127" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="F127" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G127" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H127" s="3" t="s">
-        <v>254</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H127" s="3"/>
     </row>
     <row r="128" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="F128" s="1"/>
+        <v>289</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="G128" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H128" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H128" s="3"/>
+    </row>
+    <row r="129" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>260</v>
+        <v>142</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="F129" s="1"/>
       <c r="G129" s="2" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>270</v>
+        <v>381</v>
       </c>
     </row>
     <row r="130" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5410,47 +5659,47 @@
         <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="F130" s="1"/>
       <c r="G130" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="F131" s="1"/>
       <c r="G131" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="132" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5458,97 +5707,95 @@
         <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="F132" s="1"/>
       <c r="G132" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="F133" s="1"/>
       <c r="G133" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="F134" s="1"/>
       <c r="G134" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>275</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="F135" s="1"/>
       <c r="G135" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="136" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5556,173 +5803,173 @@
         <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>239</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="F136" s="1"/>
       <c r="G136" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="F137" s="1"/>
       <c r="G137" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>129</v>
+        <v>269</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>129</v>
+        <v>271</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H138" s="3"/>
-    </row>
-    <row r="139" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="H138" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>129</v>
+        <v>235</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>129</v>
+        <v>235</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>101</v>
+        <v>240</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>145</v>
+        <v>236</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>236</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="F140" s="1"/>
       <c r="G140" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H140" s="3"/>
-    </row>
-    <row r="141" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>186</v>
+        <v>239</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F141" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G141" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H141" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H141" s="3"/>
+    </row>
+    <row r="142" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>187</v>
+        <v>242</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>228</v>
+        <v>128</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>229</v>
+        <v>128</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
     </row>
     <row r="143" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5730,13 +5977,13 @@
         <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>560</v>
+        <v>544</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>189</v>
+        <v>100</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>231</v>
+        <v>143</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>232</v>
@@ -5745,289 +5992,293 @@
         <v>232</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H143" s="3"/>
     </row>
-    <row r="144" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>561</v>
+        <v>545</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="E144" s="1"/>
+        <v>230</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>231</v>
+      </c>
       <c r="F144" s="1"/>
       <c r="G144" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F145" s="1"/>
+        <v>224</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>225</v>
+      </c>
       <c r="G145" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F146" s="1"/>
+        <v>228</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>228</v>
+      </c>
       <c r="G146" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H146" s="3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H146" s="3"/>
+    </row>
+    <row r="147" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="E147" s="1" t="s">
-        <v>222</v>
-      </c>
+      <c r="E147" s="1"/>
       <c r="F147" s="1"/>
       <c r="G147" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F148" s="1"/>
       <c r="G148" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="F149" s="1"/>
       <c r="G149" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H149" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H149" s="3" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="150" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>224</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="F150" s="1"/>
       <c r="G150" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H150" s="3"/>
-    </row>
-    <row r="151" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H150" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>224</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="F151" s="1"/>
       <c r="G151" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H151" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H151" s="3" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="152" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>569</v>
+        <v>553</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>224</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="F152" s="1"/>
       <c r="G152" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H152" s="3"/>
     </row>
-    <row r="153" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="F153" s="1"/>
+        <v>220</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>220</v>
+      </c>
       <c r="G153" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H153" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H153" s="3"/>
+    </row>
+    <row r="154" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F154" s="1"/>
+        <v>220</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>220</v>
+      </c>
       <c r="G154" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H154" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H154" s="3"/>
+    </row>
+    <row r="155" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>572</v>
+        <v>556</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F155" s="1"/>
+        <v>220</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>220</v>
+      </c>
       <c r="G155" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H155" s="3"/>
     </row>
@@ -6036,92 +6287,92 @@
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>146</v>
+        <v>203</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>181</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="F156" s="1"/>
       <c r="G156" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H156" s="3"/>
-    </row>
-    <row r="157" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H156" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="F157" s="1"/>
       <c r="G157" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>575</v>
+        <v>559</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>103</v>
+        <v>194</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>147</v>
+        <v>206</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>175</v>
+        <v>128</v>
       </c>
       <c r="F158" s="1"/>
       <c r="G158" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H158" s="3" t="s">
-        <v>179</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="H158" s="3"/>
     </row>
     <row r="159" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>158</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>176</v>
+        <v>101</v>
       </c>
       <c r="D159" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E159" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="F159" s="1"/>
+      <c r="F159" s="1" t="s">
+        <v>177</v>
+      </c>
       <c r="G159" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H159" s="3"/>
     </row>
@@ -6130,49 +6381,47 @@
         <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>55</v>
+        <v>179</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>57</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="F160" s="1"/>
       <c r="G160" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>61</v>
+        <v>171</v>
       </c>
       <c r="F161" s="1"/>
       <c r="G161" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="162" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6180,28 +6429,100 @@
         <v>161</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>62</v>
+        <v>172</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>63</v>
+        <v>173</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>64</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="F162" s="1"/>
       <c r="G162" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H162" s="3"/>
     </row>
+    <row r="163" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H163" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F164" s="1"/>
+      <c r="G164" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H165" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G162">
+  <conditionalFormatting sqref="G2:G165">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>

--- a/App/TestCases_App/User_admin.xlsx
+++ b/App/TestCases_App/User_admin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E1F1D03-483B-4F08-910B-841B9E7DC6E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3D5FF6-05F1-4E24-8EB2-63A09979DAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="655">
   <si>
     <t>Num</t>
   </si>
@@ -2164,6 +2164,30 @@
   </si>
   <si>
     <t>1. The  menu_type is modified</t>
+  </si>
+  <si>
+    <t>Invoicing: Settings, serie</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Configuración"
+2. Clicks "Añadir nueva serie"
+3. Clicks "Crear serie"</t>
+  </si>
+  <si>
+    <t>The serie is created</t>
+  </si>
+  <si>
+    <t>Invoicing: Settings, serie,cancel</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Configuración"
+2. Clicks "Añadir nueva serie"
+3. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>Permite crear una serie con un Año fiscal incorrecto: FAC004.jpg
+El despliegue del menu para introducir el texto, tapa la pantalla y el campo a rellenar: FAC005.jpg
+BLOQUEANTE: Al introducir un valor muy grande en "Digitos de secuencia" la app, se cierra. Después aunq se reinicie, en la parte Series de Facturacion, la aplicación tarda mucho, y sale la opción de "Cerrar aplicación" o "Esperar"</t>
   </si>
 </sst>
 </file>
@@ -2610,7 +2634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H167"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -3516,324 +3540,324 @@
         <v>595</v>
       </c>
     </row>
-    <row r="41" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>597</v>
+        <v>649</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="E41" s="1"/>
+        <v>650</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>651</v>
+      </c>
       <c r="F41" s="1"/>
       <c r="G41" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>598</v>
+        <v>652</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
+        <v>653</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>448</v>
+        <v>597</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>449</v>
+        <v>599</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>453</v>
+        <v>598</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>615</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
       <c r="G44" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H44" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>601</v>
+      </c>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
+        <v>42</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>43</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" s="3"/>
+    </row>
+    <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>44</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B47" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F47" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H45" s="3"/>
-    </row>
-    <row r="46" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
+      <c r="G47" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" s="3"/>
+    </row>
+    <row r="48" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
         <v>45</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>624</v>
-      </c>
-      <c r="F46" s="1"/>
-      <c r="G46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
-        <v>46</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
-        <v>47</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>620</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F49" s="1"/>
+      <c r="F49" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G49" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H49" s="3"/>
-    </row>
-    <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>647</v>
+        <v>619</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>648</v>
+        <v>620</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>646</v>
+        <v>622</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>644</v>
+        <v>128</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H51" s="3" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>618</v>
+        <v>647</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>624</v>
+        <v>648</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>623</v>
+        <v>646</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>644</v>
+      </c>
+      <c r="F53" s="1"/>
       <c r="G53" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H53" s="3"/>
-    </row>
-    <row r="54" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>464</v>
+        <v>117</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>639</v>
+        <v>618</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="2" t="s">
@@ -3845,16 +3869,16 @@
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>128</v>
@@ -3867,42 +3891,42 @@
       </c>
       <c r="H55" s="3"/>
     </row>
-    <row r="56" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>120</v>
+        <v>464</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>644</v>
-      </c>
+        <v>630</v>
+      </c>
+      <c r="F56" s="1"/>
       <c r="G56" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H56" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>455</v>
+      </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>465</v>
+        <v>119</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>128</v>
@@ -3917,113 +3941,113 @@
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
+        <v>55</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" s="3"/>
+    </row>
+    <row r="59" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>56</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
         <v>57</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B60" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E60" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F60" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
+      <c r="G60" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>58</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B61" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H59" s="3"/>
-    </row>
-    <row r="60" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" s="3"/>
+    </row>
+    <row r="62" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
         <v>59</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B62" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E62" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F62" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H60" s="3"/>
-    </row>
-    <row r="61" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>60</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H61" s="3"/>
-    </row>
-    <row r="62" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
-        <v>61</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>609</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>19</v>
@@ -4032,16 +4056,16 @@
     </row>
     <row r="63" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>287</v>
+        <v>608</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>128</v>
@@ -4056,22 +4080,22 @@
     </row>
     <row r="64" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>19</v>
@@ -4080,16 +4104,16 @@
     </row>
     <row r="65" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>466</v>
+        <v>126</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>611</v>
+        <v>287</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>128</v>
@@ -4102,120 +4126,120 @@
       </c>
       <c r="H65" s="3"/>
     </row>
-    <row r="66" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
+        <v>63</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" s="3"/>
+    </row>
+    <row r="67" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>64</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" s="3"/>
+    </row>
+    <row r="68" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
         <v>65</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E68" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="F66" s="1"/>
-      <c r="G66" s="2" t="s">
+      <c r="F68" s="1"/>
+      <c r="G68" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H66" s="3" t="s">
+      <c r="H68" s="3" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="67" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
+    <row r="69" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
         <v>66</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B69" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C69" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D69" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E69" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="F67" s="1"/>
-      <c r="G67" s="2" t="s">
+      <c r="F69" s="1"/>
+      <c r="G69" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H67" s="3" t="s">
+      <c r="H69" s="3" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
-        <v>67</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H68" s="3"/>
-    </row>
-    <row r="69" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
-        <v>68</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H69" s="3"/>
     </row>
     <row r="70" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>414</v>
+        <v>641</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>413</v>
+        <v>128</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>412</v>
+        <v>128</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>19</v>
@@ -4224,136 +4248,136 @@
     </row>
     <row r="71" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
+        <v>68</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" s="3"/>
+    </row>
+    <row r="72" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>69</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" s="3"/>
+    </row>
+    <row r="73" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
         <v>70</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D73" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E73" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="F71" s="1"/>
-      <c r="G71" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
-        <v>71</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="F72" s="1"/>
-      <c r="G72" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
-        <v>72</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>428</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
     </row>
     <row r="74" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="F74" s="1"/>
       <c r="G74" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H74" s="3"/>
-    </row>
-    <row r="75" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>438</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="F75" s="1"/>
       <c r="G75" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H75" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="76" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>128</v>
@@ -4366,138 +4390,138 @@
       </c>
       <c r="H76" s="3"/>
     </row>
-    <row r="77" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
+        <v>74</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" s="3"/>
+    </row>
+    <row r="78" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>75</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" s="3"/>
+    </row>
+    <row r="79" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
         <v>76</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D79" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E79" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="F77" s="1"/>
-      <c r="G77" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
-        <v>77</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="F78" s="1"/>
-      <c r="G78" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
-        <v>78</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>398</v>
       </c>
       <c r="F79" s="1"/>
       <c r="G79" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="F80" s="1"/>
       <c r="G80" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H80" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="81" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>399</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="F81" s="1"/>
       <c r="G81" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H81" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="82" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>287</v>
+        <v>401</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>128</v>
@@ -4510,24 +4534,24 @@
       </c>
       <c r="H82" s="3"/>
     </row>
-    <row r="83" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>337</v>
+        <v>286</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>19</v>
@@ -4536,16 +4560,16 @@
     </row>
     <row r="84" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>336</v>
+        <v>287</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>128</v>
@@ -4558,48 +4582,48 @@
       </c>
       <c r="H84" s="3"/>
     </row>
-    <row r="85" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>288</v>
+        <v>337</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>289</v>
+        <v>400</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>289</v>
+        <v>400</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H85" s="3"/>
     </row>
-    <row r="86" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>404</v>
+        <v>336</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>405</v>
+        <v>128</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>405</v>
+        <v>128</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>19</v>
@@ -4608,138 +4632,138 @@
     </row>
     <row r="87" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
+        <v>84</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H87" s="3"/>
+    </row>
+    <row r="88" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>85</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H88" s="3"/>
+    </row>
+    <row r="89" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
         <v>86</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D89" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E89" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="F89" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="G87" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
-        <v>87</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="F88" s="1"/>
-      <c r="G88" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
-        <v>88</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="F89" s="1"/>
       <c r="G89" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="F90" s="1"/>
       <c r="G90" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H90" s="3"/>
-    </row>
-    <row r="91" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>312</v>
+        <v>357</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
     </row>
     <row r="92" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>287</v>
+        <v>362</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>128</v>
@@ -4752,42 +4776,42 @@
       </c>
       <c r="H92" s="3"/>
     </row>
-    <row r="93" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>364</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="F93" s="1"/>
       <c r="G93" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H93" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>376</v>
+      </c>
     </row>
     <row r="94" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>336</v>
+        <v>287</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>128</v>
@@ -4800,236 +4824,234 @@
       </c>
       <c r="H94" s="3"/>
     </row>
-    <row r="95" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>288</v>
+        <v>337</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="F95" s="1"/>
+        <v>364</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>364</v>
+      </c>
       <c r="G95" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>366</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H95" s="3"/>
     </row>
     <row r="96" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>370</v>
+        <v>336</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="F96" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G96" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H96" s="3"/>
+    </row>
+    <row r="97" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>384</v>
+        <v>355</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>374</v>
+        <v>288</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>373</v>
+        <v>289</v>
       </c>
       <c r="F97" s="1"/>
       <c r="G97" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>386</v>
+        <v>366</v>
       </c>
     </row>
     <row r="98" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F98" s="1"/>
       <c r="G98" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>316</v>
+        <v>384</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>317</v>
+        <v>374</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>318</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="F99" s="1"/>
       <c r="G99" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>319</v>
+        <v>369</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>342</v>
+        <v>375</v>
       </c>
       <c r="F100" s="1"/>
       <c r="G100" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H100" s="3"/>
-    </row>
-    <row r="101" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>344</v>
+        <v>317</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="F101" s="1"/>
+        <v>318</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="G101" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="F102" s="1"/>
       <c r="G102" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H102" s="3"/>
     </row>
-    <row r="103" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>327</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="F103" s="1"/>
       <c r="G103" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
     </row>
     <row r="104" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>287</v>
+        <v>341</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>128</v>
@@ -5042,44 +5064,44 @@
       </c>
       <c r="H104" s="3"/>
     </row>
-    <row r="105" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>605</v>
+        <v>329</v>
       </c>
     </row>
     <row r="106" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>336</v>
+        <v>287</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>128</v>
@@ -5092,120 +5114,124 @@
       </c>
       <c r="H106" s="3"/>
     </row>
-    <row r="107" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
+        <v>104</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>105</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H108" s="3"/>
+    </row>
+    <row r="109" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
         <v>106</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B109" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C109" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="D109" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E107" s="1" t="s">
+      <c r="E109" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="F107" s="1" t="s">
+      <c r="F109" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="G107" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H107" s="3"/>
-    </row>
-    <row r="108" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="1">
+      <c r="G109" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H109" s="3"/>
+    </row>
+    <row r="110" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
         <v>107</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B110" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C110" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="D110" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E108" s="1" t="s">
+      <c r="E110" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="F108" s="1" t="s">
+      <c r="F110" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="G108" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H108" s="3" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A109" s="1">
-        <v>108</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H109" s="3"/>
-    </row>
-    <row r="110" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A110" s="1">
-        <v>109</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="F110" s="1"/>
       <c r="G110" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H110" s="3"/>
-    </row>
-    <row r="111" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="H110" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>128</v>
+        <v>333</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>128</v>
+        <v>333</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>19</v>
@@ -5214,40 +5240,38 @@
     </row>
     <row r="112" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>312</v>
+        <v>339</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>331</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="F112" s="1"/>
       <c r="G112" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H112" s="3"/>
     </row>
     <row r="113" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>287</v>
+        <v>340</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>128</v>
@@ -5260,24 +5284,24 @@
       </c>
       <c r="H113" s="3"/>
     </row>
-    <row r="114" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>19</v>
@@ -5286,16 +5310,16 @@
     </row>
     <row r="115" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>336</v>
+        <v>287</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>128</v>
@@ -5306,202 +5330,200 @@
       <c r="G115" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H115" s="3">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="H115" s="3"/>
+    </row>
+    <row r="116" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>288</v>
+        <v>337</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>289</v>
+        <v>332</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>289</v>
+        <v>332</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H116" s="3" t="s">
-        <v>315</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H116" s="3"/>
     </row>
     <row r="117" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="F117" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="G117" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H117" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H117" s="3">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>334</v>
+        <v>288</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="F118" s="1"/>
+        <v>289</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="G118" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>335</v>
+        <v>307</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="F119" s="1"/>
       <c r="G119" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>273</v>
+        <v>310</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>141</v>
+        <v>334</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>274</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="F120" s="1"/>
       <c r="G120" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>283</v>
+        <v>335</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>290</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="F121" s="1"/>
       <c r="G121" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H121" s="3"/>
-    </row>
-    <row r="122" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>284</v>
+        <v>141</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>19</v>
@@ -5510,42 +5532,42 @@
     </row>
     <row r="124" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
     </row>
     <row r="125" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>128</v>
@@ -5558,42 +5580,44 @@
       </c>
       <c r="H125" s="3"/>
     </row>
-    <row r="126" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>337</v>
+        <v>286</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H126" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="127" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>336</v>
+        <v>287</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>128</v>
@@ -5606,24 +5630,24 @@
       </c>
       <c r="H127" s="3"/>
     </row>
-    <row r="128" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>288</v>
+        <v>337</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>19</v>
@@ -5632,115 +5656,115 @@
     </row>
     <row r="129" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
+        <v>126</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="F129" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H129" s="3"/>
+    </row>
+    <row r="130" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>127</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H130" s="3"/>
+    </row>
+    <row r="131" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>128</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="C131" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="D131" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E129" s="1" t="s">
+      <c r="E131" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="F129" s="1"/>
-      <c r="G129" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H129" s="3" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A130" s="1">
-        <v>129</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="F130" s="1"/>
-      <c r="G130" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H130" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="1">
-        <v>130</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="F131" s="1"/>
       <c r="G131" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="F132" s="1"/>
       <c r="G132" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F133" s="1"/>
       <c r="G133" s="2" t="s">
@@ -5750,21 +5774,21 @@
         <v>266</v>
       </c>
     </row>
-    <row r="134" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F134" s="1"/>
       <c r="G134" s="2" t="s">
@@ -5774,21 +5798,21 @@
         <v>266</v>
       </c>
     </row>
-    <row r="135" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="F135" s="1"/>
       <c r="G135" s="2" t="s">
@@ -5798,21 +5822,21 @@
         <v>266</v>
       </c>
     </row>
-    <row r="136" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="F136" s="1"/>
       <c r="G136" s="2" t="s">
@@ -5824,19 +5848,19 @@
     </row>
     <row r="137" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F137" s="1"/>
       <c r="G137" s="2" t="s">
@@ -5846,25 +5870,23 @@
         <v>266</v>
       </c>
     </row>
-    <row r="138" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>245</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>271</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="F138" s="1"/>
       <c r="G138" s="2" t="s">
         <v>20</v>
       </c>
@@ -5874,287 +5896,289 @@
     </row>
     <row r="139" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>233</v>
+        <v>267</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>234</v>
+        <v>268</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>235</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="F139" s="1"/>
       <c r="G139" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H139" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>137</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>138</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H141" s="3" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="140" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A140" s="1">
-        <v>139</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="F140" s="1"/>
-      <c r="G140" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H140" s="3" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A141" s="1">
-        <v>140</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H141" s="3"/>
     </row>
     <row r="142" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
+        <v>139</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F142" s="1"/>
+      <c r="G142" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H142" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
+        <v>140</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H143" s="3"/>
+    </row>
+    <row r="144" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
         <v>141</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="B144" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="C144" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="D144" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="E142" s="1" t="s">
+      <c r="E144" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F142" s="1" t="s">
+      <c r="F144" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G142" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H142" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="1">
-        <v>142</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="G143" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H143" s="3"/>
-    </row>
-    <row r="144" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A144" s="1">
-        <v>143</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F144" s="1"/>
       <c r="G144" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
     </row>
     <row r="145" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>183</v>
+        <v>100</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>223</v>
+        <v>143</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H145" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H145" s="3"/>
+    </row>
+    <row r="146" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>228</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="F146" s="1"/>
       <c r="G146" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H146" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="147" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
+        <v>144</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
+        <v>145</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H148" s="3"/>
+    </row>
+    <row r="149" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
         <v>146</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="B149" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="C149" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="D149" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="E147" s="1"/>
-      <c r="F147" s="1"/>
-      <c r="G147" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H147" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A148" s="1">
-        <v>147</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F148" s="1"/>
-      <c r="G148" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H148" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A149" s="1">
-        <v>148</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>215</v>
-      </c>
+      <c r="E149" s="1"/>
       <c r="F149" s="1"/>
       <c r="G149" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="150" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="F150" s="1"/>
       <c r="G150" s="2" t="s">
@@ -6166,93 +6190,93 @@
     </row>
     <row r="151" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F151" s="1"/>
       <c r="G151" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="152" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="F152" s="1"/>
       <c r="G152" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H152" s="3"/>
-    </row>
-    <row r="153" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>220</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="F153" s="1"/>
       <c r="G153" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H153" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="154" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>220</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="F154" s="1"/>
       <c r="G154" s="2" t="s">
         <v>19</v>
       </c>
@@ -6260,16 +6284,16 @@
     </row>
     <row r="155" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>220</v>
@@ -6282,247 +6306,295 @@
       </c>
       <c r="H155" s="3"/>
     </row>
-    <row r="156" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
+        <v>153</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H156" s="3"/>
+    </row>
+    <row r="157" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
+        <v>154</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H157" s="3"/>
+    </row>
+    <row r="158" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
         <v>155</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="B158" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="C158" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D156" s="1" t="s">
+      <c r="D158" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E156" s="1" t="s">
+      <c r="E158" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="F156" s="1"/>
-      <c r="G156" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H156" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A157" s="1">
-        <v>156</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="F157" s="1"/>
-      <c r="G157" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H157" s="3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A158" s="1">
-        <v>157</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="F158" s="1"/>
       <c r="G158" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H158" s="3"/>
-    </row>
-    <row r="159" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H158" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>101</v>
+        <v>192</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>144</v>
+        <v>207</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>177</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="F159" s="1"/>
       <c r="G159" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H159" s="3"/>
-    </row>
-    <row r="160" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H159" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="F160" s="1"/>
       <c r="G160" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H160" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="H160" s="3"/>
+    </row>
+    <row r="161" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="F161" s="1"/>
+        <v>177</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>177</v>
+      </c>
       <c r="G161" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H161" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H161" s="3"/>
+    </row>
+    <row r="162" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F162" s="1"/>
       <c r="G162" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H162" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="163" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>602</v>
+        <v>562</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>56</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="F163" s="1"/>
       <c r="G163" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>603</v>
+        <v>563</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>58</v>
+        <v>172</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>59</v>
+        <v>173</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>60</v>
+        <v>174</v>
       </c>
       <c r="F164" s="1"/>
       <c r="G164" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H164" s="3"/>
+    </row>
+    <row r="165" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <v>162</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G165" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H164" s="3" t="s">
+      <c r="H165" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
+        <v>163</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F166" s="1"/>
+      <c r="G166" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H166" s="3" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="165" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="1">
+    <row r="167" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
         <v>164</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="B167" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="C165" s="1" t="s">
+      <c r="C167" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D165" s="1" t="s">
+      <c r="D167" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E165" s="1" t="s">
+      <c r="E167" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F165" s="1" t="s">
+      <c r="F167" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G165" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H165" s="3"/>
+      <c r="G167" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H167" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G165">
+  <conditionalFormatting sqref="G2:G167">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>

--- a/App/TestCases_App/User_admin.xlsx
+++ b/App/TestCases_App/User_admin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3D5FF6-05F1-4E24-8EB2-63A09979DAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC53DEE-0F03-4126-A0D9-5A4BF7727F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="660">
   <si>
     <t>Num</t>
   </si>
@@ -498,9 +498,6 @@
   </si>
   <si>
     <t>Tickets' history: information, print</t>
-  </si>
-  <si>
-    <t>No se puede "imprimir" desde el icono impresora</t>
   </si>
   <si>
     <t>1. The user sees Invoicing page</t>
@@ -2188,6 +2185,31 @@
     <t>Permite crear una serie con un Año fiscal incorrecto: FAC004.jpg
 El despliegue del menu para introducir el texto, tapa la pantalla y el campo a rellenar: FAC005.jpg
 BLOQUEANTE: Al introducir un valor muy grande en "Digitos de secuencia" la app, se cierra. Después aunq se reinicie, en la parte Series de Facturacion, la aplicación tarda mucho, y sale la opción de "Cerrar aplicación" o "Esperar"</t>
+  </si>
+  <si>
+    <t>1. The user selects a ticket
+2. Clicks "Reimprimir"</t>
+  </si>
+  <si>
+    <t>The ticket is printed</t>
+  </si>
+  <si>
+    <t>No se puede "imprimir" desde el icono impresora
+La imagen casi no se ve: TIC001.jpg</t>
+  </si>
+  <si>
+    <t>No aparece el porcentaje correcto: ACT001.jpg</t>
+  </si>
+  <si>
+    <t>No se puede subir una imagen de una carta: MEN001.jpg
+Al modificar un campo como "Nombre de la carta" el cursor retrocede una posición: MEN004.jpg (tiene q ser en mitad de la linea a modificar)
+Los botones no  van bien, tengo q pulsar varias veces "Siguiente" o "Anterior" para q respondan.</t>
+  </si>
+  <si>
+    <t>No se puede subir una imagen de una carta: MEN001.jpg
+Al desplegar el teclado, se tapa la funcionalidad: MEN003.jpg
+Parece q me guarda el menú pero cuando voy a consultarlo, ha desaparecido.
+Se produce un error al guardar el menú: MEN005.jpg,MEN006.jpg</t>
   </si>
 </sst>
 </file>
@@ -2705,10 +2727,10 @@
         <v>36</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>581</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -2716,7 +2738,7 @@
         <v>8</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -2727,7 +2749,7 @@
         <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>9</v>
@@ -2738,7 +2760,7 @@
         <v>8</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -2749,7 +2771,7 @@
         <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -2771,7 +2793,7 @@
         <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>12</v>
@@ -2793,7 +2815,7 @@
         <v>40</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>15</v>
@@ -2813,10 +2835,10 @@
         <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>588</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>589</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -2833,7 +2855,7 @@
         <v>42</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>13</v>
@@ -2853,7 +2875,7 @@
         <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>14</v>
@@ -2873,7 +2895,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>17</v>
@@ -2895,7 +2917,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>22</v>
@@ -2919,7 +2941,7 @@
         <v>46</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>25</v>
@@ -2943,7 +2965,7 @@
         <v>47</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>26</v>
@@ -2967,7 +2989,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>29</v>
@@ -2991,7 +3013,7 @@
         <v>49</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>90</v>
@@ -3015,7 +3037,7 @@
         <v>64</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>91</v>
@@ -3037,7 +3059,7 @@
         <v>65</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>94</v>
@@ -3059,7 +3081,7 @@
         <v>66</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>95</v>
@@ -3081,7 +3103,7 @@
         <v>67</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>98</v>
@@ -3175,7 +3197,7 @@
         <v>71</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>129</v>
@@ -3190,7 +3212,7 @@
         <v>8</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3201,13 +3223,13 @@
         <v>83</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>591</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="2" t="s">
@@ -3234,7 +3256,7 @@
         <v>20</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3276,7 +3298,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -3286,14 +3308,18 @@
       <c r="C29" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
+      <c r="D29" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>655</v>
+      </c>
       <c r="F29" s="1"/>
       <c r="G29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>138</v>
+        <v>656</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3307,7 +3333,7 @@
         <v>51</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -3315,7 +3341,7 @@
         <v>8</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3326,7 +3352,7 @@
         <v>89</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -3335,7 +3361,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3346,10 +3372,10 @@
         <v>103</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -3357,7 +3383,7 @@
         <v>20</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3368,10 +3394,10 @@
         <v>104</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -3379,7 +3405,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3390,10 +3416,10 @@
         <v>105</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>128</v>
@@ -3414,13 +3440,13 @@
         <v>106</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="2" t="s">
@@ -3436,20 +3462,20 @@
         <v>107</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3460,10 +3486,10 @@
         <v>108</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -3471,7 +3497,7 @@
         <v>20</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3482,10 +3508,10 @@
         <v>109</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -3493,7 +3519,7 @@
         <v>20</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3504,10 +3530,10 @@
         <v>110</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -3515,7 +3541,7 @@
         <v>8</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3523,13 +3549,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
@@ -3537,7 +3563,7 @@
         <v>8</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
@@ -3545,23 +3571,23 @@
         <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>650</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>651</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3569,13 +3595,13 @@
         <v>39</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>652</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>653</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>128</v>
@@ -3593,13 +3619,13 @@
         <v>40</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -3607,7 +3633,7 @@
         <v>8</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3615,13 +3641,13 @@
         <v>41</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -3629,7 +3655,7 @@
         <v>8</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3637,13 +3663,13 @@
         <v>42</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>449</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -3651,7 +3677,7 @@
         <v>19</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3659,19 +3685,19 @@
         <v>43</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>615</v>
-      </c>
       <c r="F46" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>19</v>
@@ -3683,19 +3709,19 @@
         <v>44</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>617</v>
-      </c>
       <c r="F47" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>19</v>
@@ -3710,20 +3736,20 @@
         <v>111</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3734,10 +3760,10 @@
         <v>112</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>128</v>
@@ -3757,20 +3783,20 @@
         <v>113</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D50" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>620</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="51" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3781,10 +3807,10 @@
         <v>114</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>128</v>
@@ -3803,20 +3829,20 @@
         <v>115</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>647</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>648</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3827,20 +3853,20 @@
         <v>116</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="54" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -3851,20 +3877,20 @@
         <v>117</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>455</v>
+        <v>659</v>
       </c>
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3875,10 +3901,10 @@
         <v>118</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>128</v>
@@ -3891,28 +3917,28 @@
       </c>
       <c r="H55" s="3"/>
     </row>
-    <row r="56" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>53</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>455</v>
+        <v>658</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3923,10 +3949,10 @@
         <v>119</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>128</v>
@@ -3947,16 +3973,16 @@
         <v>120</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D58" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>644</v>
-      </c>
       <c r="F58" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>19</v>
@@ -3968,13 +3994,13 @@
         <v>56</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>128</v>
@@ -3995,16 +4021,16 @@
         <v>121</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>19</v>
@@ -4018,10 +4044,10 @@
         <v>122</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
@@ -4038,16 +4064,16 @@
         <v>123</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D62" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>607</v>
-      </c>
       <c r="F62" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>19</v>
@@ -4062,10 +4088,10 @@
         <v>124</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>128</v>
@@ -4086,16 +4112,16 @@
         <v>125</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>19</v>
@@ -4110,10 +4136,10 @@
         <v>126</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>128</v>
@@ -4134,16 +4160,16 @@
         <v>127</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>613</v>
-      </c>
       <c r="F66" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>19</v>
@@ -4155,13 +4181,13 @@
         <v>64</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>128</v>
@@ -4179,23 +4205,23 @@
         <v>65</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="69" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4203,23 +4229,23 @@
         <v>66</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C69" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="E69" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="70" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4227,13 +4253,13 @@
         <v>67</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>128</v>
@@ -4251,19 +4277,19 @@
         <v>68</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C71" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="F71" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>19</v>
@@ -4275,19 +4301,19 @@
         <v>69</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C72" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>412</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>19</v>
@@ -4299,23 +4325,23 @@
         <v>70</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C73" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="E73" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="74" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4323,23 +4349,23 @@
         <v>71</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D74" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>428</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="75" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4347,23 +4373,23 @@
         <v>72</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="76" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4371,13 +4397,13 @@
         <v>73</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C76" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>432</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>128</v>
@@ -4395,19 +4421,19 @@
         <v>74</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C77" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F77" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>19</v>
@@ -4419,13 +4445,13 @@
         <v>75</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C78" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>440</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>128</v>
@@ -4443,23 +4469,23 @@
         <v>76</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C79" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="E79" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F79" s="1"/>
       <c r="G79" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="80" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
@@ -4467,23 +4493,23 @@
         <v>77</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D80" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>397</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="81" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4491,23 +4517,23 @@
         <v>78</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F81" s="1"/>
       <c r="G81" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="82" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4515,13 +4541,13 @@
         <v>79</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>128</v>
@@ -4539,19 +4565,19 @@
         <v>80</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>19</v>
@@ -4563,13 +4589,13 @@
         <v>81</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>128</v>
@@ -4587,19 +4613,19 @@
         <v>82</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>19</v>
@@ -4611,13 +4637,13 @@
         <v>83</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>128</v>
@@ -4635,19 +4661,19 @@
         <v>84</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D87" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="F87" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>19</v>
@@ -4659,19 +4685,19 @@
         <v>85</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C88" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>405</v>
-      </c>
       <c r="F88" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>19</v>
@@ -4683,25 +4709,25 @@
         <v>86</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C89" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="D89" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="90" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -4709,23 +4735,23 @@
         <v>87</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F90" s="1"/>
       <c r="G90" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="91" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4733,23 +4759,23 @@
         <v>88</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="92" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4757,13 +4783,13 @@
         <v>89</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>128</v>
@@ -4781,23 +4807,23 @@
         <v>90</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F93" s="1"/>
       <c r="G93" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="94" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4805,13 +4831,13 @@
         <v>91</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>128</v>
@@ -4829,19 +4855,19 @@
         <v>92</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>19</v>
@@ -4853,13 +4879,13 @@
         <v>93</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>128</v>
@@ -4877,23 +4903,23 @@
         <v>94</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="F97" s="1"/>
       <c r="G97" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="98" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4901,23 +4927,23 @@
         <v>95</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D98" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="F98" s="1"/>
       <c r="G98" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="99" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4925,23 +4951,23 @@
         <v>96</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F99" s="1"/>
       <c r="G99" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="100" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4949,23 +4975,23 @@
         <v>97</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F100" s="1"/>
       <c r="G100" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="101" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4973,25 +4999,25 @@
         <v>98</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C101" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="E101" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="F101" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="102" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4999,16 +5025,16 @@
         <v>99</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F102" s="1"/>
       <c r="G102" s="2" t="s">
@@ -5021,23 +5047,23 @@
         <v>100</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F103" s="1"/>
       <c r="G103" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="104" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5045,13 +5071,13 @@
         <v>101</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>128</v>
@@ -5069,25 +5095,25 @@
         <v>102</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="106" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5095,13 +5121,13 @@
         <v>103</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>128</v>
@@ -5119,25 +5145,25 @@
         <v>104</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="108" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5145,13 +5171,13 @@
         <v>105</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>128</v>
@@ -5169,19 +5195,19 @@
         <v>106</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D109" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="F109" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>19</v>
@@ -5193,25 +5219,25 @@
         <v>107</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C110" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="E110" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="F110" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="111" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -5219,19 +5245,19 @@
         <v>108</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>19</v>
@@ -5243,16 +5269,16 @@
         <v>109</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F112" s="1"/>
       <c r="G112" s="2" t="s">
@@ -5265,13 +5291,13 @@
         <v>110</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>128</v>
@@ -5289,19 +5315,19 @@
         <v>111</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>19</v>
@@ -5313,13 +5339,13 @@
         <v>112</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>128</v>
@@ -5337,19 +5363,19 @@
         <v>113</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>19</v>
@@ -5361,13 +5387,13 @@
         <v>114</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>128</v>
@@ -5387,25 +5413,25 @@
         <v>115</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D118" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E118" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E118" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="F118" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="119" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5413,23 +5439,23 @@
         <v>116</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C119" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>308</v>
       </c>
       <c r="F119" s="1"/>
       <c r="G119" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="120" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -5437,23 +5463,23 @@
         <v>117</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F120" s="1"/>
       <c r="G120" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="121" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -5461,23 +5487,23 @@
         <v>118</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F121" s="1"/>
       <c r="G121" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="122" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5485,25 +5511,25 @@
         <v>119</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C122" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="D122" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="F122" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="123" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -5511,19 +5537,19 @@
         <v>120</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>19</v>
@@ -5535,25 +5561,25 @@
         <v>121</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="125" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5561,13 +5587,13 @@
         <v>122</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>128</v>
@@ -5585,25 +5611,25 @@
         <v>123</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="127" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5611,13 +5637,13 @@
         <v>124</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>128</v>
@@ -5635,19 +5661,19 @@
         <v>125</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>19</v>
@@ -5659,13 +5685,13 @@
         <v>126</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>128</v>
@@ -5683,19 +5709,19 @@
         <v>127</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D130" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E130" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="F130" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>19</v>
@@ -5707,23 +5733,23 @@
         <v>128</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F131" s="1"/>
       <c r="G131" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5731,23 +5757,23 @@
         <v>129</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D132" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="F132" s="1"/>
       <c r="G132" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="133" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5755,23 +5781,23 @@
         <v>130</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D133" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="F133" s="1"/>
       <c r="G133" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="134" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5779,23 +5805,23 @@
         <v>131</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D134" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E134" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="F134" s="1"/>
       <c r="G134" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="135" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5803,23 +5829,23 @@
         <v>132</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C135" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="F135" s="1"/>
       <c r="G135" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="136" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5827,23 +5853,23 @@
         <v>133</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C136" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="E136" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="F136" s="1"/>
       <c r="G136" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="137" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5851,23 +5877,23 @@
         <v>134</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C137" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="E137" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>265</v>
       </c>
       <c r="F137" s="1"/>
       <c r="G137" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="138" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5875,23 +5901,23 @@
         <v>135</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C138" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="E138" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>247</v>
       </c>
       <c r="F138" s="1"/>
       <c r="G138" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="139" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5899,23 +5925,23 @@
         <v>136</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C139" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="E139" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="F139" s="1"/>
       <c r="G139" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="140" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5923,25 +5949,25 @@
         <v>137</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D140" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F140" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>271</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="141" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5949,25 +5975,25 @@
         <v>138</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C141" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="E141" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E141" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="F141" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="142" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -5975,23 +6001,23 @@
         <v>139</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D142" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="F142" s="1"/>
       <c r="G142" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="143" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -5999,13 +6025,13 @@
         <v>140</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>128</v>
@@ -6023,13 +6049,13 @@
         <v>141</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>128</v>
@@ -6041,7 +6067,7 @@
         <v>20</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="145" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6049,19 +6075,19 @@
         <v>142</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>100</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>19</v>
@@ -6073,23 +6099,23 @@
         <v>143</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D146" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E146" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="F146" s="1"/>
       <c r="G146" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="147" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6097,25 +6123,25 @@
         <v>144</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D147" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E147" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E147" s="1" t="s">
+      <c r="F147" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="148" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6123,19 +6149,19 @@
         <v>145</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D148" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E148" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="F148" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>19</v>
@@ -6147,13 +6173,13 @@
         <v>146</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
@@ -6161,7 +6187,7 @@
         <v>20</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="150" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6169,23 +6195,23 @@
         <v>147</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D150" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E150" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="F150" s="1"/>
       <c r="G150" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="151" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6193,23 +6219,23 @@
         <v>148</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F151" s="1"/>
       <c r="G151" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="152" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6217,23 +6243,23 @@
         <v>149</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C152" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D152" s="1" t="s">
+      <c r="E152" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="F152" s="1"/>
       <c r="G152" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="153" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6241,23 +6267,23 @@
         <v>150</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D153" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="F153" s="1"/>
       <c r="G153" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="154" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6265,16 +6291,16 @@
         <v>151</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D154" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E154" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="F154" s="1"/>
       <c r="G154" s="2" t="s">
@@ -6287,19 +6313,19 @@
         <v>152</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>19</v>
@@ -6311,19 +6337,19 @@
         <v>153</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>19</v>
@@ -6335,19 +6361,19 @@
         <v>154</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C157" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D157" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="E157" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>19</v>
@@ -6359,23 +6385,23 @@
         <v>155</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D158" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="F158" s="1"/>
       <c r="G158" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="159" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -6383,23 +6409,23 @@
         <v>156</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="160" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -6407,13 +6433,13 @@
         <v>157</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>128</v>
@@ -6429,19 +6455,19 @@
         <v>158</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>101</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>19</v>
@@ -6453,23 +6479,23 @@
         <v>159</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C162" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D162" s="1" t="s">
+      <c r="E162" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="F162" s="1"/>
       <c r="G162" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="163" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6477,23 +6503,23 @@
         <v>160</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>102</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F163" s="1"/>
       <c r="G163" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="164" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6501,29 +6527,31 @@
         <v>161</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C164" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D164" s="1" t="s">
+      <c r="E164" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="F164" s="1"/>
       <c r="G164" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H164" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>657</v>
+      </c>
     </row>
     <row r="165" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>162</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>53</v>
@@ -6549,7 +6577,7 @@
         <v>163</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>58</v>
@@ -6565,7 +6593,7 @@
         <v>8</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="167" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6573,7 +6601,7 @@
         <v>164</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>61</v>

--- a/App/TestCases_App/User_admin.xlsx
+++ b/App/TestCases_App/User_admin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC53DEE-0F03-4126-A0D9-5A4BF7727F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B6F5B4-72CB-4008-BFC2-519977461EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="663">
   <si>
     <t>Num</t>
   </si>
@@ -604,9 +604,6 @@
   </si>
   <si>
     <t>No hace nada, se queda cargando, añadir funcionalidad</t>
-  </si>
-  <si>
-    <t>Aparece un mensaje de que "seleccione una serie de facturación" que no viene por ningún sitio: FAC002.jpg</t>
   </si>
   <si>
     <t>Aparece un mensaje de que "seleccione una serie de facturación" que no viene por ningún sitio FAC002.jpg</t>
@@ -2210,6 +2207,19 @@
 Al desplegar el teclado, se tapa la funcionalidad: MEN003.jpg
 Parece q me guarda el menú pero cuando voy a consultarlo, ha desaparecido.
 Se produce un error al guardar el menú: MEN005.jpg,MEN006.jpg</t>
+  </si>
+  <si>
+    <t>Al añadir modificadores, no se está teniendo en cuenta en la suma: PED001.jpg</t>
+  </si>
+  <si>
+    <t>Aparece un mensaje de que "seleccione una serie de facturación" que no viene por ningún sitio: FAC002.jpg
+En el restaurante Gran Via, me ha permitido generar factura, pero hay errores: FAC005.jpg y FAC006.jpg</t>
+  </si>
+  <si>
+    <t>1.The invoicing is created</t>
+  </si>
+  <si>
+    <t>1.The invoicing is not created</t>
   </si>
 </sst>
 </file>
@@ -2727,10 +2737,10 @@
         <v>36</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>579</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>580</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -2738,7 +2748,7 @@
         <v>8</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -2749,7 +2759,7 @@
         <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>9</v>
@@ -2760,7 +2770,7 @@
         <v>8</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -2771,7 +2781,7 @@
         <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -2793,7 +2803,7 @@
         <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>12</v>
@@ -2815,7 +2825,7 @@
         <v>40</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>15</v>
@@ -2835,10 +2845,10 @@
         <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>587</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>588</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -2855,7 +2865,7 @@
         <v>42</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>13</v>
@@ -2863,9 +2873,11 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>659</v>
+      </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2875,7 +2887,7 @@
         <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>14</v>
@@ -2895,7 +2907,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>17</v>
@@ -2917,7 +2929,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>22</v>
@@ -2941,7 +2953,7 @@
         <v>46</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>25</v>
@@ -2965,7 +2977,7 @@
         <v>47</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>26</v>
@@ -2989,7 +3001,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>29</v>
@@ -3013,7 +3025,7 @@
         <v>49</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>90</v>
@@ -3037,7 +3049,7 @@
         <v>64</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>91</v>
@@ -3059,7 +3071,7 @@
         <v>65</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>94</v>
@@ -3081,7 +3093,7 @@
         <v>66</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>95</v>
@@ -3103,7 +3115,7 @@
         <v>67</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>98</v>
@@ -3197,7 +3209,7 @@
         <v>71</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>129</v>
@@ -3223,13 +3235,13 @@
         <v>83</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>590</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="2" t="s">
@@ -3256,7 +3268,7 @@
         <v>20</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3309,17 +3321,17 @@
         <v>137</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>654</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>655</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3341,7 +3353,7 @@
         <v>8</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3361,7 +3373,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3377,13 +3389,17 @@
       <c r="D32" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
+      <c r="E32" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>662</v>
+      </c>
       <c r="G32" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>167</v>
+        <v>660</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3405,7 +3421,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3475,7 +3491,7 @@
         <v>20</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3541,7 +3557,7 @@
         <v>8</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3549,10 +3565,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>164</v>
@@ -3563,7 +3579,7 @@
         <v>8</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
@@ -3571,23 +3587,23 @@
         <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>649</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>650</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3595,13 +3611,13 @@
         <v>39</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>651</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>652</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>128</v>
@@ -3619,13 +3635,13 @@
         <v>40</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -3633,7 +3649,7 @@
         <v>8</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3641,13 +3657,13 @@
         <v>41</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -3655,7 +3671,7 @@
         <v>8</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3663,13 +3679,13 @@
         <v>42</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>448</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -3677,7 +3693,7 @@
         <v>19</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3685,19 +3701,19 @@
         <v>43</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>614</v>
-      </c>
       <c r="F46" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>19</v>
@@ -3709,19 +3725,19 @@
         <v>44</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>616</v>
-      </c>
       <c r="F47" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>19</v>
@@ -3736,20 +3752,20 @@
         <v>111</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3760,10 +3776,10 @@
         <v>112</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>128</v>
@@ -3783,20 +3799,20 @@
         <v>113</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D50" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>619</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="51" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3807,10 +3823,10 @@
         <v>114</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>128</v>
@@ -3829,20 +3845,20 @@
         <v>115</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>646</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>647</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3853,20 +3869,20 @@
         <v>116</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="54" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -3877,20 +3893,20 @@
         <v>117</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3901,10 +3917,10 @@
         <v>118</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>128</v>
@@ -3922,23 +3938,23 @@
         <v>53</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3949,10 +3965,10 @@
         <v>119</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>128</v>
@@ -3973,16 +3989,16 @@
         <v>120</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D58" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>643</v>
-      </c>
       <c r="F58" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>19</v>
@@ -3994,13 +4010,13 @@
         <v>56</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>128</v>
@@ -4021,16 +4037,16 @@
         <v>121</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>19</v>
@@ -4044,7 +4060,7 @@
         <v>122</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>139</v>
@@ -4064,16 +4080,16 @@
         <v>123</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D62" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>606</v>
-      </c>
       <c r="F62" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>19</v>
@@ -4088,10 +4104,10 @@
         <v>124</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>128</v>
@@ -4112,16 +4128,16 @@
         <v>125</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>19</v>
@@ -4136,10 +4152,10 @@
         <v>126</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>128</v>
@@ -4160,16 +4176,16 @@
         <v>127</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>612</v>
-      </c>
       <c r="F66" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>19</v>
@@ -4181,13 +4197,13 @@
         <v>64</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>128</v>
@@ -4205,23 +4221,23 @@
         <v>65</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="69" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4229,23 +4245,23 @@
         <v>66</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C69" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>418</v>
-      </c>
       <c r="E69" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="70" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4253,13 +4269,13 @@
         <v>67</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>128</v>
@@ -4277,19 +4293,19 @@
         <v>68</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C71" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>409</v>
-      </c>
       <c r="F71" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>19</v>
@@ -4301,19 +4317,19 @@
         <v>69</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C72" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>411</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>19</v>
@@ -4325,23 +4341,23 @@
         <v>70</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C73" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="E73" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="74" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4349,23 +4365,23 @@
         <v>71</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D74" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>427</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="75" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4373,23 +4389,23 @@
         <v>72</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="76" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4397,13 +4413,13 @@
         <v>73</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C76" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>431</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>128</v>
@@ -4421,19 +4437,19 @@
         <v>74</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C77" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>437</v>
-      </c>
       <c r="F77" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>19</v>
@@ -4445,13 +4461,13 @@
         <v>75</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C78" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>439</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>128</v>
@@ -4469,23 +4485,23 @@
         <v>76</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C79" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>441</v>
-      </c>
       <c r="E79" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F79" s="1"/>
       <c r="G79" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="80" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
@@ -4493,23 +4509,23 @@
         <v>77</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D80" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="81" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4517,23 +4533,23 @@
         <v>78</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F81" s="1"/>
       <c r="G81" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="82" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4541,13 +4557,13 @@
         <v>79</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>128</v>
@@ -4565,19 +4581,19 @@
         <v>80</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>19</v>
@@ -4589,13 +4605,13 @@
         <v>81</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>128</v>
@@ -4613,19 +4629,19 @@
         <v>82</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>19</v>
@@ -4637,13 +4653,13 @@
         <v>83</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>128</v>
@@ -4661,19 +4677,19 @@
         <v>84</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D87" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="F87" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>19</v>
@@ -4685,19 +4701,19 @@
         <v>85</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C88" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="F88" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>19</v>
@@ -4709,25 +4725,25 @@
         <v>86</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C89" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D89" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="90" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -4735,23 +4751,23 @@
         <v>87</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F90" s="1"/>
       <c r="G90" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="91" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4759,23 +4775,23 @@
         <v>88</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="92" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4783,13 +4799,13 @@
         <v>89</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>128</v>
@@ -4807,23 +4823,23 @@
         <v>90</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F93" s="1"/>
       <c r="G93" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="94" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4831,13 +4847,13 @@
         <v>91</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>128</v>
@@ -4855,19 +4871,19 @@
         <v>92</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>19</v>
@@ -4879,13 +4895,13 @@
         <v>93</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>128</v>
@@ -4903,23 +4919,23 @@
         <v>94</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="F97" s="1"/>
       <c r="G97" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4927,23 +4943,23 @@
         <v>95</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D98" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>370</v>
       </c>
       <c r="F98" s="1"/>
       <c r="G98" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="99" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4951,23 +4967,23 @@
         <v>96</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F99" s="1"/>
       <c r="G99" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="100" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4975,23 +4991,23 @@
         <v>97</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F100" s="1"/>
       <c r="G100" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="101" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4999,25 +5015,25 @@
         <v>98</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C101" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="E101" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="F101" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="102" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -5025,16 +5041,16 @@
         <v>99</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F102" s="1"/>
       <c r="G102" s="2" t="s">
@@ -5047,23 +5063,23 @@
         <v>100</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F103" s="1"/>
       <c r="G103" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="104" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5071,13 +5087,13 @@
         <v>101</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>128</v>
@@ -5095,25 +5111,25 @@
         <v>102</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="106" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5121,13 +5137,13 @@
         <v>103</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>128</v>
@@ -5145,25 +5161,25 @@
         <v>104</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="108" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5171,13 +5187,13 @@
         <v>105</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>128</v>
@@ -5195,19 +5211,19 @@
         <v>106</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D109" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="F109" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>19</v>
@@ -5219,25 +5235,25 @@
         <v>107</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C110" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="E110" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="F110" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -5245,19 +5261,19 @@
         <v>108</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>19</v>
@@ -5269,16 +5285,16 @@
         <v>109</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F112" s="1"/>
       <c r="G112" s="2" t="s">
@@ -5291,13 +5307,13 @@
         <v>110</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>128</v>
@@ -5315,19 +5331,19 @@
         <v>111</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>19</v>
@@ -5339,13 +5355,13 @@
         <v>112</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>128</v>
@@ -5363,19 +5379,19 @@
         <v>113</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>19</v>
@@ -5387,13 +5403,13 @@
         <v>114</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>128</v>
@@ -5413,25 +5429,25 @@
         <v>115</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D118" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E118" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E118" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="F118" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="119" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5439,23 +5455,23 @@
         <v>116</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C119" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>307</v>
       </c>
       <c r="F119" s="1"/>
       <c r="G119" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="120" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -5463,23 +5479,23 @@
         <v>117</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F120" s="1"/>
       <c r="G120" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="121" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -5487,23 +5503,23 @@
         <v>118</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F121" s="1"/>
       <c r="G121" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="122" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5511,25 +5527,25 @@
         <v>119</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>140</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="123" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -5537,19 +5553,19 @@
         <v>120</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>19</v>
@@ -5561,25 +5577,25 @@
         <v>121</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="125" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5587,13 +5603,13 @@
         <v>122</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>128</v>
@@ -5611,25 +5627,25 @@
         <v>123</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="127" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5637,13 +5653,13 @@
         <v>124</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>128</v>
@@ -5661,19 +5677,19 @@
         <v>125</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>19</v>
@@ -5685,13 +5701,13 @@
         <v>126</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>128</v>
@@ -5709,19 +5725,19 @@
         <v>127</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D130" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E130" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="F130" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>19</v>
@@ -5733,23 +5749,23 @@
         <v>128</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>141</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F131" s="1"/>
       <c r="G131" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="132" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5757,23 +5773,23 @@
         <v>129</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D132" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>248</v>
       </c>
       <c r="F132" s="1"/>
       <c r="G132" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="133" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5781,23 +5797,23 @@
         <v>130</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D133" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="F133" s="1"/>
       <c r="G133" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="134" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5805,23 +5821,23 @@
         <v>131</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D134" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E134" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>256</v>
       </c>
       <c r="F134" s="1"/>
       <c r="G134" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="135" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5829,23 +5845,23 @@
         <v>132</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C135" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="F135" s="1"/>
       <c r="G135" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="136" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5853,23 +5869,23 @@
         <v>133</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C136" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="E136" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="F136" s="1"/>
       <c r="G136" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="137" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5877,23 +5893,23 @@
         <v>134</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C137" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="E137" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>264</v>
       </c>
       <c r="F137" s="1"/>
       <c r="G137" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="138" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5901,23 +5917,23 @@
         <v>135</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C138" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="E138" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>246</v>
       </c>
       <c r="F138" s="1"/>
       <c r="G138" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="139" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5925,23 +5941,23 @@
         <v>136</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C139" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="E139" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>268</v>
       </c>
       <c r="F139" s="1"/>
       <c r="G139" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="140" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5949,25 +5965,25 @@
         <v>137</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D140" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="F140" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>270</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="141" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5975,25 +5991,25 @@
         <v>138</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C141" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="E141" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="E141" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="F141" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="142" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6001,23 +6017,23 @@
         <v>139</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D142" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="F142" s="1"/>
       <c r="G142" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="143" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6025,13 +6041,13 @@
         <v>140</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>128</v>
@@ -6049,13 +6065,13 @@
         <v>141</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>128</v>
@@ -6067,7 +6083,7 @@
         <v>20</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="145" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6075,7 +6091,7 @@
         <v>142</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>100</v>
@@ -6084,10 +6100,10 @@
         <v>142</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>19</v>
@@ -6099,23 +6115,23 @@
         <v>143</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D146" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E146" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="F146" s="1"/>
       <c r="G146" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="147" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6123,25 +6139,25 @@
         <v>144</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D147" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E147" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E147" s="1" t="s">
+      <c r="F147" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="148" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6149,19 +6165,19 @@
         <v>145</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D148" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E148" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="F148" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>19</v>
@@ -6173,13 +6189,13 @@
         <v>146</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
@@ -6187,7 +6203,7 @@
         <v>20</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="150" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6195,23 +6211,23 @@
         <v>147</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D150" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E150" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="F150" s="1"/>
       <c r="G150" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="151" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6219,23 +6235,23 @@
         <v>148</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F151" s="1"/>
       <c r="G151" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="152" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6243,23 +6259,23 @@
         <v>149</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C152" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D152" s="1" t="s">
+      <c r="E152" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="F152" s="1"/>
       <c r="G152" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="153" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6267,23 +6283,23 @@
         <v>150</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D153" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="F153" s="1"/>
       <c r="G153" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="154" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6291,16 +6307,16 @@
         <v>151</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D154" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E154" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="F154" s="1"/>
       <c r="G154" s="2" t="s">
@@ -6313,19 +6329,19 @@
         <v>152</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>19</v>
@@ -6337,19 +6353,19 @@
         <v>153</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>19</v>
@@ -6361,19 +6377,19 @@
         <v>154</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C157" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D157" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="E157" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>19</v>
@@ -6385,23 +6401,23 @@
         <v>155</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D158" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="F158" s="1"/>
       <c r="G158" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="159" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -6409,23 +6425,23 @@
         <v>156</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="160" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -6433,13 +6449,13 @@
         <v>157</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>128</v>
@@ -6455,7 +6471,7 @@
         <v>158</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>101</v>
@@ -6464,10 +6480,10 @@
         <v>143</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>19</v>
@@ -6479,23 +6495,23 @@
         <v>159</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C162" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D162" s="1" t="s">
+      <c r="E162" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="F162" s="1"/>
       <c r="G162" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="163" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6503,7 +6519,7 @@
         <v>160</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>102</v>
@@ -6512,14 +6528,14 @@
         <v>144</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F163" s="1"/>
       <c r="G163" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="164" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6527,23 +6543,23 @@
         <v>161</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C164" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="D164" s="1" t="s">
+      <c r="E164" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="F164" s="1"/>
       <c r="G164" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="165" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6551,7 +6567,7 @@
         <v>162</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>53</v>
@@ -6577,7 +6593,7 @@
         <v>163</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>58</v>
@@ -6593,7 +6609,7 @@
         <v>8</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="167" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6601,7 +6617,7 @@
         <v>164</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>61</v>

--- a/App/TestCases_App/User_admin.xlsx
+++ b/App/TestCases_App/User_admin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B6F5B4-72CB-4008-BFC2-519977461EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C6F3FD-8B46-4B4E-9C4A-E59502FA1AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="678">
   <si>
     <t>Num</t>
   </si>
@@ -60,11 +60,6 @@
   </si>
   <si>
     <t>KO</t>
-  </si>
-  <si>
-    <t>1. Select numbers of people
-2. Select several products
-3. Clicks "Cerrar mesa"</t>
   </si>
   <si>
     <t>1. Select numbers of people
@@ -76,37 +71,7 @@
     <t>Las mesas no se unen.</t>
   </si>
   <si>
-    <t>1. Select numbers of people
-2. Select several products
-3. Add fee
-4. Clicks "Cerrar mesa"</t>
-  </si>
-  <si>
-    <t>1. Select numbers of people
-2. Select a product
-3. Add a modifier, clicks "Añadir al pedido"
-4. Clicks "Cerrar mesa"</t>
-  </si>
-  <si>
-    <t>1. Select numbers of people
-2. Select a product
-3. Add a modifier, clicks "Cancelar"
-4. Clicks "Cerrar mesa"</t>
-  </si>
-  <si>
-    <t>1. Select numbers of people
-2. Select several products with his modifiers
-3. Select menu
-4. Clicks "Cerrar mesa"</t>
-  </si>
-  <si>
     <t>Con cada producto añadido, se está añadiendo el suplemento de terraza. Waiter003.jpg</t>
-  </si>
-  <si>
-    <t>1. Select numbers of people
-2. Select products
-3. Clicks "Realizar pago"
-4. Clicks "Cerrar mesa"</t>
   </si>
   <si>
     <t>Se reparte la cuenta entre ocho, se hace un pago en efectivo, se hace un pago con tarjeta, pero al pagar el resto de la cuenta indica, se ha pagado 1/8 cuando han sido 2/8. Waiter004.jpg</t>
@@ -151,12 +116,6 @@
     <t xml:space="preserve">Es necesario pulsar varias veces "Cancelar" </t>
   </si>
   <si>
-    <t xml:space="preserve">1. Select numbers of people
-2. Select products
-3. Clicks "Enviar comanda"
-</t>
-  </si>
-  <si>
     <t>The order is sent</t>
   </si>
   <si>
@@ -222,9 +181,6 @@
   </si>
   <si>
     <t>Invoicing</t>
-  </si>
-  <si>
-    <t>pte</t>
   </si>
   <si>
     <t>Pending tasks</t>
@@ -1875,9 +1831,6 @@
     <t>USERADM161</t>
   </si>
   <si>
-    <t>Views of tables:Take order: Fee</t>
-  </si>
-  <si>
     <t>Cash closing: Normal cash register closing declared</t>
   </si>
   <si>
@@ -1893,9 +1846,6 @@
     <t>Cash closing: page</t>
   </si>
   <si>
-    <t>Views of tables: Take order, Add modifiers</t>
-  </si>
-  <si>
     <t>Views of tables: Take order, Add modifiers, cancel</t>
   </si>
   <si>
@@ -1918,9 +1868,6 @@
   </si>
   <si>
     <t>Views of tables: Take order, Join table</t>
-  </si>
-  <si>
-    <t>Views of tables: Take order</t>
   </si>
   <si>
     <t>Views of tables: page</t>
@@ -1951,12 +1898,6 @@
   </si>
   <si>
     <t>Views of tables: Take order,search a product</t>
-  </si>
-  <si>
-    <t>1. Select numbers of people
-2. Select search product
-3. Add product
-4. Clicks "Cerrar mesa"</t>
   </si>
   <si>
     <t>Tickets' history: search</t>
@@ -2209,9 +2150,6 @@
 Se produce un error al guardar el menú: MEN005.jpg,MEN006.jpg</t>
   </si>
   <si>
-    <t>Al añadir modificadores, no se está teniendo en cuenta en la suma: PED001.jpg</t>
-  </si>
-  <si>
     <t>Aparece un mensaje de que "seleccione una serie de facturación" que no viene por ningún sitio: FAC002.jpg
 En el restaurante Gran Via, me ha permitido generar factura, pero hay errores: FAC005.jpg y FAC006.jpg</t>
   </si>
@@ -2220,13 +2158,167 @@
   </si>
   <si>
     <t>1.The invoicing is not created</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Select numbers of people, clicks "Cancelar"
+</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order,search a product, cancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Select numbers of people
+2. Select a product
+3. Add a modifier, clicks "Añadir al pedido"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Select numbers of people
+2. Select a product
+3. Clicks "Cancelar"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Select numbers of people
+2. Select a product
+3. Add a modifier, clicks "Añadir al pedido"
+4. Send the order
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Select numbers of people
+2. Select products
+3. Clicks "Realizar pago"
+</t>
+  </si>
+  <si>
+    <t>The table is closed.</t>
+  </si>
+  <si>
+    <t>1. The user can "Enviar Comanda" o "Realizar pago"</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order, Add product and modifiers</t>
+  </si>
+  <si>
+    <t>1. The user only can "Cerrar mesa"</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order, delete all products of a table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Select a table with products
+2. Delete all products
+</t>
+  </si>
+  <si>
+    <t>1. Select numbers of people
+2. Select several products
+3. Add fee</t>
+  </si>
+  <si>
+    <t>1. Select numbers of people
+2. Select several products with his modifiers
+3. Select menu</t>
+  </si>
+  <si>
+    <t>1. Select numbers of people, clicks "Aceptar"
+2. Select search product
+3. Add product</t>
+  </si>
+  <si>
+    <t>USERADM165</t>
+  </si>
+  <si>
+    <t>USERADM166</t>
+  </si>
+  <si>
+    <t>USERADM167</t>
+  </si>
+  <si>
+    <t>USERADM168</t>
+  </si>
+  <si>
+    <t>Views of tables:Take order,Fee</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Al añadir modificadores, no se está teniendo en cuenta en la suma: PED001.jpg
+14/05/26: Se ha observado un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>comportamiento distinto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> si el producto añadido tiene modificadores o no. Por ejemplo el solomillo al Pedro Ximenex si tiene, al pulsar al + , me abre ese producto para q modifique ese producto, pero si x el contrario, no tiene modificadores, me añade uno más, es decir, si aparecía 1, ahora aparecen 2.
+Al pulsar sobre un producto que tiene suplemento, entrar a consultarlo, y cancelar, se recalcula el precio y a veces </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pone 1cto más o menos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: PED002.jgp, PED003.jpg</t>
+    </r>
+  </si>
+  <si>
+    <t>1. The product is added.</t>
+  </si>
+  <si>
+    <t>No veo variación al cambiar de menú</t>
+  </si>
+  <si>
+    <t>1. The products shown are the menu's product.</t>
+  </si>
+  <si>
+    <t>The fee is added</t>
+  </si>
+  <si>
+    <t>The tables are joined.</t>
+  </si>
+  <si>
+    <t>1. Select numbers of people
+2. Clicks "Cerrar mesa"</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order, close table</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2261,6 +2353,23 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2666,7 +2775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H167"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -2710,23 +2819,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -2734,13 +2843,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -2748,7 +2857,7 @@
         <v>8</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -2756,21 +2865,23 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>577</v>
+        <v>677</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="1"/>
+        <v>676</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>656</v>
+      </c>
       <c r="F4" s="1"/>
       <c r="G4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -2778,219 +2889,237 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>675</v>
+      </c>
       <c r="F5" s="1"/>
       <c r="G5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>562</v>
+        <v>669</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="1"/>
+        <v>662</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>674</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="1"/>
+        <v>663</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>673</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="G7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+        <v>664</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>671</v>
+      </c>
       <c r="G8" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>568</v>
+        <v>651</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+        <v>650</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="G9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" s="6" customFormat="1" ht="150" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>569</v>
+        <v>658</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="1"/>
+        <v>652</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>657</v>
+      </c>
       <c r="F10" s="1"/>
       <c r="G10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>570</v>
+        <v>660</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+        <v>661</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>659</v>
+      </c>
       <c r="G11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>22</v>
+        <v>653</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="G12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>654</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F13" s="1"/>
       <c r="G13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>27</v>
-      </c>
+        <v>655</v>
+      </c>
+      <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -2998,112 +3127,120 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F16" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="G16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>563</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F18" s="1"/>
+        <v>84</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="G18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F19" s="1"/>
+        <v>85</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="G19" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H19" s="3"/>
     </row>
@@ -3112,68 +3249,70 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>50</v>
+        <v>555</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" s="1"/>
+        <v>89</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>89</v>
+      </c>
       <c r="G21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>75</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>76</v>
+        <v>556</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F22" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H22" s="3"/>
     </row>
@@ -3182,23 +3321,23 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>82</v>
+        <v>8</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3206,69 +3345,75 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>566</v>
+        <v>68</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>588</v>
+        <v>71</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>589</v>
+        <v>72</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="F25" s="1"/>
+        <v>73</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+        <v>557</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>122</v>
+      </c>
       <c r="G26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>583</v>
+        <v>8</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3276,18 +3421,23 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E27" s="1"/>
+        <v>576</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>571</v>
+      </c>
       <c r="F27" s="1"/>
       <c r="G27" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3295,65 +3445,58 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>654</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>138</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>591</v>
+        <v>14</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3361,67 +3504,65 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
+        <v>129</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>642</v>
+      </c>
       <c r="F31" s="1"/>
       <c r="G31" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>662</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
       <c r="G32" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>151</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>167</v>
+        <v>578</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3429,113 +3570,117 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>128</v>
+        <v>648</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>128</v>
+        <v>649</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H34" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>647</v>
+      </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>155</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H35" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F36" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="G36" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H36" s="3"/>
+    </row>
+    <row r="37" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E37" s="1"/>
+        <v>146</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F37" s="1"/>
       <c r="G37" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E38" s="1"/>
+        <v>149</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F38" s="1"/>
       <c r="G38" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3543,21 +3688,21 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>594</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3565,1470 +3710,1464 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>592</v>
+        <v>151</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>647</v>
+        <v>154</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>649</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>650</v>
+        <v>580</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
       <c r="G42" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>595</v>
+        <v>635</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="E43" s="1"/>
+        <v>636</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>637</v>
+      </c>
       <c r="F43" s="1"/>
       <c r="G43" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>596</v>
+        <v>638</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
+        <v>639</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="G44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>446</v>
+        <v>583</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>447</v>
+        <v>585</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>460</v>
+        <v>103</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>451</v>
+        <v>584</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>613</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
       <c r="G46" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H46" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>587</v>
+      </c>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>461</v>
+        <v>104</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>615</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
       <c r="G47" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H47" s="3"/>
-    </row>
-    <row r="48" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>630</v>
+        <v>443</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="F48" s="1"/>
+        <v>601</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>601</v>
+      </c>
       <c r="G48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H48" s="3"/>
+    </row>
+    <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>633</v>
+        <v>444</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>621</v>
+        <v>602</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>128</v>
+        <v>603</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>128</v>
+        <v>603</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>617</v>
+        <v>604</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H50" s="3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
-        <v>48</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F51" s="1"/>
-      <c r="G51" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H51" s="3"/>
-    </row>
-    <row r="52" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
-        <v>49</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>623</v>
-      </c>
       <c r="D52" s="1" t="s">
-        <v>645</v>
+        <v>605</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>646</v>
+        <v>606</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>644</v>
+        <v>608</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>642</v>
+        <v>120</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>117</v>
+        <v>454</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>634</v>
+        <v>612</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>630</v>
+      </c>
+      <c r="F55" s="1"/>
       <c r="G55" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H55" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>631</v>
+      </c>
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>462</v>
+        <v>112</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>637</v>
+        <v>604</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>119</v>
+        <v>455</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>638</v>
+        <v>609</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H57" s="3"/>
     </row>
-    <row r="58" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>641</v>
+        <v>625</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>642</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="F58" s="1"/>
       <c r="G58" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H58" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>645</v>
+      </c>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>463</v>
+        <v>114</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H59" s="3"/>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>585</v>
+        <v>615</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>584</v>
+        <v>629</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H60" s="3"/>
+    </row>
+    <row r="61" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>443</v>
+        <v>624</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
+        <v>628</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="G61" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H61" s="3"/>
     </row>
-    <row r="62" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>442</v>
+        <v>574</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>604</v>
+        <v>573</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H62" s="3"/>
-    </row>
-    <row r="63" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
       <c r="G63" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H63" s="3"/>
     </row>
-    <row r="64" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>608</v>
+        <v>592</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H64" s="3"/>
     </row>
     <row r="65" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>126</v>
+        <v>456</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>285</v>
+        <v>594</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H65" s="3"/>
     </row>
     <row r="66" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>127</v>
+        <v>457</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H66" s="3"/>
     </row>
     <row r="67" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>609</v>
+        <v>277</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H67" s="3"/>
     </row>
-    <row r="68" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C68" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" s="3"/>
+    </row>
+    <row r="69" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" s="3"/>
+    </row>
+    <row r="70" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="F70" s="1"/>
+      <c r="G70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H70" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="F68" s="1"/>
-      <c r="G68" s="2" t="s">
+    </row>
+    <row r="71" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="F71" s="1"/>
+      <c r="G71" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H68" s="3" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
-        <v>66</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="C69" s="1" t="s">
+      <c r="H71" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="F69" s="1"/>
-      <c r="G69" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
-        <v>67</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H70" s="3"/>
-    </row>
-    <row r="71" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
-        <v>68</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H71" s="3"/>
     </row>
     <row r="72" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>412</v>
+        <v>627</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>411</v>
+        <v>120</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>410</v>
+        <v>120</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H72" s="3"/>
     </row>
     <row r="73" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>419</v>
+        <v>398</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="F73" s="1"/>
+        <v>400</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>400</v>
+      </c>
       <c r="G73" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H73" s="3"/>
+    </row>
+    <row r="74" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="F74" s="1"/>
+        <v>403</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>402</v>
+      </c>
       <c r="G74" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H74" s="3"/>
+    </row>
+    <row r="75" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>431</v>
+        <v>412</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>433</v>
+        <v>414</v>
       </c>
     </row>
     <row r="76" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="F76" s="1"/>
       <c r="G76" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H76" s="3"/>
-    </row>
-    <row r="77" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>436</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="F77" s="1"/>
       <c r="G77" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H77" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>425</v>
+      </c>
     </row>
     <row r="78" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H78" s="3"/>
     </row>
-    <row r="79" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F79" s="1"/>
+        <v>428</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>428</v>
+      </c>
       <c r="G79" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H79" s="3"/>
+    </row>
+    <row r="80" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>386</v>
+        <v>429</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>394</v>
+        <v>430</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="F80" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="G80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H80" s="3"/>
+    </row>
+    <row r="81" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>387</v>
+        <v>431</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>396</v>
+        <v>195</v>
       </c>
       <c r="F81" s="1"/>
       <c r="G81" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="F82" s="1"/>
       <c r="G82" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H82" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="83" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>284</v>
+        <v>392</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>397</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="F83" s="1"/>
       <c r="G83" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H83" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>396</v>
+      </c>
     </row>
     <row r="84" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>285</v>
+        <v>391</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H84" s="3"/>
     </row>
-    <row r="85" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>335</v>
+        <v>276</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H85" s="3"/>
     </row>
     <row r="86" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>334</v>
+        <v>277</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H86" s="3"/>
     </row>
-    <row r="87" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>286</v>
+        <v>327</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>287</v>
+        <v>390</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>287</v>
+        <v>390</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H87" s="3"/>
     </row>
-    <row r="88" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>402</v>
+        <v>326</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>403</v>
+        <v>120</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>403</v>
+        <v>120</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H88" s="3"/>
     </row>
     <row r="89" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>345</v>
+        <v>278</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>356</v>
+        <v>279</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>359</v>
+        <v>279</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H89" s="3"/>
+    </row>
+    <row r="90" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>346</v>
+        <v>393</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>354</v>
+        <v>394</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="F90" s="1"/>
+        <v>395</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>395</v>
+      </c>
       <c r="G90" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H90" s="3"/>
+    </row>
+    <row r="91" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="F91" s="1"/>
+        <v>348</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>351</v>
+      </c>
       <c r="G91" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="F92" s="1"/>
       <c r="G92" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H92" s="3"/>
-    </row>
-    <row r="93" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C93" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>361</v>
       </c>
       <c r="F93" s="1"/>
       <c r="G93" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>285</v>
+        <v>352</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H94" s="3"/>
     </row>
-    <row r="95" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>362</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="F95" s="1"/>
       <c r="G95" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H95" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>366</v>
+      </c>
     </row>
     <row r="96" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>334</v>
+        <v>277</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H96" s="3"/>
     </row>
-    <row r="97" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>286</v>
+        <v>327</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="F97" s="1"/>
+        <v>354</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>354</v>
+      </c>
       <c r="G97" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>364</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H97" s="3"/>
     </row>
     <row r="98" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>368</v>
+        <v>326</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="F98" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="G98" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H98" s="3"/>
+    </row>
+    <row r="99" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>382</v>
+        <v>345</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>372</v>
+        <v>278</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>371</v>
+        <v>279</v>
       </c>
       <c r="F99" s="1"/>
       <c r="G99" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>384</v>
+        <v>356</v>
       </c>
     </row>
     <row r="100" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>383</v>
+        <v>360</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="F100" s="1"/>
       <c r="G100" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>314</v>
+        <v>374</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>315</v>
+        <v>364</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>316</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="F101" s="1"/>
       <c r="G101" s="2" t="s">
         <v>8</v>
       </c>
@@ -5036,1219 +5175,1221 @@
         <v>376</v>
       </c>
     </row>
-    <row r="102" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>317</v>
+        <v>359</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>340</v>
+        <v>365</v>
       </c>
       <c r="F102" s="1"/>
       <c r="G102" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H102" s="3"/>
-    </row>
-    <row r="103" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>342</v>
+        <v>307</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="F103" s="1"/>
+        <v>308</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>308</v>
+      </c>
       <c r="G103" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="F104" s="1"/>
       <c r="G104" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H104" s="3"/>
     </row>
-    <row r="105" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="C105" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="D105" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>325</v>
-      </c>
+      <c r="F105" s="1"/>
       <c r="G105" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="106" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>285</v>
+        <v>331</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H106" s="3"/>
     </row>
-    <row r="107" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>603</v>
+        <v>319</v>
       </c>
     </row>
     <row r="108" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>334</v>
+        <v>277</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H108" s="3"/>
     </row>
-    <row r="109" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D109" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H110" s="3"/>
+    </row>
+    <row r="111" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H111" s="3"/>
+    </row>
+    <row r="112" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H109" s="3"/>
-    </row>
-    <row r="110" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="1">
-        <v>107</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A111" s="1">
-        <v>108</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H111" s="3"/>
-    </row>
-    <row r="112" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A112" s="1">
-        <v>109</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="F112" s="1"/>
+      <c r="F112" s="1" t="s">
+        <v>286</v>
+      </c>
       <c r="G112" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H112" s="3"/>
-    </row>
-    <row r="113" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="H112" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>128</v>
+        <v>323</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>128</v>
+        <v>323</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H113" s="3"/>
     </row>
     <row r="114" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>329</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="F114" s="1"/>
       <c r="G114" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H114" s="3"/>
     </row>
     <row r="115" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>285</v>
+        <v>330</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H115" s="3"/>
     </row>
-    <row r="116" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H116" s="3"/>
     </row>
     <row r="117" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>334</v>
+        <v>277</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H117" s="3">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H117" s="3"/>
+    </row>
+    <row r="118" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>286</v>
+        <v>327</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>287</v>
+        <v>322</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>287</v>
+        <v>322</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>313</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H118" s="3"/>
     </row>
     <row r="119" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="F119" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="G119" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H119" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H119" s="3">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>332</v>
+        <v>278</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="F120" s="1"/>
+        <v>279</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>279</v>
+      </c>
       <c r="G120" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="F121" s="1"/>
       <c r="G121" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>140</v>
+        <v>324</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>272</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="F122" s="1"/>
       <c r="G122" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>281</v>
+        <v>325</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>288</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="F123" s="1"/>
       <c r="G123" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H123" s="3"/>
-    </row>
-    <row r="124" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>282</v>
+        <v>132</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C125" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="D125" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="E125" s="1" t="s">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H125" s="3"/>
     </row>
     <row r="126" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="C126" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D126" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="E126" s="1" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
     </row>
     <row r="127" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="C127" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="D127" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H127" s="3"/>
     </row>
-    <row r="128" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="C128" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="D128" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H128" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="129" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C129" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D129" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H129" s="3"/>
     </row>
-    <row r="130" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>286</v>
+        <v>327</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H130" s="3"/>
     </row>
     <row r="131" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>141</v>
+        <v>326</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="F131" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="G131" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H131" s="3" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H131" s="3"/>
+    </row>
+    <row r="132" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="F132" s="1"/>
+        <v>279</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>279</v>
+      </c>
       <c r="G132" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H132" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H132" s="3"/>
+    </row>
+    <row r="133" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>249</v>
+        <v>133</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="F133" s="1"/>
       <c r="G133" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="F134" s="1"/>
       <c r="G134" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="F135" s="1"/>
       <c r="G135" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="F136" s="1"/>
       <c r="G136" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>262</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="F137" s="1"/>
       <c r="G137" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="F138" s="1"/>
       <c r="G138" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="139" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="F139" s="1"/>
       <c r="G139" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>269</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="F140" s="1"/>
       <c r="G140" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="141" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>233</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="F141" s="1"/>
       <c r="G141" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F142" s="1"/>
+        <v>259</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>261</v>
+      </c>
       <c r="G142" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H143" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="H143" s="3" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="144" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="F144" s="1"/>
       <c r="G144" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>100</v>
+        <v>229</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>142</v>
+        <v>228</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H145" s="3"/>
     </row>
-    <row r="146" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>180</v>
+        <v>232</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>228</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="F146" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="G146" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="147" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>181</v>
+        <v>92</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>221</v>
+        <v>134</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>222</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H147" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H147" s="3"/>
+    </row>
+    <row r="148" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>226</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="F148" s="1"/>
       <c r="G148" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H148" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="149" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="E149" s="1"/>
-      <c r="F149" s="1"/>
+        <v>213</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>215</v>
+      </c>
       <c r="G149" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="F150" s="1"/>
+        <v>218</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>218</v>
+      </c>
       <c r="G150" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H150" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H150" s="3"/>
+    </row>
+    <row r="151" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="151" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A151" s="1">
-        <v>148</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>213</v>
-      </c>
+      <c r="E151" s="1"/>
       <c r="F151" s="1"/>
       <c r="G151" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H151" s="3" t="s">
         <v>212</v>
@@ -6256,389 +6397,437 @@
     </row>
     <row r="152" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="F152" s="1"/>
       <c r="G152" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="153" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F153" s="1"/>
       <c r="G153" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="154" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="F154" s="1"/>
       <c r="G154" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H154" s="3"/>
-    </row>
-    <row r="155" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H154" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>218</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="F155" s="1"/>
       <c r="G155" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H155" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H155" s="3" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="156" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>218</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="F156" s="1"/>
       <c r="G156" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H156" s="3"/>
     </row>
     <row r="157" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H157" s="3"/>
     </row>
-    <row r="158" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="C158" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D158" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="F158" s="1"/>
+        <v>210</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="G158" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H158" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H158" s="3"/>
+    </row>
+    <row r="159" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C159" s="1" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="159" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A159" s="1">
-        <v>156</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="D159" s="1" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F159" s="1"/>
+        <v>210</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="G159" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H159" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H159" s="3"/>
+    </row>
+    <row r="160" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="160" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A160" s="1">
-        <v>157</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="E160" s="1" t="s">
-        <v>128</v>
+        <v>194</v>
       </c>
       <c r="F160" s="1"/>
       <c r="G160" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H160" s="3"/>
-    </row>
-    <row r="161" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H160" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>101</v>
+        <v>182</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>143</v>
+        <v>197</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>175</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="F161" s="1"/>
       <c r="G161" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H161" s="3"/>
-    </row>
-    <row r="162" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>178</v>
+        <v>120</v>
       </c>
       <c r="F162" s="1"/>
       <c r="G162" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H162" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="H162" s="3"/>
+    </row>
+    <row r="163" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E163" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H163" s="3"/>
+    </row>
+    <row r="164" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F163" s="1"/>
-      <c r="G163" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H163" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="1">
-        <v>161</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="C164" s="1" t="s">
+      <c r="E164" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="F164" s="1"/>
       <c r="G164" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>656</v>
+        <v>171</v>
       </c>
     </row>
     <row r="165" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F165" s="1"/>
+      <c r="G165" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H165" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="C166" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G165" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H165" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A166" s="1">
+      <c r="D166" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="E166" s="1" t="s">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="F166" s="1"/>
       <c r="G166" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>602</v>
+        <v>666</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H167" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H167" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F168" s="1"/>
+      <c r="G168" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H168" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H169" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G167">
+  <conditionalFormatting sqref="G2:G169">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>

--- a/App/TestCases_App/User_admin.xlsx
+++ b/App/TestCases_App/User_admin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C6F3FD-8B46-4B4E-9C4A-E59502FA1AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61B70F6-F3B1-422D-9F63-1706AE21C0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="682">
   <si>
     <t>Num</t>
   </si>
@@ -1888,9 +1888,6 @@
     <t>1. The search is displayed</t>
   </si>
   <si>
-    <t>No hay tickets</t>
-  </si>
-  <si>
     <t>1.The user writes a world in the box of the search</t>
   </si>
   <si>
@@ -2144,20 +2141,11 @@
 Los botones no  van bien, tengo q pulsar varias veces "Siguiente" o "Anterior" para q respondan.</t>
   </si>
   <si>
-    <t>No se puede subir una imagen de una carta: MEN001.jpg
-Al desplegar el teclado, se tapa la funcionalidad: MEN003.jpg
-Parece q me guarda el menú pero cuando voy a consultarlo, ha desaparecido.
-Se produce un error al guardar el menú: MEN005.jpg,MEN006.jpg</t>
-  </si>
-  <si>
     <t>Aparece un mensaje de que "seleccione una serie de facturación" que no viene por ningún sitio: FAC002.jpg
 En el restaurante Gran Via, me ha permitido generar factura, pero hay errores: FAC005.jpg y FAC006.jpg</t>
   </si>
   <si>
     <t>1.The invoicing is created</t>
-  </si>
-  <si>
-    <t>1.The invoicing is not created</t>
   </si>
   <si>
     <t xml:space="preserve">1. Select numbers of people, clicks "Cancelar"
@@ -2312,6 +2300,34 @@
   </si>
   <si>
     <t>Views of tables: Take order, close table</t>
+  </si>
+  <si>
+    <t>No se puede subir una imagen de una carta: MEN001.jpg,MEN008.jpg
+Al desplegar el teclado, se tapa la funcionalidad: MEN003.jpg
+Parece q me guarda el menú pero cuando voy a consultarlo, ha desaparecido.
+Se produce un error al guardar el menú: MEN005.jpg,MEN006.jpg</t>
+  </si>
+  <si>
+    <t>Menus_types: scan</t>
+  </si>
+  <si>
+    <t>Aparece el error "Unathorized"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks "Escanear carta"
+2. Clicks "Seleccionar de galería", and selects a photo
+3. Clicks "Escanear carta"
+</t>
+  </si>
+  <si>
+    <t>1. The menu_type is scanned</t>
+  </si>
+  <si>
+    <t>Pte</t>
+  </si>
+  <si>
+    <t>No hay tickets
+15/05/26: El ticket practicamente no se ve, y ademas dice que el pago total de 13,80e está hecho con tarjeta, cuando parte esta hecho con tarjeta y parte con efectivo: HISTIC001.jpg</t>
   </si>
 </sst>
 </file>
@@ -2775,7 +2791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -2868,13 +2884,13 @@
         <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="2" t="s">
@@ -2898,7 +2914,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="2" t="s">
@@ -2916,13 +2932,13 @@
         <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="2" t="s">
@@ -2943,17 +2959,17 @@
         <v>565</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -2964,16 +2980,16 @@
         <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -2988,10 +3004,10 @@
         <v>35</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>21</v>
@@ -3012,20 +3028,20 @@
         <v>36</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3036,16 +3052,16 @@
         <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3063,7 +3079,7 @@
         <v>559</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
@@ -3087,7 +3103,7 @@
         <v>564</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>23</v>
@@ -3111,7 +3127,7 @@
         <v>560</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -3406,9 +3422,7 @@
       <c r="E26" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>122</v>
-      </c>
+      <c r="F26" s="1"/>
       <c r="G26" s="2" t="s">
         <v>8</v>
       </c>
@@ -3424,10 +3438,10 @@
         <v>77</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>576</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>577</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>571</v>
@@ -3440,7 +3454,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -3454,10 +3468,10 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>572</v>
+        <v>681</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3473,7 +3487,7 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>127</v>
@@ -3493,9 +3507,9 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3510,17 +3524,17 @@
         <v>129</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>641</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>642</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3542,7 +3556,7 @@
         <v>8</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3559,10 +3573,10 @@
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3579,16 +3593,14 @@
         <v>144</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>649</v>
-      </c>
+        <v>646</v>
+      </c>
+      <c r="F34" s="1"/>
       <c r="G34" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3607,7 +3619,7 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>159</v>
@@ -3746,7 +3758,7 @@
         <v>8</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3757,7 +3769,7 @@
         <v>450</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>156</v>
@@ -3768,7 +3780,7 @@
         <v>8</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
@@ -3779,20 +3791,20 @@
         <v>451</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="E43" s="1" t="s">
         <v>636</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>637</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3803,10 +3815,10 @@
         <v>452</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>639</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>120</v>
@@ -3827,10 +3839,10 @@
         <v>453</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -3838,7 +3850,7 @@
         <v>8</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3849,10 +3861,10 @@
         <v>103</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -3860,7 +3872,7 @@
         <v>8</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3879,7 +3891,7 @@
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="2" t="s">
-        <v>13</v>
+        <v>680</v>
       </c>
       <c r="H47" s="7" t="s">
         <v>447</v>
@@ -3896,13 +3908,13 @@
         <v>443</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="F48" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>13</v>
@@ -3920,13 +3932,13 @@
         <v>444</v>
       </c>
       <c r="D49" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="F49" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>13</v>
@@ -3941,13 +3953,13 @@
         <v>107</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="2" t="s">
@@ -3965,10 +3977,10 @@
         <v>108</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>120</v>
@@ -3988,20 +4000,20 @@
         <v>109</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>606</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4012,10 +4024,10 @@
         <v>110</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>120</v>
@@ -4034,13 +4046,13 @@
         <v>454</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>633</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>634</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="2" t="s">
@@ -4058,20 +4070,20 @@
         <v>111</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -4082,20 +4094,20 @@
         <v>112</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>646</v>
+        <v>675</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4106,10 +4118,10 @@
         <v>455</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>120</v>
@@ -4124,70 +4136,70 @@
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>113</v>
+        <v>455</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>614</v>
+        <v>676</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>625</v>
+        <v>678</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>616</v>
+        <v>679</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="F59" s="1"/>
       <c r="G59" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H59" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>644</v>
+      </c>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>630</v>
+        <v>120</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>630</v>
+        <v>120</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>13</v>
@@ -4196,22 +4208,22 @@
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>628</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>120</v>
+        <v>629</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>120</v>
+        <v>629</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>13</v>
@@ -4220,89 +4232,89 @@
     </row>
     <row r="62" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
+        <v>60</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H62" s="3"/>
+    </row>
+    <row r="63" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
         <v>61</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="D62" s="1" t="s">
+      <c r="C63" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
+      <c r="D63" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
         <v>62</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H63" s="3"/>
-    </row>
-    <row r="64" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H64" s="3"/>
+    </row>
+    <row r="65" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
         <v>63</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D65" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H64" s="3"/>
-    </row>
-    <row r="65" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
-        <v>64</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="F65" s="1" t="s">
-        <v>120</v>
+        <v>592</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>13</v>
@@ -4311,22 +4323,22 @@
     </row>
     <row r="66" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>595</v>
+        <v>120</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>595</v>
+        <v>120</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>13</v>
@@ -4335,22 +4347,22 @@
     </row>
     <row r="67" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>277</v>
+        <v>595</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>120</v>
+        <v>594</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>120</v>
+        <v>594</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>13</v>
@@ -4359,22 +4371,22 @@
     </row>
     <row r="68" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>598</v>
+        <v>277</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>599</v>
+        <v>120</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>599</v>
+        <v>120</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>13</v>
@@ -4383,64 +4395,64 @@
     </row>
     <row r="69" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>597</v>
       </c>
       <c r="E69" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" s="3"/>
+    </row>
+    <row r="70" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>68</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F70" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G69" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H69" s="3"/>
-    </row>
-    <row r="70" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
-        <v>69</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="F70" s="1"/>
       <c r="G70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>415</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H70" s="3"/>
     </row>
     <row r="71" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>406</v>
@@ -4450,51 +4462,51 @@
         <v>8</v>
       </c>
       <c r="H71" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>70</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="F72" s="1"/>
+      <c r="G72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
-        <v>71</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H72" s="3"/>
     </row>
     <row r="73" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>399</v>
+        <v>626</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>13</v>
@@ -4503,22 +4515,22 @@
     </row>
     <row r="74" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>13</v>
@@ -4527,64 +4539,64 @@
     </row>
     <row r="75" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
+        <v>73</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H75" s="3"/>
+    </row>
+    <row r="76" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
         <v>74</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C76" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D76" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E76" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="F75" s="1"/>
-      <c r="G75" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
-        <v>75</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>418</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
     </row>
     <row r="77" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>418</v>
@@ -4594,219 +4606,219 @@
         <v>8</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="78" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
+        <v>76</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="F78" s="1"/>
+      <c r="G78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
         <v>77</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D79" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="E79" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F79" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G78" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H78" s="3"/>
-    </row>
-    <row r="79" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
+      <c r="G79" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H79" s="3"/>
+    </row>
+    <row r="80" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
         <v>78</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D80" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="E80" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="F80" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="G79" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H79" s="3"/>
-    </row>
-    <row r="80" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
+      <c r="G80" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H80" s="3"/>
+    </row>
+    <row r="81" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
         <v>79</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E81" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F81" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H80" s="3"/>
-    </row>
-    <row r="81" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
+      <c r="G81" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H81" s="3"/>
+    </row>
+    <row r="82" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
         <v>80</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D82" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E82" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="F81" s="1"/>
-      <c r="G81" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
-        <v>81</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>387</v>
       </c>
       <c r="F82" s="1"/>
       <c r="G82" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F83" s="1"/>
       <c r="G83" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H83" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>82</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="F84" s="1"/>
+      <c r="G84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H84" s="3" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="84" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
+    <row r="85" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
         <v>83</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D85" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E85" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="F85" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G84" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H84" s="3"/>
-    </row>
-    <row r="85" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
+      <c r="G85" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H85" s="3"/>
+    </row>
+    <row r="86" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
         <v>84</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B86" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D86" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E86" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="F86" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H85" s="3"/>
-    </row>
-    <row r="86" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
-        <v>85</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>13</v>
@@ -4815,22 +4827,22 @@
     </row>
     <row r="87" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>390</v>
+        <v>120</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>390</v>
+        <v>120</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>13</v>
@@ -4839,46 +4851,46 @@
     </row>
     <row r="88" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
+        <v>86</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H88" s="3"/>
+    </row>
+    <row r="89" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
         <v>87</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D89" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E89" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="F89" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H88" s="3"/>
-    </row>
-    <row r="89" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
-        <v>88</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>13</v>
@@ -4887,22 +4899,22 @@
     </row>
     <row r="90" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>394</v>
+        <v>278</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>395</v>
+        <v>279</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>395</v>
+        <v>279</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>13</v>
@@ -4911,168 +4923,168 @@
     </row>
     <row r="91" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
+        <v>89</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H91" s="3"/>
+    </row>
+    <row r="92" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
         <v>90</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B92" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C92" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D92" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E92" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="F92" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="G91" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H91" s="3" t="s">
+      <c r="G92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H92" s="3" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="92" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
+    <row r="93" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
         <v>91</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B93" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E93" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="F92" s="1"/>
-      <c r="G92" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
-        <v>92</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>349</v>
       </c>
       <c r="F93" s="1"/>
       <c r="G93" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H93" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>92</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="F94" s="1"/>
+      <c r="G94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="94" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
+    <row r="95" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
         <v>93</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="D95" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="E95" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F94" s="1" t="s">
+      <c r="F95" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G94" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H94" s="3"/>
-    </row>
-    <row r="95" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
+      <c r="G95" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H95" s="3"/>
+    </row>
+    <row r="96" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
         <v>94</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B96" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D96" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="E96" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="F95" s="1"/>
-      <c r="G95" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H95" s="3" t="s">
+      <c r="F96" s="1"/>
+      <c r="G96" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
-        <v>95</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H96" s="3"/>
     </row>
     <row r="97" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>354</v>
+        <v>120</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>354</v>
+        <v>120</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>13</v>
@@ -5081,338 +5093,338 @@
     </row>
     <row r="98" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
+        <v>96</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H98" s="3"/>
+    </row>
+    <row r="99" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
         <v>97</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B99" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C99" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D99" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E99" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F98" s="1" t="s">
+      <c r="F99" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G98" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H98" s="3"/>
-    </row>
-    <row r="99" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
+      <c r="G99" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H99" s="3"/>
+    </row>
+    <row r="100" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
         <v>98</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B100" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C100" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="D100" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="E100" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="F99" s="1"/>
-      <c r="G99" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A100" s="1">
-        <v>99</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>361</v>
       </c>
       <c r="F100" s="1"/>
       <c r="G100" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="101" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F101" s="1"/>
       <c r="G101" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
     </row>
     <row r="102" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F102" s="1"/>
       <c r="G102" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H102" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>101</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="F103" s="1"/>
+      <c r="G103" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H103" s="3" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="103" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="1">
+    <row r="104" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
         <v>102</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B104" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C104" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="D104" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="E104" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="F103" s="1" t="s">
+      <c r="F104" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="G103" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H103" s="3" t="s">
+      <c r="G104" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H104" s="3" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A104" s="1">
-        <v>103</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F104" s="1"/>
-      <c r="G104" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H104" s="3"/>
     </row>
     <row r="105" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="F105" s="1"/>
       <c r="G105" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H105" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H105" s="3"/>
+    </row>
+    <row r="106" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>104</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="F106" s="1"/>
+      <c r="G106" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H106" s="3" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="106" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A106" s="1">
+    <row r="107" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
         <v>105</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B107" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C107" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="D107" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="E106" s="1" t="s">
+      <c r="E107" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F106" s="1" t="s">
+      <c r="F107" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G106" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H106" s="3"/>
-    </row>
-    <row r="107" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A107" s="1">
+      <c r="G107" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H107" s="3"/>
+    </row>
+    <row r="108" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
         <v>106</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B108" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C108" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="D108" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E107" s="1" t="s">
+      <c r="E108" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="F107" s="1" t="s">
+      <c r="F108" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="G107" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H107" s="3" t="s">
+      <c r="G108" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H108" s="3" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A108" s="1">
-        <v>107</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H108" s="3"/>
     </row>
     <row r="109" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>318</v>
+        <v>120</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>318</v>
+        <v>120</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H109" s="3" t="s">
-        <v>591</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H109" s="3"/>
     </row>
     <row r="110" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
+        <v>108</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
         <v>109</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B111" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C111" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="D111" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="E110" s="1" t="s">
+      <c r="E111" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F110" s="1" t="s">
+      <c r="F111" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H110" s="3"/>
-    </row>
-    <row r="111" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="1">
-        <v>110</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>13</v>
@@ -5421,142 +5433,142 @@
     </row>
     <row r="112" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
+        <v>110</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H112" s="3"/>
+    </row>
+    <row r="113" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
         <v>111</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B113" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C113" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="D113" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E112" s="1" t="s">
+      <c r="E113" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="F112" s="1" t="s">
+      <c r="F113" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="G112" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H112" s="3" t="s">
+      <c r="G113" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H113" s="3" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="113" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A113" s="1">
-        <v>112</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H113" s="3"/>
     </row>
     <row r="114" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="F114" s="1"/>
+      <c r="F114" s="1" t="s">
+        <v>323</v>
+      </c>
       <c r="G114" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H114" s="3"/>
     </row>
-    <row r="115" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
+        <v>113</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F115" s="1"/>
+      <c r="G115" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H115" s="3"/>
+    </row>
+    <row r="116" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
         <v>114</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B116" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C116" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="D116" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F115" s="1" t="s">
+      <c r="F116" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G115" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H115" s="3"/>
-    </row>
-    <row r="116" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A116" s="1">
+      <c r="G116" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H116" s="3"/>
+    </row>
+    <row r="117" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
         <v>115</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B117" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C117" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="D117" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="E117" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="F116" s="1" t="s">
+      <c r="F117" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H116" s="3"/>
-    </row>
-    <row r="117" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A117" s="1">
-        <v>116</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>13</v>
@@ -5565,22 +5577,22 @@
     </row>
     <row r="118" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>322</v>
+        <v>120</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>322</v>
+        <v>120</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>13</v>
@@ -5589,190 +5601,190 @@
     </row>
     <row r="119" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
+        <v>117</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H119" s="3"/>
+    </row>
+    <row r="120" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
         <v>118</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B120" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C120" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="D120" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="E119" s="1" t="s">
+      <c r="E120" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F119" s="1" t="s">
+      <c r="F120" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G119" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H119" s="3">
+      <c r="G120" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H120" s="3">
         <v>702</v>
       </c>
     </row>
-    <row r="120" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A120" s="1">
+    <row r="121" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
         <v>119</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B121" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C121" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="D121" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="E120" s="1" t="s">
+      <c r="E121" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="F120" s="1" t="s">
+      <c r="F121" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G120" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H120" s="3" t="s">
+      <c r="G121" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H121" s="3" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="121" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A121" s="1">
+    <row r="122" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
         <v>120</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B122" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C122" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="D122" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E121" s="1" t="s">
+      <c r="E122" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="F121" s="1"/>
-      <c r="G121" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A122" s="1">
-        <v>121</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>323</v>
       </c>
       <c r="F122" s="1"/>
       <c r="G122" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F123" s="1"/>
       <c r="G123" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H123" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>122</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="F124" s="1"/>
+      <c r="G124" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H124" s="3" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="124" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="1">
+    <row r="125" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
         <v>123</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B125" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C125" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="D125" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E124" s="1" t="s">
+      <c r="E125" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F124" s="1" t="s">
+      <c r="F125" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="G124" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H124" s="3" t="s">
+      <c r="G125" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H125" s="3" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="125" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A125" s="1">
-        <v>124</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H125" s="3"/>
     </row>
     <row r="126" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>280</v>
@@ -5781,104 +5793,104 @@
         <v>280</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H126" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H126" s="3"/>
+    </row>
+    <row r="127" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>125</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H127" s="3" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="127" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A127" s="1">
+    <row r="128" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
         <v>126</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B128" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C128" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D128" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="E127" s="1" t="s">
+      <c r="E128" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F127" s="1" t="s">
+      <c r="F128" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G127" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H127" s="3"/>
-    </row>
-    <row r="128" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A128" s="1">
+      <c r="G128" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H128" s="3"/>
+    </row>
+    <row r="129" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
         <v>127</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B129" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="C129" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="D129" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="E128" s="1" t="s">
+      <c r="E129" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="F128" s="1" t="s">
+      <c r="F129" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="G128" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H128" s="3" t="s">
+      <c r="G129" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H129" s="3" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="129" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A129" s="1">
-        <v>128</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G129" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H129" s="3"/>
     </row>
     <row r="130" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>283</v>
+        <v>120</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>283</v>
+        <v>120</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>13</v>
@@ -5887,139 +5899,139 @@
     </row>
     <row r="131" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
+        <v>129</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H131" s="3"/>
+    </row>
+    <row r="132" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
         <v>130</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B132" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="C132" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="D132" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="E131" s="1" t="s">
+      <c r="E132" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F131" s="1" t="s">
+      <c r="F132" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G131" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H131" s="3"/>
-    </row>
-    <row r="132" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="1">
+      <c r="G132" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H132" s="3"/>
+    </row>
+    <row r="133" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
         <v>131</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="B133" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="C133" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="D133" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="E132" s="1" t="s">
+      <c r="E133" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="F132" s="1" t="s">
+      <c r="F133" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G132" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H132" s="3"/>
-    </row>
-    <row r="133" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A133" s="1">
-        <v>132</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F133" s="1"/>
       <c r="G133" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H133" s="3" t="s">
-        <v>371</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H133" s="3"/>
     </row>
     <row r="134" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
+        <v>132</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="E134" s="1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="F134" s="1"/>
       <c r="G134" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F135" s="1"/>
       <c r="G135" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
     </row>
     <row r="136" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="F136" s="1"/>
       <c r="G136" s="2" t="s">
@@ -6029,21 +6041,21 @@
         <v>256</v>
       </c>
     </row>
-    <row r="137" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F137" s="1"/>
       <c r="G137" s="2" t="s">
@@ -6055,19 +6067,19 @@
     </row>
     <row r="138" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F138" s="1"/>
       <c r="G138" s="2" t="s">
@@ -6077,21 +6089,21 @@
         <v>256</v>
       </c>
     </row>
-    <row r="139" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F139" s="1"/>
       <c r="G139" s="2" t="s">
@@ -6103,19 +6115,19 @@
     </row>
     <row r="140" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="F140" s="1"/>
       <c r="G140" s="2" t="s">
@@ -6127,19 +6139,19 @@
     </row>
     <row r="141" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="F141" s="1"/>
       <c r="G141" s="2" t="s">
@@ -6149,25 +6161,23 @@
         <v>256</v>
       </c>
     </row>
-    <row r="142" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="F142" s="1" t="s">
-        <v>261</v>
-      </c>
+      <c r="F142" s="1"/>
       <c r="G142" s="2" t="s">
         <v>14</v>
       </c>
@@ -6175,89 +6185,91 @@
         <v>256</v>
       </c>
     </row>
-    <row r="143" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>225</v>
+        <v>259</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H143" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>142</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H144" s="3" t="s">
         <v>373</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A144" s="1">
-        <v>143</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="F144" s="1"/>
-      <c r="G144" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H144" s="3" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="145" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="F145" s="1"/>
       <c r="G145" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H145" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H145" s="3" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="146" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>228</v>
@@ -6269,269 +6281,269 @@
         <v>120</v>
       </c>
       <c r="G146" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H146" s="3"/>
+    </row>
+    <row r="147" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
+        <v>145</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G147" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H146" s="3" t="s">
+      <c r="H147" s="3" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="147" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="1">
+    <row r="148" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
         <v>146</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="B148" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="C148" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="D148" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E147" s="1" t="s">
+      <c r="E148" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="F147" s="1" t="s">
+      <c r="F148" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="G147" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H147" s="3"/>
-    </row>
-    <row r="148" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A148" s="1">
+      <c r="G148" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H148" s="3"/>
+    </row>
+    <row r="149" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
         <v>147</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="B149" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="C149" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D148" s="1" t="s">
+      <c r="D149" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E148" s="1" t="s">
+      <c r="E149" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="F148" s="1"/>
-      <c r="G148" s="2" t="s">
+      <c r="F149" s="1"/>
+      <c r="G149" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H148" s="3" t="s">
+      <c r="H149" s="3" t="s">
         <v>219</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="1">
-        <v>148</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="G149" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H149" s="3" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="150" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H150" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H150" s="3" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="151" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
+        <v>149</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H151" s="3"/>
+    </row>
+    <row r="152" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
         <v>150</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="B152" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="C152" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D151" s="1" t="s">
+      <c r="D152" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E151" s="1"/>
-      <c r="F151" s="1"/>
-      <c r="G151" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H151" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A152" s="1">
-        <v>151</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>202</v>
-      </c>
+      <c r="E152" s="1"/>
       <c r="F152" s="1"/>
       <c r="G152" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F153" s="1"/>
       <c r="G153" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F154" s="1"/>
       <c r="G154" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="F155" s="1"/>
       <c r="G155" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="F156" s="1"/>
       <c r="G156" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H156" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H156" s="3" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="157" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>210</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="F157" s="1"/>
       <c r="G157" s="2" t="s">
         <v>13</v>
       </c>
@@ -6539,16 +6551,16 @@
     </row>
     <row r="158" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>210</v>
@@ -6563,16 +6575,16 @@
     </row>
     <row r="159" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>210</v>
@@ -6585,249 +6597,273 @@
       </c>
       <c r="H159" s="3"/>
     </row>
-    <row r="160" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
+        <v>158</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H160" s="3"/>
+    </row>
+    <row r="161" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
         <v>159</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="B161" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="C161" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D160" s="1" t="s">
+      <c r="D161" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E160" s="1" t="s">
+      <c r="E161" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="F160" s="1"/>
-      <c r="G160" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H160" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A161" s="1">
-        <v>160</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="F161" s="1"/>
       <c r="G161" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="162" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="F162" s="1"/>
       <c r="G162" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
+        <v>161</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F163" s="1"/>
+      <c r="G163" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H162" s="3"/>
-    </row>
-    <row r="163" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="1">
+      <c r="H163" s="3"/>
+    </row>
+    <row r="164" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
         <v>162</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="C163" s="1" t="s">
+      <c r="B164" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="C164" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D163" s="1" t="s">
+      <c r="D164" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E163" s="1" t="s">
+      <c r="E164" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F163" s="1" t="s">
+      <c r="F164" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="G163" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H163" s="3"/>
-    </row>
-    <row r="164" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A164" s="1">
-        <v>163</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F164" s="1"/>
       <c r="G164" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H164" s="3" t="s">
-        <v>171</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H164" s="3"/>
     </row>
     <row r="165" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="F165" s="1"/>
       <c r="G165" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>665</v>
+        <v>589</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>162</v>
+        <v>94</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F166" s="1"/>
       <c r="G166" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
+        <v>165</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F167" s="1"/>
+      <c r="G167" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H167" s="3" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
         <v>166</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="C167" s="1" t="s">
+      <c r="B168" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="C168" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D167" s="1" t="s">
+      <c r="D168" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E167" s="1" t="s">
+      <c r="E168" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F167" s="1" t="s">
+      <c r="F168" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G167" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H167" s="3" t="s">
+      <c r="G168" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H168" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="168" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A168" s="1">
+    <row r="169" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
         <v>167</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="C168" s="1" t="s">
+      <c r="B169" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="C169" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D168" s="1" t="s">
+      <c r="D169" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E168" s="1" t="s">
+      <c r="E169" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F168" s="1"/>
-      <c r="G168" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H168" s="3" t="s">
+      <c r="F169" s="1"/>
+      <c r="G169" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H169" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="169" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="1">
+    <row r="170" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
         <v>168</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="C169" s="1" t="s">
+      <c r="B170" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="C170" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D169" s="1" t="s">
+      <c r="D170" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E169" s="1" t="s">
+      <c r="E170" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F169" s="1" t="s">
+      <c r="F170" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G169" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H169" s="3"/>
+      <c r="G170" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H170" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G169">
+  <conditionalFormatting sqref="G2:G170">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>

--- a/App/TestCases_App/User_admin.xlsx
+++ b/App/TestCases_App/User_admin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61B70F6-F3B1-422D-9F63-1706AE21C0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74648248-8637-41C9-A243-79082D307A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1888,9 +1888,6 @@
     <t>1. The search is displayed</t>
   </si>
   <si>
-    <t>1.The user writes a world in the box of the search</t>
-  </si>
-  <si>
     <t>Menus_types: search</t>
   </si>
   <si>
@@ -2006,9 +2003,6 @@
     <t>1. The user sees the menu_type</t>
   </si>
   <si>
-    <t>Se edita la carta, no se ve solo</t>
-  </si>
-  <si>
     <t>1.The user clicks eye icon (carta personalizada)
 2. Clicks "Cancelar"</t>
   </si>
@@ -2203,11 +2197,6 @@
     <t>1. Select numbers of people
 2. Select several products
 3. Add fee</t>
-  </si>
-  <si>
-    <t>1. Select numbers of people
-2. Select several products with his modifiers
-3. Select menu</t>
   </si>
   <si>
     <t>1. Select numbers of people, clicks "Aceptar"
@@ -2283,12 +2272,6 @@
     <t>1. The product is added.</t>
   </si>
   <si>
-    <t>No veo variación al cambiar de menú</t>
-  </si>
-  <si>
-    <t>1. The products shown are the menu's product.</t>
-  </si>
-  <si>
     <t>The fee is added</t>
   </si>
   <si>
@@ -2328,6 +2311,25 @@
   <si>
     <t>No hay tickets
 15/05/26: El ticket practicamente no se ve, y ademas dice que el pago total de 13,80e está hecho con tarjeta, cuando parte esta hecho con tarjeta y parte con efectivo: HISTIC001.jpg</t>
+  </si>
+  <si>
+    <t>1. The user writes a world in the box of the search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se edita la carta, no se ve solo
+</t>
+  </si>
+  <si>
+    <t>No veo variación al cambiar de menú
+18/05/26: El menú desplegable, donde escoges "CARTA", se ha quedado vacio sin carta: MEN007.jpg</t>
+  </si>
+  <si>
+    <t>1. The menu is selected.</t>
+  </si>
+  <si>
+    <t>1. Select numbers of people
+2. Select several products with his modifiers
+3. Select menu (button "CARTA")</t>
   </si>
 </sst>
 </file>
@@ -2884,13 +2886,13 @@
         <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="2" t="s">
@@ -2914,7 +2916,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="2" t="s">
@@ -2932,13 +2934,13 @@
         <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>666</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>671</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="2" t="s">
@@ -2959,17 +2961,17 @@
         <v>565</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>660</v>
+        <v>681</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -2980,16 +2982,16 @@
         <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3004,10 +3006,10 @@
         <v>35</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>21</v>
@@ -3028,20 +3030,20 @@
         <v>36</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3052,16 +3054,16 @@
         <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3079,7 +3081,7 @@
         <v>559</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
@@ -3103,7 +3105,7 @@
         <v>564</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>23</v>
@@ -3127,7 +3129,7 @@
         <v>560</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -3438,10 +3440,10 @@
         <v>77</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>575</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>576</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>571</v>
@@ -3471,7 +3473,7 @@
         <v>8</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3524,17 +3526,17 @@
         <v>129</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3556,7 +3558,7 @@
         <v>8</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3576,7 +3578,7 @@
         <v>8</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3593,14 +3595,14 @@
         <v>144</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3758,7 +3760,7 @@
         <v>8</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3769,7 +3771,7 @@
         <v>450</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>156</v>
@@ -3780,7 +3782,7 @@
         <v>8</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
@@ -3791,20 +3793,20 @@
         <v>451</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>634</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>636</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3815,10 +3817,10 @@
         <v>452</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>120</v>
@@ -3839,10 +3841,10 @@
         <v>453</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -3850,7 +3852,7 @@
         <v>8</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3861,10 +3863,10 @@
         <v>103</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -3872,7 +3874,7 @@
         <v>8</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3891,7 +3893,7 @@
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="2" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="H47" s="7" t="s">
         <v>447</v>
@@ -3908,13 +3910,13 @@
         <v>443</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="F48" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>13</v>
@@ -3932,13 +3934,13 @@
         <v>444</v>
       </c>
       <c r="D49" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="F49" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>13</v>
@@ -3953,13 +3955,13 @@
         <v>107</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="2" t="s">
@@ -3977,10 +3979,10 @@
         <v>108</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>120</v>
@@ -4000,20 +4002,20 @@
         <v>109</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>605</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>606</v>
+        <v>678</v>
       </c>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4024,10 +4026,10 @@
         <v>110</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>120</v>
@@ -4046,13 +4048,13 @@
         <v>454</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="2" t="s">
@@ -4070,20 +4072,20 @@
         <v>111</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -4094,20 +4096,20 @@
         <v>112</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4118,10 +4120,10 @@
         <v>455</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>120</v>
@@ -4142,20 +4144,20 @@
         <v>455</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -4166,20 +4168,20 @@
         <v>113</v>
       </c>
       <c r="C59" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>615</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4190,10 +4192,10 @@
         <v>114</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>120</v>
@@ -4214,16 +4216,16 @@
         <v>115</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>13</v>
@@ -4238,10 +4240,10 @@
         <v>116</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>120</v>
@@ -4262,16 +4264,16 @@
         <v>117</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>572</v>
+        <v>677</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>13</v>
@@ -4308,13 +4310,13 @@
         <v>434</v>
       </c>
       <c r="D65" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>592</v>
-      </c>
       <c r="F65" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>13</v>
@@ -4332,7 +4334,7 @@
         <v>440</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>120</v>
@@ -4356,13 +4358,13 @@
         <v>436</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>13</v>
@@ -4404,13 +4406,13 @@
         <v>437</v>
       </c>
       <c r="D69" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>598</v>
-      </c>
       <c r="F69" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>13</v>
@@ -4428,7 +4430,7 @@
         <v>442</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>120</v>
@@ -4500,7 +4502,7 @@
         <v>405</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>120</v>
@@ -5404,7 +5406,7 @@
         <v>8</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="111" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6696,7 +6698,7 @@
         <v>162</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>93</v>
@@ -6720,7 +6722,7 @@
         <v>163</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>168</v>
@@ -6744,7 +6746,7 @@
         <v>164</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>94</v>
@@ -6768,7 +6770,7 @@
         <v>165</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>162</v>
@@ -6784,7 +6786,7 @@
         <v>8</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="168" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6792,7 +6794,7 @@
         <v>166</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>45</v>
@@ -6818,7 +6820,7 @@
         <v>167</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>50</v>
@@ -6842,7 +6844,7 @@
         <v>168</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>53</v>

--- a/App/TestCases_App/User_admin.xlsx
+++ b/App/TestCases_App/User_admin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74648248-8637-41C9-A243-79082D307A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09466A4B-1FC1-458E-AD3A-9D2F50D9557C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="692">
   <si>
     <t>Num</t>
   </si>
@@ -196,9 +196,6 @@
     <t>1. The "pending task" page is not correctly.</t>
   </si>
   <si>
-    <t>Error al consultar tareas pendientes: maitre004.jpg y maitre005.jpg</t>
-  </si>
-  <si>
     <t>Pending tasks: synchronize</t>
   </si>
   <si>
@@ -213,12 +210,6 @@
     <t>Change user</t>
   </si>
   <si>
-    <t>1. The user clicks "Cambiar de usuario"</t>
-  </si>
-  <si>
-    <t>1. The operation is done</t>
-  </si>
-  <si>
     <t>USERADM016</t>
   </si>
   <si>
@@ -259,18 +250,10 @@
     <t>Cash closing's history: See</t>
   </si>
   <si>
-    <t xml:space="preserve">1. The user sees a cash closing's
-</t>
-  </si>
-  <si>
     <t>1. The cash closing is shown.</t>
   </si>
   <si>
     <t>Cash closing's history: Print</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. The user prints a cash closing's
-</t>
   </si>
   <si>
     <t>1. The cash closing is printed.</t>
@@ -581,9 +564,6 @@
   </si>
   <si>
     <t>No es posible cambiarse de plan, sale el mensaje: "Para contratar el plan XXX, contacta con soporte.</t>
-  </si>
-  <si>
-    <t>Aparece una pantalla con errores, que además no se puede cerrar: sin001.jpg</t>
   </si>
   <si>
     <t>1. The backups page is correctly</t>
@@ -1196,11 +1176,6 @@
     <t>1. The categorie is deleted.</t>
   </si>
   <si>
-    <t xml:space="preserve">No se indican los campos obligatorios y al pulsar "Crear" no hace nada. 
-La imagen del teclado impide ver el resto de la funcionalidad: CATEG004.jpg
-</t>
-  </si>
-  <si>
     <t>Se busca el número 6, pero la búsqueda no es correcta, para que encuentre el resultado, hay q introducir un espacio delante, algo q no debería ser necesario:CATEG005.jpg</t>
   </si>
   <si>
@@ -1266,9 +1241,6 @@
   <si>
     <t xml:space="preserve">1. The user clicks the garbage icon of a rol
 </t>
-  </si>
-  <si>
-    <t>Debería de preguntar si se quiere modificar y permitir cancelar.</t>
   </si>
   <si>
     <t>Debería de preguntar si se quiere borrar y permitir cancelar.</t>
@@ -2217,6 +2189,123 @@
   </si>
   <si>
     <t>Views of tables:Take order,Fee</t>
+  </si>
+  <si>
+    <t>1. The product is added.</t>
+  </si>
+  <si>
+    <t>The fee is added</t>
+  </si>
+  <si>
+    <t>The tables are joined.</t>
+  </si>
+  <si>
+    <t>1. Select numbers of people
+2. Clicks "Cerrar mesa"</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order, close table</t>
+  </si>
+  <si>
+    <t>No se puede subir una imagen de una carta: MEN001.jpg,MEN008.jpg
+Al desplegar el teclado, se tapa la funcionalidad: MEN003.jpg
+Parece q me guarda el menú pero cuando voy a consultarlo, ha desaparecido.
+Se produce un error al guardar el menú: MEN005.jpg,MEN006.jpg</t>
+  </si>
+  <si>
+    <t>Menus_types: scan</t>
+  </si>
+  <si>
+    <t>Aparece el error "Unathorized"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks "Escanear carta"
+2. Clicks "Seleccionar de galería", and selects a photo
+3. Clicks "Escanear carta"
+</t>
+  </si>
+  <si>
+    <t>1. The menu_type is scanned</t>
+  </si>
+  <si>
+    <t>Pte</t>
+  </si>
+  <si>
+    <t>No hay tickets
+15/05/26: El ticket practicamente no se ve, y ademas dice que el pago total de 13,80e está hecho con tarjeta, cuando parte esta hecho con tarjeta y parte con efectivo: HISTIC001.jpg</t>
+  </si>
+  <si>
+    <t>1. The user writes a world in the box of the search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se edita la carta, no se ve solo
+</t>
+  </si>
+  <si>
+    <t>No veo variación al cambiar de menú
+18/05/26: El menú desplegable, donde escoges "CARTA", se ha quedado vacio sin carta: MEN007.jpg</t>
+  </si>
+  <si>
+    <t>1. The menu is selected.</t>
+  </si>
+  <si>
+    <t>1. Select numbers of people
+2. Select several products with his modifiers
+3. Select menu (button "CARTA")</t>
+  </si>
+  <si>
+    <t>Change restaurant</t>
+  </si>
+  <si>
+    <t>USERADM169</t>
+  </si>
+  <si>
+    <t>USERADM170</t>
+  </si>
+  <si>
+    <t>1. The user is changed</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Cambiar de usuario"
+2. Click on the back arrow
+3. Select restuarant
+4. Select another user
+5. Write the password
+6. Clicks "Acceder"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Cambiar de usuario"
+2. Select another user
+3. Write the password
+4. Clicks "Acceder"</t>
+  </si>
+  <si>
+    <t>1. The restaurant is changed</t>
+  </si>
+  <si>
+    <t>Error al consultar tareas pendientes: maitre004.jpg y maitre005.jpg
+20/05/26: Solo aparace una tarea para sincronizar, pero al hacerlo indica: FAILED. Se queda siempre en este estado.</t>
+  </si>
+  <si>
+    <t>Aparece una pantalla con errores, que además no se puede cerrar: sin001.jpg
+20/05/26: Parece que sincroniza pero siempre queda la tarea a Faled, caso anterior.</t>
+  </si>
+  <si>
+    <t>Views of tables: Take order, promo</t>
+  </si>
+  <si>
+    <t>1. The pay is correctly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Select numbers of people (eg.promo 4x3)
+2. Select products
+3. Clicks "Realizar pago"
+4. Split payment
+</t>
+  </si>
+  <si>
+    <t>Pago incorrecto. Una promoción es aplicada (4x3), pero al dividir la cuenta entre seis, la promoción se pierde : PROMO009.jpg ,PROMO010.jpg, PROMO011.jpg
+Una comida de 80, con una promo (4x3) le quita 20. 60 a pagar, se divide entre 3 y hace un pago, quedan 40, se retrocede y se vuelve, se ha perdidoel calculo correcto:PROMO012.jpg</t>
   </si>
   <si>
     <r>
@@ -2265,71 +2354,34 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: PED002.jgp, PED003.jpg</t>
+      <t>: PED002.jgp, PED003.jpg
+22/05/26: En la pantalla de modificadores, aparece, "Grupos disponibles:xxxx" no entiendo el sentido de esa información:MES004.jpg
+22/05/26 HA añadido un suplemento de 0,01 cts que no se de donde ha salido: MES005.jpg</t>
     </r>
   </si>
   <si>
-    <t>1. The product is added.</t>
-  </si>
-  <si>
-    <t>The fee is added</t>
-  </si>
-  <si>
-    <t>The tables are joined.</t>
-  </si>
-  <si>
-    <t>1. Select numbers of people
-2. Clicks "Cerrar mesa"</t>
-  </si>
-  <si>
-    <t>Views of tables: Take order, close table</t>
-  </si>
-  <si>
-    <t>No se puede subir una imagen de una carta: MEN001.jpg,MEN008.jpg
-Al desplegar el teclado, se tapa la funcionalidad: MEN003.jpg
-Parece q me guarda el menú pero cuando voy a consultarlo, ha desaparecido.
-Se produce un error al guardar el menú: MEN005.jpg,MEN006.jpg</t>
-  </si>
-  <si>
-    <t>Menus_types: scan</t>
-  </si>
-  <si>
-    <t>Aparece el error "Unathorized"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. The user clicks "Escanear carta"
-2. Clicks "Seleccionar de galería", and selects a photo
-3. Clicks "Escanear carta"
+    <t>En vez de indicar "Tarjeta" como en Web, muestra "CARD", aunque casi ni se ve: HISCIE001.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user sees a cash closing's
+2. Select one
+3.  Clicks the "i" icon
 </t>
   </si>
   <si>
-    <t>1. The menu_type is scanned</t>
-  </si>
-  <si>
-    <t>Pte</t>
-  </si>
-  <si>
-    <t>No hay tickets
-15/05/26: El ticket practicamente no se ve, y ademas dice que el pago total de 13,80e está hecho con tarjeta, cuando parte esta hecho con tarjeta y parte con efectivo: HISTIC001.jpg</t>
-  </si>
-  <si>
-    <t>1. The user writes a world in the box of the search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se edita la carta, no se ve solo
+    <t xml:space="preserve">1. The user sees a cash closing's
+2. Select one
+3.  Clicks the printer icon
 </t>
   </si>
   <si>
-    <t>No veo variación al cambiar de menú
-18/05/26: El menú desplegable, donde escoges "CARTA", se ha quedado vacio sin carta: MEN007.jpg</t>
-  </si>
-  <si>
-    <t>1. The menu is selected.</t>
-  </si>
-  <si>
-    <t>1. Select numbers of people
-2. Select several products with his modifiers
-3. Select menu (button "CARTA")</t>
+    <t>No se indican los campos obligatorios y al pulsar "Crear" no hace nada. 
+La imagen del teclado impide ver el resto de la funcionalidad: CATEG004.jpg
+22/05/26: Después de crear una categoría aparece un mensaje de que no hay categorias registradas: CATEG010.jpg</t>
+  </si>
+  <si>
+    <t>Debería de preguntar si se quiere modificar y permitir cancelar.
+22/05/26 No se puede salir de la edición del ROL: CATEG011.jpg</t>
   </si>
 </sst>
 </file>
@@ -2793,7 +2845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -2802,7 +2854,7 @@
     <col min="4" max="4" width="41.5703125" style="5" customWidth="1"/>
     <col min="5" max="6" width="33.42578125" style="5" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="5"/>
-    <col min="8" max="8" width="68.28515625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="68.85546875" style="5" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
@@ -2853,7 +2905,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -2864,10 +2916,10 @@
         <v>29</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -2875,7 +2927,7 @@
         <v>8</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -2886,20 +2938,20 @@
         <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -2910,13 +2962,13 @@
         <v>31</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="2" t="s">
@@ -2934,13 +2986,13 @@
         <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>657</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>666</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="2" t="s">
@@ -2958,20 +3010,20 @@
         <v>33</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -2982,16 +3034,16 @@
         <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -3006,10 +3058,10 @@
         <v>35</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>21</v>
@@ -3022,7 +3074,7 @@
       </c>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" s="6" customFormat="1" ht="150" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" s="6" customFormat="1" ht="210" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -3030,20 +3082,20 @@
         <v>36</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>664</v>
+        <v>686</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3054,16 +3106,16 @@
         <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -3078,10 +3130,10 @@
         <v>38</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
@@ -3102,10 +3154,10 @@
         <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>23</v>
@@ -3118,7 +3170,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -3126,208 +3178,208 @@
         <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>560</v>
+        <v>682</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="E14" s="1"/>
+        <v>684</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>683</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>12</v>
+        <v>685</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F16" s="1"/>
       <c r="G16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="B18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H17" s="3" t="s">
+      <c r="F18" s="1"/>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="D19" s="1" t="s">
+      <c r="B20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+      <c r="F21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>21</v>
-      </c>
       <c r="B22" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -3336,338 +3388,340 @@
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>43</v>
+        <v>548</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F23" s="1"/>
+        <v>115</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="G23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>67</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="1" t="s">
+      <c r="B25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="F26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>24</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="1" t="s">
+    </row>
+    <row r="27" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="C27" s="1" t="s">
-        <v>574</v>
+        <v>549</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>575</v>
+        <v>116</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>571</v>
+        <v>117</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="H27" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
+        <v>566</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>563</v>
+      </c>
       <c r="F28" s="1"/>
       <c r="G28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>125</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>127</v>
+        <v>667</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D30" s="1"/>
+        <v>120</v>
+      </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>639</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E32" s="1"/>
+        <v>630</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>631</v>
+      </c>
       <c r="F32" s="1"/>
       <c r="G32" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D33" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>644</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>643</v>
+        <v>568</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E35" s="1"/>
+        <v>139</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>636</v>
+      </c>
       <c r="F35" s="1"/>
       <c r="G35" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>159</v>
+        <v>635</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
       <c r="G36" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H36" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F37" s="1"/>
+        <v>115</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="G37" s="2" t="s">
         <v>13</v>
       </c>
@@ -3675,62 +3729,62 @@
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E39" s="1"/>
+        <v>144</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="F39" s="1"/>
       <c r="G39" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>448</v>
+        <v>97</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
@@ -3738,43 +3792,43 @@
         <v>14</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>580</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>578</v>
+        <v>149</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
@@ -3782,91 +3836,91 @@
         <v>8</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>634</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
+        <v>42</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="F44" s="1"/>
+      <c r="G44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
         <v>43</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H44" s="3"/>
-    </row>
-    <row r="45" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
-        <v>44</v>
-      </c>
       <c r="B45" s="1" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>581</v>
+        <v>627</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
+        <v>628</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="G45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>585</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H45" s="3"/>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>103</v>
+        <v>445</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -3874,358 +3928,356 @@
         <v>8</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>438</v>
+        <v>574</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>439</v>
+        <v>576</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>447</v>
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>599</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
       <c r="G48" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H48" s="3"/>
+        <v>666</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
+        <v>47</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>48</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H49" s="3"/>
-    </row>
-    <row r="50" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
+      <c r="B50" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" s="3"/>
+    </row>
+    <row r="51" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>49</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="E50" s="1" t="s">
+      <c r="B51" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="F50" s="1"/>
-      <c r="G50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
-        <v>50</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>618</v>
-      </c>
       <c r="D51" s="1" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="F51" s="1"/>
       <c r="G51" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="52" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
+        <v>50</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>51</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="F52" s="1"/>
-      <c r="G52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
-        <v>52</v>
-      </c>
       <c r="B53" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>120</v>
+        <v>596</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H53" s="3"/>
-    </row>
-    <row r="54" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>454</v>
+        <v>105</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>630</v>
+        <v>597</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>631</v>
+        <v>115</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>446</v>
-      </c>
+      <c r="H54" s="3"/>
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>111</v>
+        <v>446</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>602</v>
+        <v>621</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>455</v>
+        <v>107</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="F57" s="1"/>
       <c r="G57" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H57" s="3"/>
-    </row>
-    <row r="58" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>56</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>671</v>
+        <v>611</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>673</v>
+        <v>598</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="F58" s="1"/>
+        <v>115</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="G58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>672</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H58" s="3"/>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>57</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>611</v>
+        <v>662</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>622</v>
+        <v>664</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>613</v>
+        <v>665</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>58</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="F60" s="1"/>
       <c r="G60" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H60" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>634</v>
+      </c>
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>59</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>612</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>627</v>
+        <v>115</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>627</v>
+        <v>115</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>13</v>
@@ -4237,19 +4289,19 @@
         <v>60</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>621</v>
+        <v>604</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>120</v>
+        <v>619</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>120</v>
+        <v>619</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>13</v>
@@ -4261,86 +4313,86 @@
         <v>61</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>572</v>
+        <v>613</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>677</v>
+        <v>617</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>610</v>
+        <v>115</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>610</v>
+        <v>115</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H63" s="3"/>
+    </row>
+    <row r="64" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>62</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>435</v>
+        <v>564</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
+        <v>668</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>602</v>
+      </c>
       <c r="G64" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H64" s="3"/>
-    </row>
-    <row r="65" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>63</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>591</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
       <c r="G65" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H65" s="3"/>
     </row>
-    <row r="66" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>64</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>120</v>
+        <v>583</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>120</v>
+        <v>583</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>13</v>
@@ -4352,19 +4404,19 @@
         <v>65</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>593</v>
+        <v>115</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>593</v>
+        <v>115</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>13</v>
@@ -4376,19 +4428,19 @@
         <v>66</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>277</v>
+        <v>586</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>120</v>
+        <v>585</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>120</v>
+        <v>585</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>13</v>
@@ -4400,19 +4452,19 @@
         <v>67</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>596</v>
+        <v>271</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>597</v>
+        <v>115</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>597</v>
+        <v>115</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>13</v>
@@ -4424,115 +4476,115 @@
         <v>68</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>120</v>
+        <v>589</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>120</v>
+        <v>589</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H70" s="3"/>
     </row>
-    <row r="71" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>69</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>410</v>
+        <v>587</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="F71" s="1"/>
+        <v>115</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="G71" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>415</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H71" s="3"/>
     </row>
     <row r="72" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>70</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="F72" s="1"/>
       <c r="G72" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>71</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>624</v>
+        <v>401</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="F73" s="1"/>
       <c r="G73" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H73" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="74" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>72</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>399</v>
+        <v>616</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>400</v>
+        <v>115</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>400</v>
+        <v>115</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>13</v>
@@ -4544,19 +4596,19 @@
         <v>73</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>13</v>
@@ -4568,47 +4620,47 @@
         <v>74</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="F76" s="1"/>
+        <v>395</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>394</v>
+      </c>
       <c r="G76" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H76" s="3"/>
+    </row>
+    <row r="77" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>75</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
     </row>
     <row r="78" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4616,23 +4668,23 @@
         <v>76</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="F78" s="1"/>
       <c r="G78" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
     </row>
     <row r="79" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4640,211 +4692,211 @@
         <v>77</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="F79" s="1"/>
       <c r="G79" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H79" s="3"/>
-    </row>
-    <row r="80" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>78</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>428</v>
+        <v>115</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>428</v>
+        <v>115</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H80" s="3"/>
     </row>
-    <row r="81" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>79</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>120</v>
+        <v>420</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>120</v>
+        <v>420</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H81" s="3"/>
     </row>
-    <row r="82" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>80</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F82" s="1"/>
+        <v>115</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="G82" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H82" s="3"/>
+    </row>
+    <row r="83" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>81</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>378</v>
+        <v>423</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>386</v>
+        <v>424</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>387</v>
+        <v>189</v>
       </c>
       <c r="F83" s="1"/>
       <c r="G83" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>82</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="C84" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>388</v>
       </c>
       <c r="F84" s="1"/>
       <c r="G84" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>83</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="C85" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D85" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>120</v>
-      </c>
+      <c r="F85" s="1"/>
       <c r="G85" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H85" s="3"/>
-    </row>
-    <row r="86" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>84</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>276</v>
+        <v>383</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>389</v>
+        <v>115</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>389</v>
+        <v>115</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H86" s="3"/>
     </row>
-    <row r="87" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>85</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>120</v>
+        <v>381</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>120</v>
+        <v>381</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>13</v>
@@ -4856,19 +4908,19 @@
         <v>86</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>327</v>
+        <v>271</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>390</v>
+        <v>115</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>390</v>
+        <v>115</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>13</v>
@@ -4880,43 +4932,43 @@
         <v>87</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>120</v>
+        <v>382</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>120</v>
+        <v>382</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H89" s="3"/>
     </row>
-    <row r="90" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>88</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>278</v>
+        <v>320</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>279</v>
+        <v>115</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>279</v>
+        <v>115</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>13</v>
@@ -4928,19 +4980,19 @@
         <v>89</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>394</v>
+        <v>272</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>395</v>
+        <v>273</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>395</v>
+        <v>273</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>13</v>
@@ -4952,165 +5004,165 @@
         <v>90</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>336</v>
+        <v>385</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>337</v>
+        <v>386</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>348</v>
+        <v>387</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H92" s="3"/>
+    </row>
+    <row r="93" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>91</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="F93" s="1"/>
+        <v>342</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>345</v>
+      </c>
       <c r="G93" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" s="6" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>92</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="F94" s="1"/>
       <c r="G94" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>93</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="F95" s="1"/>
       <c r="G95" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H95" s="3"/>
-    </row>
-    <row r="96" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>94</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="F96" s="1"/>
+        <v>115</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="G96" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H96" s="3"/>
+    </row>
+    <row r="97" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>95</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="F97" s="1"/>
       <c r="G97" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H97" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>359</v>
+      </c>
     </row>
     <row r="98" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>96</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>327</v>
+        <v>271</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>354</v>
+        <v>115</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>354</v>
+        <v>115</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>13</v>
@@ -5122,71 +5174,71 @@
         <v>97</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>120</v>
+        <v>348</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>120</v>
+        <v>348</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H99" s="3"/>
     </row>
-    <row r="100" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>98</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>278</v>
+        <v>320</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="F100" s="1"/>
+        <v>115</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="G100" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H100" s="3"/>
+    </row>
+    <row r="101" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>99</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>360</v>
+        <v>272</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>361</v>
+        <v>273</v>
       </c>
       <c r="F101" s="1"/>
       <c r="G101" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
     </row>
     <row r="102" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5194,23 +5246,23 @@
         <v>100</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="F102" s="1"/>
       <c r="G102" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>376</v>
+        <v>355</v>
       </c>
     </row>
     <row r="103" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5218,239 +5270,239 @@
         <v>101</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="F103" s="1"/>
       <c r="G103" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>102</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>306</v>
+        <v>352</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>307</v>
+        <v>368</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>308</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="F104" s="1"/>
       <c r="G104" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>103</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>333</v>
+        <v>301</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F105" s="1"/>
+        <v>302</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>302</v>
+      </c>
       <c r="G105" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H105" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>361</v>
+      </c>
     </row>
     <row r="106" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>104</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="F106" s="1"/>
       <c r="G106" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H106" s="3"/>
+    </row>
+    <row r="107" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>105</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="F107" s="1"/>
       <c r="G107" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H107" s="3"/>
-    </row>
-    <row r="108" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>106</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>317</v>
+        <v>115</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>317</v>
+        <v>115</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H108" s="3" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H108" s="3"/>
+    </row>
+    <row r="109" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>107</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="C109" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H109" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="D109" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H109" s="3"/>
     </row>
     <row r="110" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>108</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>327</v>
+        <v>271</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>318</v>
+        <v>115</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>318</v>
+        <v>115</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>589</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H110" s="3"/>
     </row>
     <row r="111" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>109</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>120</v>
+        <v>312</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>120</v>
+        <v>312</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H111" s="3"/>
-    </row>
-    <row r="112" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>110</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>278</v>
+        <v>320</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>279</v>
+        <v>115</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>279</v>
+        <v>115</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>13</v>
@@ -5462,139 +5514,139 @@
         <v>111</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H113" s="3"/>
+    </row>
+    <row r="114" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>112</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>328</v>
+        <v>279</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H114" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="115" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>113</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="F115" s="1"/>
+        <v>317</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>317</v>
+      </c>
       <c r="G115" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H115" s="3"/>
     </row>
-    <row r="116" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>114</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="F116" s="1"/>
       <c r="G116" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H116" s="3"/>
     </row>
-    <row r="117" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>115</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>321</v>
+        <v>115</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>321</v>
+        <v>115</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H117" s="3"/>
     </row>
-    <row r="118" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>116</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>120</v>
+        <v>315</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>120</v>
+        <v>315</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>13</v>
@@ -5606,19 +5658,19 @@
         <v>117</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>327</v>
+        <v>271</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>322</v>
+        <v>115</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>322</v>
+        <v>115</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>13</v>
@@ -5630,70 +5682,70 @@
         <v>118</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>120</v>
+        <v>316</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>120</v>
+        <v>316</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H120" s="3">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="H120" s="3"/>
+    </row>
+    <row r="121" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>119</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>278</v>
+        <v>320</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>279</v>
+        <v>115</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>279</v>
+        <v>115</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H121" s="3">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>120</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="F122" s="1"/>
+        <v>273</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>273</v>
+      </c>
       <c r="G122" s="2" t="s">
         <v>8</v>
       </c>
@@ -5701,222 +5753,222 @@
         <v>299</v>
       </c>
     </row>
-    <row r="123" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>121</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>323</v>
+        <v>292</v>
       </c>
       <c r="F123" s="1"/>
       <c r="G123" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>122</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F124" s="1"/>
       <c r="G124" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>123</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>132</v>
+        <v>319</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>264</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="F125" s="1"/>
       <c r="G125" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>124</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>273</v>
+        <v>127</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H126" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="127" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>125</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D127" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E127" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="F127" s="1" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H127" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H127" s="3"/>
+    </row>
+    <row r="128" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>126</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>120</v>
+        <v>274</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>120</v>
+        <v>274</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H128" s="3"/>
-    </row>
-    <row r="129" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>127</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>281</v>
+        <v>115</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>281</v>
+        <v>115</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H129" s="3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H129" s="3"/>
+    </row>
+    <row r="130" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>128</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>120</v>
+        <v>275</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>120</v>
+        <v>275</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H130" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="131" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>129</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>327</v>
+        <v>271</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>283</v>
+        <v>115</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>283</v>
+        <v>115</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>13</v>
@@ -5928,119 +5980,119 @@
         <v>130</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>120</v>
+        <v>277</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>120</v>
+        <v>277</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H132" s="3"/>
     </row>
-    <row r="133" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>131</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>278</v>
+        <v>320</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>279</v>
+        <v>115</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>279</v>
+        <v>115</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H133" s="3"/>
     </row>
-    <row r="134" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>132</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>133</v>
+        <v>272</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F134" s="1"/>
+        <v>273</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>273</v>
+      </c>
       <c r="G134" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H134" s="3" t="s">
-        <v>371</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H134" s="3"/>
     </row>
     <row r="135" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>133</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>238</v>
+        <v>128</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="F135" s="1"/>
       <c r="G135" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>134</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="F136" s="1"/>
       <c r="G136" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
     </row>
     <row r="137" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6048,47 +6100,47 @@
         <v>135</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="F137" s="1"/>
       <c r="G137" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>136</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="F138" s="1"/>
       <c r="G138" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="139" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6096,47 +6148,47 @@
         <v>137</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="F139" s="1"/>
       <c r="G139" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>138</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="F140" s="1"/>
       <c r="G140" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="141" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6144,23 +6196,23 @@
         <v>139</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="F141" s="1"/>
       <c r="G141" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="142" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6168,99 +6220,99 @@
         <v>140</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="F142" s="1"/>
       <c r="G142" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>141</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>261</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="F143" s="1"/>
       <c r="G143" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>142</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>143</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="F145" s="1"/>
+        <v>219</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>219</v>
+      </c>
       <c r="G145" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="146" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6268,123 +6320,121 @@
         <v>144</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="F146" s="1"/>
       <c r="G146" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H146" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>365</v>
+      </c>
     </row>
     <row r="147" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>145</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H147" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H147" s="3"/>
+    </row>
+    <row r="148" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>146</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>92</v>
+        <v>226</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H148" s="3"/>
-    </row>
-    <row r="149" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>147</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>172</v>
+        <v>87</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>220</v>
+        <v>129</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F149" s="1"/>
+        <v>216</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="G149" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H149" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H149" s="3"/>
+    </row>
+    <row r="150" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>148</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D150" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F150" s="1"/>
+      <c r="G150" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H150" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="G150" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H150" s="3" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="151" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6392,184 +6442,186 @@
         <v>149</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H151" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H151" s="3" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="152" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>150</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E152" s="1"/>
-      <c r="F152" s="1"/>
+      <c r="E152" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>212</v>
+      </c>
       <c r="G152" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H152" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H152" s="3"/>
+    </row>
+    <row r="153" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>151</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>202</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="E153" s="1"/>
       <c r="F153" s="1"/>
       <c r="G153" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>152</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F154" s="1"/>
       <c r="G154" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>153</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="F155" s="1"/>
       <c r="G155" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>154</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F156" s="1"/>
       <c r="G156" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>155</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="F157" s="1"/>
       <c r="G157" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H157" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H157" s="3" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="158" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>156</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="C158" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D158" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>210</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="F158" s="1"/>
       <c r="G158" s="2" t="s">
         <v>13</v>
       </c>
@@ -6580,19 +6632,19 @@
         <v>157</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>13</v>
@@ -6604,71 +6656,71 @@
         <v>158</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H160" s="3"/>
     </row>
-    <row r="161" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>159</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F161" s="1"/>
+        <v>204</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="G161" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H161" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H161" s="3"/>
+    </row>
+    <row r="162" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>160</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F162" s="1"/>
       <c r="G162" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="163" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -6676,143 +6728,141 @@
         <v>161</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
       <c r="F163" s="1"/>
       <c r="G163" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H163" s="3"/>
-    </row>
-    <row r="164" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H163" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>162</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>93</v>
+        <v>178</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>167</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="F164" s="1"/>
       <c r="G164" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H164" s="3"/>
     </row>
-    <row r="165" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>163</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>169</v>
+        <v>130</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F165" s="1"/>
+        <v>161</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="G165" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H165" s="3" t="s">
-        <v>171</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H165" s="3"/>
     </row>
     <row r="166" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>164</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F166" s="1"/>
       <c r="G166" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H166" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>165</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>162</v>
+        <v>89</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="F167" s="1"/>
       <c r="G167" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>166</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>46</v>
+        <v>158</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>48</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="F168" s="1"/>
       <c r="G168" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>49</v>
+        <v>633</v>
       </c>
     </row>
     <row r="169" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6820,52 +6870,102 @@
         <v>167</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F169" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="G169" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>168</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>55</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="F170" s="1"/>
       <c r="G170" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H170" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H170" s="3" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
+        <v>169</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H171" s="3"/>
+    </row>
+    <row r="172" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
+        <v>170</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H172" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G170">
+  <conditionalFormatting sqref="G2:G172">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>

--- a/App/TestCases_App/User_admin.xlsx
+++ b/App/TestCases_App/User_admin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09466A4B-1FC1-458E-AD3A-9D2F50D9557C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686A7129-FCA4-4B37-8579-581C267FE42D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2845,7 +2845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H172"/>
+  <dimension ref="A1:H173"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -2908,293 +2908,279 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>560</v>
-      </c>
+    <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="G3" s="2"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>660</v>
+        <v>559</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>643</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>558</v>
+        <v>660</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>9</v>
+        <v>659</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>655</v>
+        <v>558</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>649</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>557</v>
+        <v>655</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>672</v>
+        <v>649</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>670</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>650</v>
+        <v>672</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>656</v>
-      </c>
+        <v>671</v>
+      </c>
+      <c r="F8" s="1"/>
       <c r="G8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" s="6" customFormat="1" ht="210" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" s="6" customFormat="1" ht="210" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="F11" s="1"/>
+      <c r="G11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>683</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3202,208 +3188,208 @@
         <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>552</v>
+        <v>682</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="E15" s="1"/>
+        <v>684</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>683</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="G15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>12</v>
+        <v>685</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F17" s="1"/>
       <c r="G17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
+        <v>15</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H18" s="3" t="s">
+      <c r="F19" s="1"/>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>17</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>19</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>546</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+      <c r="G22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>21</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>13</v>
@@ -3412,338 +3398,340 @@
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>23</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>687</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
+        <v>23</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" s="7" t="s">
+      <c r="G27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="7" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+    <row r="28" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>563</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="H28" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
+        <v>566</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>563</v>
+      </c>
       <c r="F29" s="1"/>
       <c r="G29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>122</v>
+        <v>667</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31" s="1"/>
+        <v>120</v>
+      </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>631</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E33" s="1"/>
+        <v>630</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>631</v>
+      </c>
       <c r="F33" s="1"/>
       <c r="G33" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D34" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>636</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>635</v>
+        <v>568</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E36" s="1"/>
+        <v>139</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>636</v>
+      </c>
       <c r="F36" s="1"/>
       <c r="G36" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>154</v>
+        <v>635</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>115</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
       <c r="G37" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H37" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="F38" s="1"/>
+        <v>115</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="G38" s="2" t="s">
         <v>13</v>
       </c>
@@ -3751,62 +3739,62 @@
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>142</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E40" s="1"/>
+        <v>144</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="F40" s="1"/>
       <c r="G40" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>440</v>
+        <v>97</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
@@ -3814,43 +3802,43 @@
         <v>14</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>572</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>570</v>
+        <v>149</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -3858,91 +3846,91 @@
         <v>8</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>624</v>
+        <v>570</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>626</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H44" s="3" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>42</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="F45" s="1"/>
+      <c r="G45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="45" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
+    <row r="46" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>43</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E46" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H45" s="3"/>
-    </row>
-    <row r="46" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
-        <v>44</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
       <c r="G46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>577</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H46" s="3"/>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>98</v>
+        <v>445</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -3953,355 +3941,353 @@
         <v>577</v>
       </c>
     </row>
-    <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>430</v>
+        <v>574</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>431</v>
+        <v>576</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>439</v>
+        <v>8</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>591</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
       <c r="G49" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H49" s="3"/>
+        <v>666</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
+        <v>47</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" s="3"/>
+    </row>
+    <row r="51" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>48</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B51" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F51" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="G50" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H50" s="3"/>
-    </row>
-    <row r="51" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
+      <c r="G51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>49</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="F51" s="1"/>
-      <c r="G51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H51" s="3" t="s">
+      <c r="F52" s="1"/>
+      <c r="G52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
         <v>437</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
-        <v>50</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
+        <v>50</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>51</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E54" s="1" t="s">
         <v>596</v>
-      </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
-        <v>52</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H54" s="3"/>
-    </row>
-    <row r="55" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>446</v>
+        <v>105</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>622</v>
+        <v>597</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>623</v>
+        <v>115</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H55" s="3" t="s">
-        <v>438</v>
-      </c>
+      <c r="H55" s="3"/>
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>106</v>
+        <v>446</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>594</v>
+        <v>621</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>599</v>
+        <v>619</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H57" s="3" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>55</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="F58" s="1"/>
+      <c r="G58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H58" s="3" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="58" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
+    <row r="59" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
         <v>56</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B59" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C59" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E59" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F59" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H58" s="3"/>
-    </row>
-    <row r="59" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
-        <v>57</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="F59" s="1"/>
       <c r="G59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>663</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H59" s="3"/>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>603</v>
+        <v>662</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>614</v>
+        <v>664</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>605</v>
+        <v>665</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H60" s="3" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>58</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="F61" s="1"/>
+      <c r="G61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H61" s="3" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>59</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H61" s="3"/>
     </row>
     <row r="62" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>619</v>
+        <v>115</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>619</v>
+        <v>115</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>13</v>
@@ -4310,22 +4296,22 @@
     </row>
     <row r="63" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>115</v>
+        <v>619</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>115</v>
+        <v>619</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>13</v>
@@ -4334,89 +4320,89 @@
     </row>
     <row r="64" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
+        <v>61</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H64" s="3"/>
+    </row>
+    <row r="65" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
         <v>62</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D65" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E65" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F65" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="G64" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
+      <c r="G65" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
         <v>63</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B66" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H65" s="3"/>
-    </row>
-    <row r="66" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H66" s="3"/>
+    </row>
+    <row r="67" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
         <v>64</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C67" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F67" s="1" t="s">
         <v>583</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H66" s="3"/>
-    </row>
-    <row r="67" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
-        <v>65</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>13</v>
@@ -4425,22 +4411,22 @@
     </row>
     <row r="68" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>585</v>
+        <v>115</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>585</v>
+        <v>115</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>13</v>
@@ -4449,22 +4435,22 @@
     </row>
     <row r="69" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>271</v>
+        <v>586</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>115</v>
+        <v>585</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>115</v>
+        <v>585</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>13</v>
@@ -4473,22 +4459,22 @@
     </row>
     <row r="70" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>588</v>
+        <v>271</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>589</v>
+        <v>115</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>589</v>
+        <v>115</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>13</v>
@@ -4497,64 +4483,64 @@
     </row>
     <row r="71" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
+        <v>68</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" s="3"/>
+    </row>
+    <row r="72" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
         <v>69</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D72" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="F72" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G71" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H71" s="3"/>
-    </row>
-    <row r="72" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
-        <v>70</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="F72" s="1"/>
       <c r="G72" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>407</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H72" s="3"/>
     </row>
     <row r="73" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>398</v>
@@ -4564,51 +4550,51 @@
         <v>8</v>
       </c>
       <c r="H73" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>71</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="F74" s="1"/>
+      <c r="G74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
-        <v>72</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H74" s="3"/>
     </row>
     <row r="75" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>391</v>
+        <v>616</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>392</v>
+        <v>115</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>392</v>
+        <v>115</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>13</v>
@@ -4617,22 +4603,22 @@
     </row>
     <row r="76" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>13</v>
@@ -4641,64 +4627,64 @@
     </row>
     <row r="77" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
+        <v>74</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H77" s="3"/>
+    </row>
+    <row r="78" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
         <v>75</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D78" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E78" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="F77" s="1"/>
-      <c r="G77" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
-        <v>76</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>410</v>
       </c>
       <c r="F78" s="1"/>
       <c r="G78" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
     </row>
     <row r="79" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>410</v>
@@ -4708,219 +4694,219 @@
         <v>8</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="80" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
+        <v>77</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="F80" s="1"/>
+      <c r="G80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
         <v>78</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E81" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F81" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H80" s="3"/>
-    </row>
-    <row r="81" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
+      <c r="G81" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H81" s="3"/>
+    </row>
+    <row r="82" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
         <v>79</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D82" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E82" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F82" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="G81" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H81" s="3"/>
-    </row>
-    <row r="82" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
+      <c r="G82" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H82" s="3"/>
+    </row>
+    <row r="83" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
         <v>80</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C83" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D83" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E83" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="F83" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G82" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H82" s="3"/>
-    </row>
-    <row r="83" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
+      <c r="G83" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H83" s="3"/>
+    </row>
+    <row r="84" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
         <v>81</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D84" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E84" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="F83" s="1"/>
-      <c r="G83" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
-        <v>82</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>379</v>
       </c>
       <c r="F84" s="1"/>
       <c r="G84" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F85" s="1"/>
       <c r="G85" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H85" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>83</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F86" s="1"/>
+      <c r="G86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H86" s="3" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="86" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
+    <row r="87" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
         <v>84</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B87" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C87" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E87" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F86" s="1" t="s">
+      <c r="F87" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G86" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H86" s="3"/>
-    </row>
-    <row r="87" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
+      <c r="G87" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H87" s="3"/>
+    </row>
+    <row r="88" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
         <v>85</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B88" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D88" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="F88" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H87" s="3"/>
-    </row>
-    <row r="88" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
-        <v>86</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>13</v>
@@ -4929,22 +4915,22 @@
     </row>
     <row r="89" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>321</v>
+        <v>271</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>382</v>
+        <v>115</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>382</v>
+        <v>115</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>13</v>
@@ -4953,46 +4939,46 @@
     </row>
     <row r="90" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
+        <v>87</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H90" s="3"/>
+    </row>
+    <row r="91" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
         <v>88</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B91" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C91" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D91" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F90" s="1" t="s">
+      <c r="F91" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H90" s="3"/>
-    </row>
-    <row r="91" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
-        <v>89</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>13</v>
@@ -5001,22 +4987,22 @@
     </row>
     <row r="92" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>386</v>
+        <v>272</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>387</v>
+        <v>273</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>387</v>
+        <v>273</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>13</v>
@@ -5025,168 +5011,168 @@
     </row>
     <row r="93" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
+        <v>90</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H93" s="3"/>
+    </row>
+    <row r="94" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
         <v>91</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B94" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C94" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="D94" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="E94" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="F93" s="1" t="s">
+      <c r="F94" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="G93" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H93" s="3" t="s">
+      <c r="G94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="94" spans="1:8" s="6" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
+    <row r="95" spans="1:8" s="6" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
         <v>92</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="D95" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="E95" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="F94" s="1"/>
-      <c r="G94" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
-        <v>93</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="F95" s="1"/>
       <c r="G95" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H95" s="3" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>93</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="F96" s="1"/>
+      <c r="G96" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="96" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
+    <row r="97" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
         <v>94</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B97" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C97" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="D97" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="E97" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F96" s="1" t="s">
+      <c r="F97" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G96" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H96" s="3"/>
-    </row>
-    <row r="97" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A97" s="1">
+      <c r="G97" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H97" s="3"/>
+    </row>
+    <row r="98" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
         <v>95</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B98" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C98" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="D98" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="E98" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="F97" s="1"/>
-      <c r="G97" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H97" s="3" t="s">
+      <c r="F98" s="1"/>
+      <c r="G98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H98" s="3" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A98" s="1">
-        <v>96</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H98" s="3"/>
     </row>
     <row r="99" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>321</v>
+        <v>271</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>348</v>
+        <v>115</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>348</v>
+        <v>115</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>13</v>
@@ -5195,338 +5181,338 @@
     </row>
     <row r="100" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
+        <v>97</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H100" s="3"/>
+    </row>
+    <row r="101" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
         <v>98</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B101" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C101" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="D101" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="E101" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F100" s="1" t="s">
+      <c r="F101" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G100" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H100" s="3"/>
-    </row>
-    <row r="101" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A101" s="1">
+      <c r="G101" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H101" s="3"/>
+    </row>
+    <row r="102" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
         <v>99</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C102" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D102" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E102" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="F101" s="1"/>
-      <c r="G101" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A102" s="1">
-        <v>100</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="F102" s="1"/>
       <c r="G102" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="103" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F103" s="1"/>
       <c r="G103" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>691</v>
+        <v>355</v>
       </c>
     </row>
     <row r="104" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F104" s="1"/>
       <c r="G104" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H104" s="3" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>102</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="F105" s="1"/>
+      <c r="G105" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H105" s="3" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="105" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="1">
+    <row r="106" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
         <v>103</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B106" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D106" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E106" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="F105" s="1" t="s">
+      <c r="F106" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="G105" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H105" s="3" t="s">
+      <c r="G106" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H106" s="3" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A106" s="1">
-        <v>104</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="F106" s="1"/>
-      <c r="G106" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H106" s="3"/>
     </row>
     <row r="107" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="F107" s="1"/>
       <c r="G107" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H107" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H107" s="3"/>
+    </row>
+    <row r="108" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>105</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F108" s="1"/>
+      <c r="G108" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H108" s="3" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="108" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A108" s="1">
+    <row r="109" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
         <v>106</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B109" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C109" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="D109" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="E108" s="1" t="s">
+      <c r="E109" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F108" s="1" t="s">
+      <c r="F109" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G108" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H108" s="3"/>
-    </row>
-    <row r="109" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A109" s="1">
+      <c r="G109" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H109" s="3"/>
+    </row>
+    <row r="110" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
         <v>107</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B110" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C110" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="D110" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="E110" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F109" s="1" t="s">
+      <c r="F110" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="G109" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H109" s="3" t="s">
+      <c r="G110" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H110" s="3" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="110" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A110" s="1">
-        <v>108</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H110" s="3"/>
     </row>
     <row r="111" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>321</v>
+        <v>271</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>312</v>
+        <v>115</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>312</v>
+        <v>115</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H111" s="3" t="s">
-        <v>581</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H111" s="3"/>
     </row>
     <row r="112" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
+        <v>109</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
         <v>110</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B113" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C113" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="D113" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E112" s="1" t="s">
+      <c r="E113" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F112" s="1" t="s">
+      <c r="F113" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H112" s="3"/>
-    </row>
-    <row r="113" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="1">
-        <v>111</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>13</v>
@@ -5535,142 +5521,142 @@
     </row>
     <row r="114" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
+        <v>111</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H114" s="3"/>
+    </row>
+    <row r="115" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
         <v>112</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B115" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C115" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="D115" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E115" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="F114" s="1" t="s">
+      <c r="F115" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="G114" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H114" s="3" t="s">
+      <c r="G115" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H115" s="3" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A115" s="1">
-        <v>113</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H115" s="3"/>
     </row>
     <row r="116" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="F116" s="1"/>
+      <c r="F116" s="1" t="s">
+        <v>317</v>
+      </c>
       <c r="G116" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H116" s="3"/>
     </row>
-    <row r="117" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
+        <v>114</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="F117" s="1"/>
+      <c r="G117" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H117" s="3"/>
+    </row>
+    <row r="118" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
         <v>115</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B118" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C118" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="D118" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="E118" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F117" s="1" t="s">
+      <c r="F118" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G117" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H117" s="3"/>
-    </row>
-    <row r="118" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A118" s="1">
+      <c r="G118" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H118" s="3"/>
+    </row>
+    <row r="119" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
         <v>116</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B119" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C119" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="D119" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="F118" s="1" t="s">
+      <c r="F119" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H118" s="3"/>
-    </row>
-    <row r="119" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A119" s="1">
-        <v>117</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>13</v>
@@ -5679,22 +5665,22 @@
     </row>
     <row r="120" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>321</v>
+        <v>271</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>316</v>
+        <v>115</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>316</v>
+        <v>115</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>13</v>
@@ -5703,190 +5689,190 @@
     </row>
     <row r="121" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
+        <v>118</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H121" s="3"/>
+    </row>
+    <row r="122" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
         <v>119</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B122" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C122" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="D122" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E121" s="1" t="s">
+      <c r="E122" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F121" s="1" t="s">
+      <c r="F122" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G121" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H121" s="3">
+      <c r="G122" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H122" s="3">
         <v>702</v>
       </c>
     </row>
-    <row r="122" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A122" s="1">
+    <row r="123" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
         <v>120</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B123" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C123" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D123" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E122" s="1" t="s">
+      <c r="E123" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="F122" s="1" t="s">
+      <c r="F123" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="G122" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H122" s="3" t="s">
+      <c r="G123" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H123" s="3" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="123" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A123" s="1">
+    <row r="124" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
         <v>121</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B124" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="C124" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="D124" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="E123" s="1" t="s">
+      <c r="E124" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="F123" s="1"/>
-      <c r="G123" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H123" s="3" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A124" s="1">
-        <v>122</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="F124" s="1"/>
       <c r="G124" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F125" s="1"/>
       <c r="G125" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H125" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>123</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="F126" s="1"/>
+      <c r="G126" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H126" s="3" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="126" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="1">
+    <row r="127" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
         <v>124</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B127" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="C127" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="D127" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E126" s="1" t="s">
+      <c r="E127" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F126" s="1" t="s">
+      <c r="F127" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="G126" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H126" s="3" t="s">
+      <c r="G127" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H127" s="3" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="127" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A127" s="1">
-        <v>125</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H127" s="3"/>
     </row>
     <row r="128" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>274</v>
@@ -5895,104 +5881,104 @@
         <v>274</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H128" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H128" s="3"/>
+    </row>
+    <row r="129" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>126</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H129" s="3" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="129" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A129" s="1">
+    <row r="130" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
         <v>127</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B130" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="C130" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="D130" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="E129" s="1" t="s">
+      <c r="E130" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F129" s="1" t="s">
+      <c r="F130" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G129" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H129" s="3"/>
-    </row>
-    <row r="130" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A130" s="1">
+      <c r="G130" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H130" s="3"/>
+    </row>
+    <row r="131" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
         <v>128</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B131" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="C131" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D131" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="E130" s="1" t="s">
+      <c r="E131" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="F130" s="1" t="s">
+      <c r="F131" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="G130" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H130" s="3" t="s">
+      <c r="G131" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H131" s="3" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="131" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A131" s="1">
-        <v>129</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G131" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H131" s="3"/>
     </row>
     <row r="132" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>321</v>
+        <v>271</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>277</v>
+        <v>115</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>277</v>
+        <v>115</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>13</v>
@@ -6001,139 +5987,139 @@
     </row>
     <row r="133" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
+        <v>130</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H133" s="3"/>
+    </row>
+    <row r="134" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
         <v>131</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B134" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="C134" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="D134" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E133" s="1" t="s">
+      <c r="E134" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F133" s="1" t="s">
+      <c r="F134" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G133" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H133" s="3"/>
-    </row>
-    <row r="134" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="1">
+      <c r="G134" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H134" s="3"/>
+    </row>
+    <row r="135" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
         <v>132</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B135" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="C135" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="D135" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E134" s="1" t="s">
+      <c r="E135" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="F134" s="1" t="s">
+      <c r="F135" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="G134" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H134" s="3"/>
-    </row>
-    <row r="135" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A135" s="1">
-        <v>133</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="F135" s="1"/>
       <c r="G135" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H135" s="3" t="s">
-        <v>364</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H135" s="3"/>
     </row>
     <row r="136" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>232</v>
+        <v>128</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F136" s="1"/>
       <c r="G136" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F137" s="1"/>
       <c r="G137" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
     </row>
     <row r="138" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F138" s="1"/>
       <c r="G138" s="2" t="s">
@@ -6143,21 +6129,21 @@
         <v>250</v>
       </c>
     </row>
-    <row r="139" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F139" s="1"/>
       <c r="G139" s="2" t="s">
@@ -6169,19 +6155,19 @@
     </row>
     <row r="140" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F140" s="1"/>
       <c r="G140" s="2" t="s">
@@ -6191,21 +6177,21 @@
         <v>250</v>
       </c>
     </row>
-    <row r="141" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F141" s="1"/>
       <c r="G141" s="2" t="s">
@@ -6217,19 +6203,19 @@
     </row>
     <row r="142" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="F142" s="1"/>
       <c r="G142" s="2" t="s">
@@ -6241,19 +6227,19 @@
     </row>
     <row r="143" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="F143" s="1"/>
       <c r="G143" s="2" t="s">
@@ -6263,25 +6249,23 @@
         <v>250</v>
       </c>
     </row>
-    <row r="144" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="F144" s="1" t="s">
-        <v>255</v>
-      </c>
+      <c r="F144" s="1"/>
       <c r="G144" s="2" t="s">
         <v>14</v>
       </c>
@@ -6289,89 +6273,91 @@
         <v>250</v>
       </c>
     </row>
-    <row r="145" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H145" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
+        <v>143</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H146" s="3" t="s">
         <v>366</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A146" s="1">
-        <v>144</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F146" s="1"/>
-      <c r="G146" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H146" s="3" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="147" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>115</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="F147" s="1"/>
       <c r="G147" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H147" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>365</v>
+      </c>
     </row>
     <row r="148" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>222</v>
@@ -6383,269 +6369,269 @@
         <v>115</v>
       </c>
       <c r="G148" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H148" s="3"/>
+    </row>
+    <row r="149" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>146</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G149" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H148" s="3" t="s">
+      <c r="H149" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="149" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="1">
+    <row r="150" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
         <v>147</v>
       </c>
-      <c r="B149" s="1" t="s">
+      <c r="B150" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="C150" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D149" s="1" t="s">
+      <c r="D150" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E149" s="1" t="s">
+      <c r="E150" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F149" s="1" t="s">
+      <c r="F150" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="G149" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H149" s="3"/>
-    </row>
-    <row r="150" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A150" s="1">
+      <c r="G150" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H150" s="3"/>
+    </row>
+    <row r="151" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
         <v>148</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="B151" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="C151" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D150" s="1" t="s">
+      <c r="D151" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E150" s="1" t="s">
+      <c r="E151" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F150" s="1"/>
-      <c r="G150" s="2" t="s">
+      <c r="F151" s="1"/>
+      <c r="G151" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H150" s="3" t="s">
+      <c r="H151" s="3" t="s">
         <v>213</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="1">
-        <v>149</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H151" s="3" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="152" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H152" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="153" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
+        <v>150</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H153" s="3"/>
+    </row>
+    <row r="154" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
         <v>151</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="B154" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="C153" s="1" t="s">
+      <c r="C154" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D153" s="1" t="s">
+      <c r="D154" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E153" s="1"/>
-      <c r="F153" s="1"/>
-      <c r="G153" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H153" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A154" s="1">
-        <v>152</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>196</v>
-      </c>
+      <c r="E154" s="1"/>
       <c r="F154" s="1"/>
       <c r="G154" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F155" s="1"/>
       <c r="G155" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F156" s="1"/>
       <c r="G156" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="F157" s="1"/>
       <c r="G157" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="F158" s="1"/>
       <c r="G158" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H158" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H158" s="3" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="159" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>204</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="F159" s="1"/>
       <c r="G159" s="2" t="s">
         <v>13</v>
       </c>
@@ -6653,16 +6639,16 @@
     </row>
     <row r="160" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>204</v>
@@ -6677,16 +6663,16 @@
     </row>
     <row r="161" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>204</v>
@@ -6699,273 +6685,297 @@
       </c>
       <c r="H161" s="3"/>
     </row>
-    <row r="162" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
+        <v>159</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H162" s="3"/>
+    </row>
+    <row r="163" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
         <v>160</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="B163" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="C163" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D162" s="1" t="s">
+      <c r="D163" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E162" s="1" t="s">
+      <c r="E163" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="F162" s="1"/>
-      <c r="G162" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H162" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A163" s="1">
-        <v>161</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="F163" s="1"/>
       <c r="G163" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="164" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>578</v>
+        <v>545</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="F164" s="1"/>
       <c r="G164" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <v>162</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F165" s="1"/>
+      <c r="G165" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H164" s="3"/>
-    </row>
-    <row r="165" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="1">
+      <c r="H165" s="3"/>
+    </row>
+    <row r="166" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
         <v>163</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="B166" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="C165" s="1" t="s">
+      <c r="C166" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D165" s="1" t="s">
+      <c r="D166" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E165" s="1" t="s">
+      <c r="E166" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F165" s="1" t="s">
+      <c r="F166" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G165" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H165" s="3"/>
-    </row>
-    <row r="166" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A166" s="1">
-        <v>164</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F166" s="1"/>
       <c r="G166" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H166" s="3" t="s">
-        <v>165</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H166" s="3"/>
     </row>
     <row r="167" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>651</v>
+        <v>580</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F167" s="1"/>
       <c r="G167" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>157</v>
+        <v>89</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F168" s="1"/>
       <c r="G168" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H168" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
+        <v>166</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F169" s="1"/>
+      <c r="G169" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H169" s="3" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="169" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A169" s="1">
+    <row r="170" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
         <v>167</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="B170" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="C169" s="1" t="s">
+      <c r="C170" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D169" s="1" t="s">
+      <c r="D170" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E169" s="1" t="s">
+      <c r="E170" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F169" s="1" t="s">
+      <c r="F170" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G169" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H169" s="3" t="s">
+      <c r="G170" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H170" s="3" t="s">
         <v>680</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A170" s="1">
-        <v>168</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F170" s="1"/>
-      <c r="G170" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H170" s="3" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="171" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
+        <v>168</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F171" s="1"/>
+      <c r="G171" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H171" s="3" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
         <v>169</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="B172" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="C171" s="1" t="s">
+      <c r="C172" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D171" s="1" t="s">
+      <c r="D172" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="E171" s="1" t="s">
+      <c r="E172" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="F171" s="1" t="s">
+      <c r="F172" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="G171" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H171" s="3"/>
-    </row>
-    <row r="172" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A172" s="1">
+      <c r="G172" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H172" s="3"/>
+    </row>
+    <row r="173" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
         <v>170</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="B173" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="C172" s="1" t="s">
+      <c r="C173" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="D172" s="1" t="s">
+      <c r="D173" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="E172" s="1" t="s">
+      <c r="E173" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="F172" s="1" t="s">
+      <c r="F173" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="G172" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H172" s="3"/>
+      <c r="G173" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H173" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G172">
+  <conditionalFormatting sqref="G2:G173">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>

--- a/App/TestCases_App/User_admin.xlsx
+++ b/App/TestCases_App/User_admin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686A7129-FCA4-4B37-8579-581C267FE42D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C001550-FFDC-4326-93A0-84A423DE7524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="0" windowWidth="23265" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="693">
   <si>
     <t>Num</t>
   </si>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>Las mesas no se unen.</t>
-  </si>
-  <si>
-    <t>Con cada producto añadido, se está añadiendo el suplemento de terraza. Waiter003.jpg</t>
   </si>
   <si>
     <t>Se reparte la cuenta entre ocho, se hace un pago en efectivo, se hace un pago con tarjeta, pero al pagar el resto de la cuenta indica, se ha pagado 1/8 cuando han sido 2/8. Waiter004.jpg</t>
@@ -1220,9 +1217,6 @@
     <t>Añadir barra de desplazamiento lateral en el listado de modificadores</t>
   </si>
   <si>
-    <t>Añadir barra de desplazamiento lateral en el listado de productos.</t>
-  </si>
-  <si>
     <t>Añadir barra de desplazamiento lateral en el listado de promociones</t>
   </si>
   <si>
@@ -2240,10 +2234,6 @@
   <si>
     <t xml:space="preserve">Se edita la carta, no se ve solo
 </t>
-  </si>
-  <si>
-    <t>No veo variación al cambiar de menú
-18/05/26: El menú desplegable, donde escoges "CARTA", se ha quedado vacio sin carta: MEN007.jpg</t>
   </si>
   <si>
     <t>1. The menu is selected.</t>
@@ -2382,6 +2372,22 @@
   <si>
     <t>Debería de preguntar si se quiere modificar y permitir cancelar.
 22/05/26 No se puede salir de la edición del ROL: CATEG011.jpg</t>
+  </si>
+  <si>
+    <t>No veo variación al cambiar de menú
+18/05/26: El menú desplegable, donde escoges "CARTA", se ha quedado vacio sin carta: MEN007.jpg
+25/05/26 Después de pulsarle más de una vez, el botón se bloquea y ya no muestra el desplegable.</t>
+  </si>
+  <si>
+    <t>Con cada producto añadido, se está añadiendo el suplemento de terraza. Waiter003.jpg
+25/05/26 Después de pulsarle más de una vez, el botón se bloquea y ya no muestra el desplegable.</t>
+  </si>
+  <si>
+    <t>25/05/26: El menu se crea, pero no aparece, y al sincronizar, da error: MEN006.jpg</t>
+  </si>
+  <si>
+    <t>Añadir barra de desplazamiento lateral en el listado de productos.
+25/05/26: Hay un menu entre los productos:PRO010.jpg, PRO011.jpg</t>
   </si>
 </sst>
 </file>
@@ -2889,23 +2895,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2923,13 +2929,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -2937,7 +2943,7 @@
         <v>8</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -2945,23 +2951,23 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -2969,16 +2975,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="2" t="s">
@@ -2988,52 +2994,52 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>655</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>657</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>670</v>
+        <v>689</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3041,22 +3047,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H9" s="3"/>
     </row>
@@ -3065,22 +3071,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H10" s="3"/>
     </row>
@@ -3089,23 +3095,23 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3113,22 +3119,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H12" s="3"/>
     </row>
@@ -3137,22 +3143,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H13" s="3"/>
     </row>
@@ -3161,23 +3167,23 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
@@ -3185,23 +3191,23 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3209,13 +3215,13 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -3223,7 +3229,7 @@
         <v>8</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3231,23 +3237,23 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3255,22 +3261,22 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H18" s="3"/>
     </row>
@@ -3279,23 +3285,23 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3303,25 +3309,25 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3329,22 +3335,22 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H21" s="3"/>
     </row>
@@ -3353,22 +3359,22 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H22" s="3"/>
     </row>
@@ -3377,22 +3383,22 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H23" s="3"/>
     </row>
@@ -3401,22 +3407,22 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H24" s="3"/>
     </row>
@@ -3425,23 +3431,23 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3449,23 +3455,23 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3473,25 +3479,25 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="7" t="s">
         <v>68</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3499,23 +3505,23 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3523,23 +3529,23 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3547,10 +3553,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -3559,7 +3565,7 @@
         <v>8</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3567,10 +3573,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -3578,7 +3584,7 @@
         <v>8</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3586,10 +3592,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -3598,7 +3604,7 @@
         <v>8</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3606,23 +3612,23 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3630,13 +3636,13 @@
         <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
@@ -3644,7 +3650,7 @@
         <v>8</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3652,10 +3658,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -3664,7 +3670,7 @@
         <v>8</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3672,23 +3678,23 @@
         <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3696,13 +3702,13 @@
         <v>34</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -3710,7 +3716,7 @@
         <v>8</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3718,22 +3724,22 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="E38" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H38" s="3"/>
     </row>
@@ -3742,20 +3748,20 @@
         <v>36</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="E39" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H39" s="3"/>
     </row>
@@ -3764,23 +3770,23 @@
         <v>37</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3788,21 +3794,21 @@
         <v>38</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3810,21 +3816,21 @@
         <v>39</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3832,13 +3838,13 @@
         <v>40</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -3846,7 +3852,7 @@
         <v>8</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3854,13 +3860,13 @@
         <v>41</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -3868,7 +3874,7 @@
         <v>8</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
@@ -3876,23 +3882,23 @@
         <v>42</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>624</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>626</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3900,22 +3906,22 @@
         <v>43</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H46" s="3"/>
     </row>
@@ -3924,13 +3930,13 @@
         <v>44</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C47" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>573</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>575</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -3938,7 +3944,7 @@
         <v>8</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3946,13 +3952,13 @@
         <v>45</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C48" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>574</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>576</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -3960,7 +3966,7 @@
         <v>8</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3968,21 +3974,21 @@
         <v>46</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3990,22 +3996,22 @@
         <v>47</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H50" s="3"/>
     </row>
@@ -4014,22 +4020,22 @@
         <v>48</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H51" s="3"/>
     </row>
@@ -4038,23 +4044,23 @@
         <v>49</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4062,22 +4068,22 @@
         <v>50</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4085,23 +4091,23 @@
         <v>51</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4109,20 +4115,20 @@
         <v>52</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H55" s="3"/>
     </row>
@@ -4131,23 +4137,23 @@
         <v>53</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4155,23 +4161,23 @@
         <v>54</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -4179,23 +4185,23 @@
         <v>55</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4203,22 +4209,22 @@
         <v>56</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H59" s="3"/>
     </row>
@@ -4227,23 +4233,23 @@
         <v>57</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C60" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>664</v>
-      </c>
       <c r="E60" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -4251,23 +4257,23 @@
         <v>58</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C61" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>605</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4275,22 +4281,22 @@
         <v>59</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H62" s="3"/>
     </row>
@@ -4299,22 +4305,22 @@
         <v>60</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H63" s="3"/>
     </row>
@@ -4323,22 +4329,22 @@
         <v>61</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H64" s="3"/>
     </row>
@@ -4347,41 +4353,42 @@
         <v>62</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H65" s="3"/>
     </row>
     <row r="66" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>63</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H66" s="3"/>
     </row>
@@ -4390,46 +4397,48 @@
         <v>64</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H67" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>691</v>
+      </c>
     </row>
     <row r="68" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>65</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H68" s="3"/>
     </row>
@@ -4438,22 +4447,22 @@
         <v>66</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H69" s="3"/>
     </row>
@@ -4462,22 +4471,22 @@
         <v>67</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H70" s="3"/>
     </row>
@@ -4486,22 +4495,22 @@
         <v>68</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H71" s="3"/>
     </row>
@@ -4510,22 +4519,22 @@
         <v>69</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H72" s="3"/>
     </row>
@@ -4534,23 +4543,23 @@
         <v>70</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="74" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4558,23 +4567,23 @@
         <v>71</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="75" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4582,22 +4591,22 @@
         <v>72</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H75" s="3"/>
     </row>
@@ -4606,22 +4615,22 @@
         <v>73</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C76" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="F76" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H76" s="3"/>
     </row>
@@ -4630,22 +4639,22 @@
         <v>74</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C77" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D77" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="F77" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H77" s="3"/>
     </row>
@@ -4654,23 +4663,23 @@
         <v>75</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C78" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="F78" s="1"/>
       <c r="G78" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="79" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4678,23 +4687,23 @@
         <v>76</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F79" s="1"/>
       <c r="G79" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="80" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4702,23 +4711,23 @@
         <v>77</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="81" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4726,22 +4735,22 @@
         <v>78</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H81" s="3"/>
     </row>
@@ -4750,22 +4759,22 @@
         <v>79</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C82" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="D82" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="F82" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H82" s="3"/>
     </row>
@@ -4774,22 +4783,22 @@
         <v>80</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H83" s="3"/>
     </row>
@@ -4798,23 +4807,23 @@
         <v>81</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F84" s="1"/>
       <c r="G84" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="85" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
@@ -4822,23 +4831,23 @@
         <v>82</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F85" s="1"/>
       <c r="G85" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="86" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4846,23 +4855,23 @@
         <v>83</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F86" s="1"/>
       <c r="G86" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="87" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4870,22 +4879,22 @@
         <v>84</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H87" s="3"/>
     </row>
@@ -4894,22 +4903,22 @@
         <v>85</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H88" s="3"/>
     </row>
@@ -4918,22 +4927,22 @@
         <v>86</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H89" s="3"/>
     </row>
@@ -4942,22 +4951,22 @@
         <v>87</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H90" s="3"/>
     </row>
@@ -4966,22 +4975,22 @@
         <v>88</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H91" s="3"/>
     </row>
@@ -4990,22 +4999,22 @@
         <v>89</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D92" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="F92" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H92" s="3"/>
     </row>
@@ -5014,22 +5023,22 @@
         <v>90</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C93" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="F93" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H93" s="3"/>
     </row>
@@ -5038,25 +5047,25 @@
         <v>91</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C94" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:8" s="6" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5064,23 +5073,23 @@
         <v>92</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F95" s="1"/>
       <c r="G95" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="96" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -5088,23 +5097,23 @@
         <v>93</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F96" s="1"/>
       <c r="G96" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="97" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5112,22 +5121,22 @@
         <v>94</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H97" s="3"/>
     </row>
@@ -5136,23 +5145,23 @@
         <v>95</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F98" s="1"/>
       <c r="G98" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="99" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5160,22 +5169,22 @@
         <v>96</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H99" s="3"/>
     </row>
@@ -5184,22 +5193,22 @@
         <v>97</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H100" s="3"/>
     </row>
@@ -5208,22 +5217,22 @@
         <v>98</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H101" s="3"/>
     </row>
@@ -5232,23 +5241,23 @@
         <v>99</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D102" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="F102" s="1"/>
       <c r="G102" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="103" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5256,23 +5265,23 @@
         <v>100</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D103" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="F103" s="1"/>
       <c r="G103" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="104" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5280,23 +5289,23 @@
         <v>101</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F104" s="1"/>
       <c r="G104" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="105" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5304,23 +5313,23 @@
         <v>102</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F105" s="1"/>
       <c r="G105" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="106" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5328,25 +5337,25 @@
         <v>103</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C106" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="E106" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="E106" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="F106" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="107" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -5354,20 +5363,20 @@
         <v>104</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F107" s="1"/>
       <c r="G107" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H107" s="3"/>
     </row>
@@ -5376,23 +5385,23 @@
         <v>105</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F108" s="1"/>
       <c r="G108" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="109" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5400,22 +5409,22 @@
         <v>106</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H109" s="3"/>
     </row>
@@ -5424,25 +5433,25 @@
         <v>107</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="111" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5450,22 +5459,22 @@
         <v>108</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H111" s="3"/>
     </row>
@@ -5474,25 +5483,25 @@
         <v>109</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="113" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5500,22 +5509,22 @@
         <v>110</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H113" s="3"/>
     </row>
@@ -5524,49 +5533,49 @@
         <v>111</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D114" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E114" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="F114" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H114" s="3"/>
     </row>
-    <row r="115" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>112</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C115" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="E115" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E115" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="F115" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>362</v>
+        <v>692</v>
       </c>
     </row>
     <row r="116" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -5574,22 +5583,22 @@
         <v>113</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H116" s="3"/>
     </row>
@@ -5598,16 +5607,16 @@
         <v>114</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F117" s="1"/>
       <c r="G117" s="2" t="s">
@@ -5620,22 +5629,22 @@
         <v>115</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H118" s="3"/>
     </row>
@@ -5644,22 +5653,22 @@
         <v>116</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H119" s="3"/>
     </row>
@@ -5668,22 +5677,22 @@
         <v>117</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H120" s="3"/>
     </row>
@@ -5692,22 +5701,22 @@
         <v>118</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H121" s="3"/>
     </row>
@@ -5716,22 +5725,22 @@
         <v>119</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H122" s="3">
         <v>702</v>
@@ -5742,25 +5751,25 @@
         <v>120</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D123" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E123" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E123" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="F123" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="124" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5768,23 +5777,23 @@
         <v>121</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C124" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="E124" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="F124" s="1"/>
       <c r="G124" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="125" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -5792,23 +5801,23 @@
         <v>122</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F125" s="1"/>
       <c r="G125" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="126" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -5816,23 +5825,23 @@
         <v>123</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F126" s="1"/>
       <c r="G126" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="127" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5840,25 +5849,25 @@
         <v>124</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C127" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D127" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="F127" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="128" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -5866,22 +5875,22 @@
         <v>125</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H128" s="3"/>
     </row>
@@ -5890,25 +5899,25 @@
         <v>126</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="130" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5916,22 +5925,22 @@
         <v>127</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H130" s="3"/>
     </row>
@@ -5940,25 +5949,25 @@
         <v>128</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="132" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5966,22 +5975,22 @@
         <v>129</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H132" s="3"/>
     </row>
@@ -5990,22 +5999,22 @@
         <v>130</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H133" s="3"/>
     </row>
@@ -6014,22 +6023,22 @@
         <v>131</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H134" s="3"/>
     </row>
@@ -6038,22 +6047,22 @@
         <v>132</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D135" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E135" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="F135" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H135" s="3"/>
     </row>
@@ -6062,23 +6071,23 @@
         <v>133</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F136" s="1"/>
       <c r="G136" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="137" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6086,23 +6095,23 @@
         <v>134</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D137" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="F137" s="1"/>
       <c r="G137" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="138" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6110,23 +6119,23 @@
         <v>135</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D138" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="F138" s="1"/>
       <c r="G138" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="139" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6134,23 +6143,23 @@
         <v>136</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D139" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E139" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="F139" s="1"/>
       <c r="G139" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="140" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6158,23 +6167,23 @@
         <v>137</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C140" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E140" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="F140" s="1"/>
       <c r="G140" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="141" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6182,23 +6191,23 @@
         <v>138</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C141" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="E141" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>246</v>
       </c>
       <c r="F141" s="1"/>
       <c r="G141" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="142" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6206,23 +6215,23 @@
         <v>139</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C142" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="E142" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="F142" s="1"/>
       <c r="G142" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="143" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6230,23 +6239,23 @@
         <v>140</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C143" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="E143" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="F143" s="1"/>
       <c r="G143" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="144" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6254,23 +6263,23 @@
         <v>141</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C144" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="E144" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="F144" s="1"/>
       <c r="G144" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="145" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6278,25 +6287,25 @@
         <v>142</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D145" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F145" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E145" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="G145" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="146" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6304,25 +6313,25 @@
         <v>143</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C146" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="E146" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="E146" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="F146" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="147" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6330,23 +6339,23 @@
         <v>144</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D147" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E147" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="F147" s="1"/>
       <c r="G147" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="148" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6354,22 +6363,22 @@
         <v>145</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H148" s="3"/>
     </row>
@@ -6378,25 +6387,25 @@
         <v>146</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="150" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6404,22 +6413,22 @@
         <v>147</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H150" s="3"/>
     </row>
@@ -6428,23 +6437,23 @@
         <v>148</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D151" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E151" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="F151" s="1"/>
       <c r="G151" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="152" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6452,25 +6461,25 @@
         <v>149</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D152" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E152" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E152" s="1" t="s">
+      <c r="F152" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F152" s="1" t="s">
+      <c r="G152" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H152" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H152" s="3" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="153" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6478,22 +6487,22 @@
         <v>150</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D153" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E153" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="F153" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H153" s="3"/>
     </row>
@@ -6502,21 +6511,21 @@
         <v>151</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
       <c r="G154" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="155" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6524,23 +6533,23 @@
         <v>152</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D155" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E155" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="F155" s="1"/>
       <c r="G155" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="156" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6548,23 +6557,23 @@
         <v>153</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F156" s="1"/>
       <c r="G156" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="157" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6572,23 +6581,23 @@
         <v>154</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C157" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D157" s="1" t="s">
+      <c r="E157" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="F157" s="1"/>
       <c r="G157" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="158" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6596,23 +6605,23 @@
         <v>155</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D158" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="F158" s="1"/>
       <c r="G158" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="159" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6620,20 +6629,20 @@
         <v>156</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D159" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H159" s="3"/>
     </row>
@@ -6642,22 +6651,22 @@
         <v>157</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H160" s="3"/>
     </row>
@@ -6666,22 +6675,22 @@
         <v>158</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H161" s="3"/>
     </row>
@@ -6690,22 +6699,22 @@
         <v>159</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C162" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D162" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="E162" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H162" s="3"/>
     </row>
@@ -6714,23 +6723,23 @@
         <v>160</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D163" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="F163" s="1"/>
       <c r="G163" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="164" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -6738,23 +6747,23 @@
         <v>161</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F164" s="1"/>
       <c r="G164" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="165" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -6762,20 +6771,20 @@
         <v>162</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F165" s="1"/>
       <c r="G165" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H165" s="3"/>
     </row>
@@ -6784,22 +6793,22 @@
         <v>163</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H166" s="3"/>
     </row>
@@ -6808,23 +6817,23 @@
         <v>164</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C167" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D167" s="1" t="s">
+      <c r="E167" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="E167" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="F167" s="1"/>
       <c r="G167" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="168" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6832,23 +6841,23 @@
         <v>165</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F168" s="1"/>
       <c r="G168" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="169" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6856,23 +6865,23 @@
         <v>166</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C169" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D169" s="1" t="s">
+      <c r="E169" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="F169" s="1"/>
       <c r="G169" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="170" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6880,25 +6889,25 @@
         <v>167</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C170" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D170" s="1" t="s">
+      <c r="E170" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E170" s="1" t="s">
+      <c r="F170" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F170" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G170" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="171" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -6906,23 +6915,23 @@
         <v>168</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C171" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D171" s="1" t="s">
+      <c r="E171" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="F171" s="1"/>
       <c r="G171" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="172" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -6930,22 +6939,22 @@
         <v>169</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H172" s="3"/>
     </row>
@@ -6954,22 +6963,22 @@
         <v>170</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H173" s="3"/>
     </row>

--- a/App/TestCases_App/User_admin.xlsx
+++ b/App/TestCases_App/User_admin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C001550-FFDC-4326-93A0-84A423DE7524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E801FC96-440C-405B-82DD-D64E052C03E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="0" windowWidth="23265" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="702">
   <si>
     <t>Num</t>
   </si>
@@ -1331,9 +1331,6 @@
     <t>1 .The user can do zoom,  between 50% and 200%</t>
   </si>
   <si>
-    <t>Tables's map: zones, create, cancel</t>
-  </si>
-  <si>
     <t>1. The zone is created.</t>
   </si>
   <si>
@@ -2031,10 +2028,6 @@
 2. Clicks "Cancelar"</t>
   </si>
   <si>
-    <t>1. The user creates a zone
-2. Clicks "Cancelar"</t>
-  </si>
-  <si>
     <t>1. The user clicks garbage icon
 2. Clicks "Cancelar"</t>
   </si>
@@ -2094,11 +2087,6 @@
   </si>
   <si>
     <t>No aparece el porcentaje correcto: ACT001.jpg</t>
-  </si>
-  <si>
-    <t>No se puede subir una imagen de una carta: MEN001.jpg
-Al modificar un campo como "Nombre de la carta" el cursor retrocede una posición: MEN004.jpg (tiene q ser en mitad de la linea a modificar)
-Los botones no  van bien, tengo q pulsar varias veces "Siguiente" o "Anterior" para q respondan.</t>
   </si>
   <si>
     <t>Aparece un mensaje de que "seleccione una serie de facturación" que no viene por ningún sitio: FAC002.jpg
@@ -2388,6 +2376,53 @@
   <si>
     <t>Añadir barra de desplazamiento lateral en el listado de productos.
 25/05/26: Hay un menu entre los productos:PRO010.jpg, PRO011.jpg</t>
+  </si>
+  <si>
+    <t>No se puede subir una imagen de una carta: MEN001.jpg
+Al modificar un campo como "Nombre de la carta" el cursor retrocede una posición: MEN004.jpg (tiene q ser en mitad de la linea a modificar)
+Los botones no  van bien, tengo q pulsar varias veces "Siguiente" o "Anterior" para q respondan.
+26/05/26: Se ha creado un modificador, Celiacos con los valores si/no, en la carta, aparece el valor del modificador, pero no el nombre, con lo q no sabes que es: MEN008.jpg</t>
+  </si>
+  <si>
+    <t>Tables's map: zones, delete</t>
+  </si>
+  <si>
+    <t>1. The user selects a zone
+2. Menu 3 points: clicks "Editar"
+3. Modify fields
+4. Clicks "Actualizar"</t>
+  </si>
+  <si>
+    <t>1. The zone is updated</t>
+  </si>
+  <si>
+    <t>Tables's map: zones, edit, cancel</t>
+  </si>
+  <si>
+    <t>1. The user selects a zone
+2. Menu 3 points: clicks "Editar"
+3. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>Tables's map: zones, edit</t>
+  </si>
+  <si>
+    <t>Tables's map: zones, edit, cancel(with X)</t>
+  </si>
+  <si>
+    <t>1. The user selects a zone
+2. Menu 3 points: clicks "Editar"
+3. Clicks the X</t>
+  </si>
+  <si>
+    <t>Con la tablet en formato apaisado, el X para cerrar la ventana no funciona, y el botón "Cancelar" no se ve:ZONE006.jpg</t>
+  </si>
+  <si>
+    <t>1. The user creates a zone
+2. Clicks "Eliminar"</t>
+  </si>
+  <si>
+    <t>No se muestra ningún aviso para cancelar la operación como en el resto de funcionalidad, borra sin preguntar.</t>
   </si>
 </sst>
 </file>
@@ -2851,7 +2886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H173"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -2932,10 +2967,10 @@
         <v>28</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>558</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -2943,7 +2978,7 @@
         <v>8</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -2954,20 +2989,20 @@
         <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -2978,13 +3013,13 @@
         <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="2" t="s">
@@ -3002,20 +3037,20 @@
         <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -3026,20 +3061,20 @@
         <v>32</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3050,16 +3085,16 @@
         <v>33</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>12</v>
@@ -3074,10 +3109,10 @@
         <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>20</v>
@@ -3098,20 +3133,20 @@
         <v>35</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3122,16 +3157,16 @@
         <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>12</v>
@@ -3146,10 +3181,10 @@
         <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>20</v>
@@ -3170,10 +3205,10 @@
         <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>22</v>
@@ -3194,20 +3229,20 @@
         <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3218,10 +3253,10 @@
         <v>39</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -3240,7 +3275,7 @@
         <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>15</v>
@@ -3264,7 +3299,7 @@
         <v>41</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>18</v>
@@ -3288,7 +3323,7 @@
         <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>19</v>
@@ -3312,7 +3347,7 @@
         <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>76</v>
@@ -3338,7 +3373,7 @@
         <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>77</v>
@@ -3362,7 +3397,7 @@
         <v>55</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>80</v>
@@ -3386,7 +3421,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>81</v>
@@ -3410,7 +3445,7 @@
         <v>57</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>84</v>
@@ -3461,7 +3496,7 @@
         <v>64</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>65</v>
@@ -3471,7 +3506,7 @@
         <v>8</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3485,7 +3520,7 @@
         <v>66</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>67</v>
@@ -3508,7 +3543,7 @@
         <v>70</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>115</v>
@@ -3532,13 +3567,13 @@
         <v>71</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="E29" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="2" t="s">
@@ -3565,7 +3600,7 @@
         <v>8</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3618,17 +3653,17 @@
         <v>123</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3650,7 +3685,7 @@
         <v>8</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3670,7 +3705,7 @@
         <v>8</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3687,14 +3722,14 @@
         <v>138</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3816,7 +3851,7 @@
         <v>39</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>145</v>
@@ -3838,7 +3873,7 @@
         <v>40</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>148</v>
@@ -3852,7 +3887,7 @@
         <v>8</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3860,10 +3895,10 @@
         <v>41</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>150</v>
@@ -3874,7 +3909,7 @@
         <v>8</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
@@ -3882,23 +3917,23 @@
         <v>42</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>622</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>624</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3906,13 +3941,13 @@
         <v>43</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>114</v>
@@ -3930,13 +3965,13 @@
         <v>44</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -3944,7 +3979,7 @@
         <v>8</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3955,10 +3990,10 @@
         <v>97</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -3966,7 +4001,7 @@
         <v>8</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3977,18 +4012,18 @@
         <v>98</v>
       </c>
       <c r="C49" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>429</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3999,16 +4034,16 @@
         <v>99</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D50" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>589</v>
-      </c>
       <c r="F50" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>12</v>
@@ -4023,16 +4058,16 @@
         <v>100</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>591</v>
-      </c>
       <c r="F51" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>12</v>
@@ -4047,20 +4082,20 @@
         <v>101</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4071,10 +4106,10 @@
         <v>102</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>114</v>
@@ -4094,20 +4129,20 @@
         <v>103</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>594</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4118,10 +4153,10 @@
         <v>104</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>114</v>
@@ -4137,23 +4172,23 @@
         <v>53</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4164,20 +4199,20 @@
         <v>105</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -4188,20 +4223,20 @@
         <v>106</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4209,13 +4244,13 @@
         <v>56</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>114</v>
@@ -4236,23 +4271,23 @@
         <v>107</v>
       </c>
       <c r="C60" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>660</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>663</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" s="6" customFormat="1" ht="120" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>58</v>
       </c>
@@ -4260,20 +4295,20 @@
         <v>108</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>632</v>
+        <v>690</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4284,10 +4319,10 @@
         <v>109</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>114</v>
@@ -4308,16 +4343,16 @@
         <v>110</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>12</v>
@@ -4332,10 +4367,10 @@
         <v>111</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>114</v>
@@ -4356,16 +4391,16 @@
         <v>112</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>12</v>
@@ -4380,7 +4415,7 @@
         <v>113</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>125</v>
@@ -4397,25 +4432,25 @@
         <v>64</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D67" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>581</v>
-      </c>
       <c r="F67" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="68" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4423,13 +4458,13 @@
         <v>65</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>114</v>
@@ -4447,19 +4482,19 @@
         <v>66</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>12</v>
@@ -4471,10 +4506,10 @@
         <v>67</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>270</v>
@@ -4490,402 +4525,400 @@
       </c>
       <c r="H70" s="3"/>
     </row>
-    <row r="71" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>427</v>
+        <v>694</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>586</v>
+        <v>695</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>587</v>
+        <v>114</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>587</v>
+        <v>114</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H71" s="3"/>
     </row>
     <row r="72" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>585</v>
       </c>
       <c r="E72" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H72" s="3"/>
+    </row>
+    <row r="73" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>69</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="F73" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G72" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H72" s="3"/>
-    </row>
-    <row r="73" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
-        <v>70</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="F73" s="1"/>
       <c r="G73" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>405</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H73" s="3"/>
     </row>
     <row r="74" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>399</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
+        <v>71</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F75" s="1"/>
+      <c r="G75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
         <v>72</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="E75" s="1" t="s">
+      <c r="B76" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H76" s="3"/>
+    </row>
+    <row r="77" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>72</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F77" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G75" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H75" s="3"/>
-    </row>
-    <row r="76" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
-        <v>73</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H76" s="3"/>
-    </row>
-    <row r="77" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
-        <v>74</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="G77" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H77" s="3"/>
     </row>
-    <row r="78" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>401</v>
+        <v>697</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>402</v>
+        <v>698</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>403</v>
+        <v>114</v>
       </c>
       <c r="F78" s="1"/>
       <c r="G78" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>409</v>
+        <v>691</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>408</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>410</v>
+        <v>388</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="F80" s="1"/>
+        <v>390</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>390</v>
+      </c>
       <c r="G80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H80" s="3"/>
+    </row>
+    <row r="81" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>114</v>
+        <v>392</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H81" s="3"/>
     </row>
-    <row r="82" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>418</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="F82" s="1"/>
       <c r="G82" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H82" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="83" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="F83" s="1"/>
       <c r="G83" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H83" s="3"/>
-    </row>
-    <row r="84" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>188</v>
+        <v>407</v>
       </c>
       <c r="F84" s="1"/>
       <c r="G84" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>368</v>
+        <v>410</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="F85" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="G85" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H85" s="3"/>
+    </row>
+    <row r="86" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>369</v>
+        <v>415</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="F86" s="1"/>
+        <v>417</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>417</v>
+      </c>
       <c r="G86" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H86" s="3"/>
+    </row>
+    <row r="87" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>370</v>
+        <v>418</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>381</v>
+        <v>419</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>114</v>
@@ -4898,90 +4931,90 @@
       </c>
       <c r="H87" s="3"/>
     </row>
-    <row r="88" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>371</v>
+        <v>420</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>269</v>
+        <v>421</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>379</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="F88" s="1"/>
       <c r="G88" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H88" s="3"/>
-    </row>
-    <row r="89" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>270</v>
+        <v>376</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="F89" s="1"/>
       <c r="G89" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H89" s="3"/>
-    </row>
-    <row r="90" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>320</v>
+        <v>382</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>380</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="F90" s="1"/>
       <c r="G90" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H90" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="91" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>319</v>
+        <v>381</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>114</v>
@@ -4994,236 +5027,236 @@
       </c>
       <c r="H91" s="3"/>
     </row>
-    <row r="92" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
+        <v>85</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H92" s="3"/>
+    </row>
+    <row r="93" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>86</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H93" s="3"/>
+    </row>
+    <row r="94" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>87</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H94" s="3"/>
+    </row>
+    <row r="95" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>88</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H95" s="3"/>
+    </row>
+    <row r="96" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
         <v>89</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B96" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H96" s="3"/>
+    </row>
+    <row r="97" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>90</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H92" s="3"/>
-    </row>
-    <row r="93" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
-        <v>90</v>
-      </c>
-      <c r="B93" s="1" t="s">
+      <c r="C97" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H97" s="3"/>
+    </row>
+    <row r="98" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>91</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H93" s="3"/>
-    </row>
-    <row r="94" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
-        <v>91</v>
-      </c>
-      <c r="B94" s="1" t="s">
+      <c r="C98" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" s="6" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>92</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" s="6" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
-        <v>92</v>
-      </c>
-      <c r="B95" s="1" t="s">
+      <c r="C99" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="F99" s="1"/>
+      <c r="G99" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>93</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="F95" s="1"/>
-      <c r="G95" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
-        <v>93</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C96" s="1" t="s">
+      <c r="C100" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="D100" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="E100" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="F96" s="1"/>
-      <c r="G96" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H96" s="3" t="s">
+      <c r="F100" s="1"/>
+      <c r="G100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A97" s="1">
-        <v>94</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H97" s="3"/>
-    </row>
-    <row r="98" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A98" s="1">
-        <v>95</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="F98" s="1"/>
-      <c r="G98" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
-        <v>96</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H99" s="3"/>
-    </row>
-    <row r="100" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A100" s="1">
-        <v>97</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H100" s="3"/>
     </row>
     <row r="101" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>114</v>
@@ -5236,286 +5269,282 @@
       </c>
       <c r="H101" s="3"/>
     </row>
-    <row r="102" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>272</v>
+        <v>346</v>
       </c>
       <c r="F102" s="1"/>
       <c r="G102" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
     </row>
     <row r="103" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>352</v>
+        <v>270</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="F103" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="G103" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>354</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H103" s="3"/>
     </row>
     <row r="104" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>365</v>
+        <v>336</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>356</v>
+        <v>320</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="F104" s="1"/>
+        <v>347</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>347</v>
+      </c>
       <c r="G104" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>688</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H104" s="3"/>
     </row>
     <row r="105" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>366</v>
+        <v>319</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="F105" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="G105" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H105" s="3"/>
+    </row>
+    <row r="106" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>301</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="F106" s="1"/>
       <c r="G106" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>302</v>
+        <v>350</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>325</v>
+        <v>353</v>
       </c>
       <c r="F107" s="1"/>
       <c r="G107" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H107" s="3"/>
-    </row>
-    <row r="108" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>313</v>
+        <v>355</v>
       </c>
       <c r="F108" s="1"/>
       <c r="G108" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>328</v>
+        <v>685</v>
       </c>
     </row>
     <row r="109" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>304</v>
+        <v>351</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>324</v>
+        <v>366</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="F109" s="1"/>
       <c r="G109" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H109" s="3"/>
-    </row>
-    <row r="110" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>270</v>
+        <v>326</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="F111" s="1"/>
       <c r="G111" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H111" s="3"/>
     </row>
-    <row r="112" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>311</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="F112" s="1"/>
       <c r="G112" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>579</v>
+        <v>328</v>
       </c>
     </row>
     <row r="113" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>114</v>
@@ -5528,210 +5557,214 @@
       </c>
       <c r="H113" s="3"/>
     </row>
-    <row r="114" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H114" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="115" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
+        <v>108</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H115" s="3"/>
+    </row>
+    <row r="116" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>109</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>110</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H117" s="3"/>
+    </row>
+    <row r="118" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>111</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H118" s="3"/>
+    </row>
+    <row r="119" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
         <v>112</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B119" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>113</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A116" s="1">
-        <v>113</v>
-      </c>
-      <c r="B116" s="1" t="s">
+      <c r="C120" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H120" s="3"/>
+    </row>
+    <row r="121" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>114</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E116" s="1" t="s">
+      <c r="C121" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="F116" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H116" s="3"/>
-    </row>
-    <row r="117" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A117" s="1">
-        <v>114</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="F117" s="1"/>
-      <c r="G117" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H117" s="3"/>
-    </row>
-    <row r="118" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A118" s="1">
-        <v>115</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H118" s="3"/>
-    </row>
-    <row r="119" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A119" s="1">
-        <v>116</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="G119" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H119" s="3"/>
-    </row>
-    <row r="120" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A120" s="1">
-        <v>117</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H120" s="3"/>
-    </row>
-    <row r="121" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A121" s="1">
-        <v>118</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>315</v>
-      </c>
+      <c r="F121" s="1"/>
       <c r="G121" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H121" s="3"/>
     </row>
     <row r="122" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>114</v>
@@ -5742,294 +5775,292 @@
       <c r="G122" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H122" s="3">
-        <v>702</v>
-      </c>
+      <c r="H122" s="3"/>
     </row>
     <row r="123" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>272</v>
+        <v>314</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>272</v>
+        <v>314</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H123" s="3" t="s">
-        <v>298</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H123" s="3"/>
     </row>
     <row r="124" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
+        <v>117</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H124" s="3"/>
+    </row>
+    <row r="125" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>118</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H125" s="3"/>
+    </row>
+    <row r="126" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>119</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H126" s="3">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>120</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
         <v>121</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B128" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F128" s="1"/>
+      <c r="G128" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>122</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F124" s="1"/>
-      <c r="G124" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H124" s="3" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A125" s="1">
-        <v>122</v>
-      </c>
-      <c r="B125" s="1" t="s">
+      <c r="C129" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F129" s="1"/>
+      <c r="G129" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>123</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="C125" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="F125" s="1"/>
-      <c r="G125" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H125" s="3" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A126" s="1">
-        <v>123</v>
-      </c>
-      <c r="B126" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F130" s="1"/>
+      <c r="G130" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>124</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="C126" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="F126" s="1"/>
-      <c r="G126" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H126" s="3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="1">
-        <v>124</v>
-      </c>
-      <c r="B127" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>125</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D127" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H132" s="3"/>
+    </row>
+    <row r="133" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
         <v>126</v>
       </c>
-      <c r="E127" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H127" s="3" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A128" s="1">
-        <v>125</v>
-      </c>
-      <c r="B128" s="1" t="s">
+      <c r="B133" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="E128" s="1" t="s">
+      <c r="C133" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="F128" s="1" t="s">
+      <c r="F133" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="G128" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H128" s="3"/>
-    </row>
-    <row r="129" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A129" s="1">
-        <v>126</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="G129" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H129" s="3" t="s">
+      <c r="G133" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H133" s="3" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="130" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A130" s="1">
-        <v>127</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G130" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H130" s="3"/>
-    </row>
-    <row r="131" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A131" s="1">
-        <v>128</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="G131" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H131" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A132" s="1">
-        <v>129</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H132" s="3"/>
-    </row>
-    <row r="133" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A133" s="1">
-        <v>130</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="G133" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H133" s="3"/>
     </row>
     <row r="134" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>319</v>
+        <v>268</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>114</v>
@@ -6042,189 +6073,191 @@
       </c>
       <c r="H134" s="3"/>
     </row>
-    <row r="135" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H135" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="136" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>227</v>
+        <v>260</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>127</v>
+        <v>270</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="F136" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="G136" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H136" s="3" t="s">
-        <v>362</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H136" s="3"/>
     </row>
     <row r="137" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>231</v>
+        <v>320</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="F137" s="1"/>
+        <v>276</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>276</v>
+      </c>
       <c r="G137" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H137" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H137" s="3"/>
+    </row>
+    <row r="138" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>234</v>
+        <v>319</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F138" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="G138" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H138" s="3" t="s">
-        <v>249</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H138" s="3"/>
     </row>
     <row r="139" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F139" s="1"/>
+        <v>272</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>272</v>
+      </c>
       <c r="G139" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H139" s="3" t="s">
-        <v>249</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H139" s="3"/>
     </row>
     <row r="140" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>255</v>
+        <v>127</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="F140" s="1"/>
       <c r="G140" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>249</v>
+        <v>362</v>
       </c>
     </row>
     <row r="141" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="F141" s="1"/>
       <c r="G141" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
     </row>
     <row r="142" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="F142" s="1"/>
       <c r="G142" s="2" t="s">
@@ -6236,19 +6269,19 @@
     </row>
     <row r="143" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="F143" s="1"/>
       <c r="G143" s="2" t="s">
@@ -6258,21 +6291,21 @@
         <v>249</v>
       </c>
     </row>
-    <row r="144" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F144" s="1"/>
       <c r="G144" s="2" t="s">
@@ -6284,23 +6317,21 @@
     </row>
     <row r="145" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>254</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="F145" s="1"/>
       <c r="G145" s="2" t="s">
         <v>13</v>
       </c>
@@ -6310,681 +6341,779 @@
     </row>
     <row r="146" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>218</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="F146" s="1"/>
       <c r="G146" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="F147" s="1"/>
       <c r="G147" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="F148" s="1"/>
       <c r="G148" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H148" s="3"/>
-    </row>
-    <row r="149" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>114</v>
+        <v>252</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>114</v>
+        <v>254</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
     </row>
     <row r="150" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>86</v>
+        <v>216</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>128</v>
+        <v>217</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H150" s="3"/>
-    </row>
-    <row r="151" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H150" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>165</v>
+        <v>223</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F151" s="1"/>
       <c r="G151" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H151" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
+        <v>145</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H152" s="3"/>
+    </row>
+    <row r="153" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
+        <v>146</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G153" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H151" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="1">
-        <v>149</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H152" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="1">
-        <v>150</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G153" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H153" s="3"/>
+      <c r="H153" s="3" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="154" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>167</v>
+        <v>86</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E154" s="1"/>
-      <c r="F154" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>215</v>
+      </c>
       <c r="G154" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H154" s="3" t="s">
-        <v>205</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H154" s="3"/>
     </row>
     <row r="155" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="F155" s="1"/>
       <c r="G155" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F156" s="1"/>
+        <v>207</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>208</v>
+      </c>
       <c r="G156" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="F157" s="1"/>
+        <v>211</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="G157" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H157" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H157" s="3"/>
+    </row>
+    <row r="158" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>193</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="E158" s="1"/>
       <c r="F158" s="1"/>
       <c r="G158" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
     </row>
     <row r="159" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H159" s="3"/>
-    </row>
-    <row r="160" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H159" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>203</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="F160" s="1"/>
       <c r="G160" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H160" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H160" s="3" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="161" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>203</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="F161" s="1"/>
       <c r="G161" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H161" s="3"/>
-    </row>
-    <row r="162" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>203</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="F162" s="1"/>
       <c r="G162" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H162" s="3"/>
-    </row>
-    <row r="163" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F163" s="1"/>
       <c r="G163" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H163" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H163" s="3"/>
+    </row>
+    <row r="164" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F164" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="G164" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H164" s="3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H164" s="3"/>
+    </row>
+    <row r="165" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>576</v>
+        <v>539</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F165" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="G165" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H165" s="3"/>
     </row>
-    <row r="166" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>577</v>
+        <v>540</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>87</v>
+        <v>184</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="E166" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H166" s="3"/>
+    </row>
+    <row r="167" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
         <v>160</v>
       </c>
-      <c r="F166" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="G166" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H166" s="3"/>
-    </row>
-    <row r="167" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A167" s="1">
-        <v>164</v>
-      </c>
       <c r="B167" s="1" t="s">
-        <v>578</v>
+        <v>541</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="F167" s="1"/>
       <c r="G167" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>649</v>
+        <v>542</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="F168" s="1"/>
       <c r="G168" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>650</v>
+        <v>575</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="F169" s="1"/>
       <c r="G169" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H169" s="3" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H169" s="3"/>
+    </row>
+    <row r="170" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>651</v>
+        <v>576</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>45</v>
+        <v>129</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>47</v>
+        <v>160</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H170" s="3" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H170" s="3"/>
+    </row>
+    <row r="171" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>652</v>
+        <v>577</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>48</v>
+        <v>161</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>49</v>
+        <v>162</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>50</v>
+        <v>163</v>
       </c>
       <c r="F171" s="1"/>
       <c r="G171" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
+        <v>165</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F172" s="1"/>
+      <c r="G172" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H172" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
+        <v>166</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F173" s="1"/>
+      <c r="G173" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H173" s="3" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
+        <v>167</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H174" s="3" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A175" s="1">
+        <v>168</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F175" s="1"/>
+      <c r="G175" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H175" s="3" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A176" s="1">
         <v>169</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="B176" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H176" s="3"/>
+    </row>
+    <row r="177" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A177" s="1">
+        <v>170</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="C172" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="E172" s="1" t="s">
+      <c r="E177" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="F172" s="1" t="s">
+      <c r="F177" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="G172" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H172" s="3"/>
-    </row>
-    <row r="173" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A173" s="1">
-        <v>170</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="G173" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H173" s="3"/>
+      <c r="G177" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H177" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G173">
+  <conditionalFormatting sqref="G2:G177">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>

--- a/App/TestCases_App/User_admin.xlsx
+++ b/App/TestCases_App/User_admin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E801FC96-440C-405B-82DD-D64E052C03E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C06543-226E-4700-B61B-4E74C79F49D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="714">
   <si>
     <t>Num</t>
   </si>
@@ -2423,6 +2423,48 @@
   </si>
   <si>
     <t>No se muestra ningún aviso para cancelar la operación como en el resto de funcionalidad, borra sin preguntar.</t>
+  </si>
+  <si>
+    <t>Se crea una factura tipo: y la llama de Canje. Se debería llamar igual: FAC007.jpg</t>
+  </si>
+  <si>
+    <t>1. The serie is modified</t>
+  </si>
+  <si>
+    <t>Invoicing: Settings, edit serie</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Series de facturación"
+2. Clicks one
+3. Modify type
+4. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Series de facturación"
+2. Clicks one
+3. Modify type: ("Simplificada", "Completa", "Rectificativa",  "Sustitutiva")
+4. Clicks "Guardar cambios"</t>
+  </si>
+  <si>
+    <t>USERADM171</t>
+  </si>
+  <si>
+    <t>USERADM172</t>
+  </si>
+  <si>
+    <t>USERADM173</t>
+  </si>
+  <si>
+    <t>USERADM174</t>
+  </si>
+  <si>
+    <t>USERADM175</t>
+  </si>
+  <si>
+    <t>USERADM176</t>
+  </si>
+  <si>
+    <t>USERADM177</t>
   </si>
 </sst>
 </file>
@@ -2886,7 +2928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -2949,488 +2991,502 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+    <row r="3" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>557</v>
+      </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>556</v>
+        <v>655</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="E4" s="1"/>
+        <v>654</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>638</v>
+      </c>
       <c r="F4" s="1"/>
       <c r="G4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>655</v>
+        <v>555</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>654</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>638</v>
+        <v>653</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>559</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>555</v>
+        <v>650</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
+        <v>644</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>650</v>
+        <v>554</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>644</v>
+        <v>666</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>652</v>
+        <v>665</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>666</v>
+        <v>645</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="F8" s="1"/>
+        <v>651</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>651</v>
+      </c>
       <c r="G8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>686</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>562</v>
+        <v>633</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>651</v>
+        <v>20</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>651</v>
+        <v>20</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" s="6" customFormat="1" ht="210" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>639</v>
+      </c>
+      <c r="F10" s="1"/>
       <c r="G10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" s="6" customFormat="1" ht="210" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="F11" s="1"/>
+        <v>641</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>641</v>
+      </c>
       <c r="G11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>680</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>642</v>
+        <v>548</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>641</v>
+        <v>20</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>641</v>
+        <v>20</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F13" s="1"/>
       <c r="G13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>553</v>
+        <v>676</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>636</v>
+        <v>678</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>22</v>
+        <v>677</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>676</v>
+        <v>549</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>677</v>
-      </c>
+        <v>637</v>
+      </c>
+      <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>679</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="E16" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="F16" s="1"/>
       <c r="G16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="1"/>
+      <c r="F17" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="G17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>16</v>
-      </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="1"/>
+        <v>78</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="G19" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>543</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>12</v>
@@ -3439,340 +3495,338 @@
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>545</v>
+        <v>42</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="F24" s="1"/>
       <c r="G24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>61</v>
+        <v>682</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>63</v>
+        <v>681</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F26" s="1"/>
+        <v>67</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="G26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>66</v>
+        <v>546</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>683</v>
+        <v>115</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>67</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="F27" s="1"/>
       <c r="G27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>115</v>
+        <v>564</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>116</v>
+        <v>560</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H28" s="8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H28" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>560</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D30" s="1"/>
+        <v>119</v>
+      </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>662</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>119</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
+        <v>123</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>627</v>
+      </c>
       <c r="F32" s="1"/>
       <c r="G32" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>123</v>
+        <v>43</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>627</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>124</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
+        <v>133</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>631</v>
+      </c>
       <c r="F35" s="1"/>
       <c r="G35" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>565</v>
+        <v>630</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>631</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>630</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
+        <v>136</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="G37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>153</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H37" s="3"/>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="F38" s="1"/>
       <c r="G38" s="2" t="s">
         <v>12</v>
       </c>
@@ -3780,62 +3834,62 @@
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>141</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H39" s="3"/>
-    </row>
-    <row r="40" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>95</v>
+        <v>437</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>141</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>96</v>
+        <v>438</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
@@ -3843,43 +3897,43 @@
         <v>13</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>151</v>
+        <v>569</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>148</v>
+        <v>567</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -3887,113 +3941,117 @@
         <v>8</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>567</v>
+        <v>620</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E44" s="1"/>
+        <v>621</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>622</v>
+      </c>
       <c r="F44" s="1"/>
       <c r="G44" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="F45" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="G45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H45" s="3"/>
+    </row>
+    <row r="46" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>441</v>
+        <v>97</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>623</v>
+        <v>704</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>624</v>
+        <v>706</v>
       </c>
       <c r="E46" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="F46" s="1"/>
+      <c r="G46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F47" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G46" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H46" s="3"/>
-    </row>
-    <row r="47" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
-        <v>44</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
       <c r="G47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>574</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H47" s="3"/>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -4004,355 +4062,353 @@
         <v>574</v>
       </c>
     </row>
-    <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>427</v>
+        <v>571</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>428</v>
+        <v>573</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>436</v>
+        <v>8</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>588</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
       <c r="G50" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H50" s="3"/>
+        <v>661</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="51" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="G51" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H51" s="3"/>
-    </row>
-    <row r="52" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
-        <v>49</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C52" s="1" t="s">
+      <c r="G52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H52" s="3"/>
+    </row>
+    <row r="53" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="F52" s="1"/>
-      <c r="G52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H52" s="3" t="s">
+      <c r="F53" s="1"/>
+      <c r="G53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H53" s="3" t="s">
         <v>434</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
-        <v>50</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>103</v>
+        <v>443</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
-        <v>52</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H55" s="3"/>
-    </row>
-    <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>443</v>
+        <v>106</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>618</v>
+        <v>594</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>619</v>
+        <v>114</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H56" s="3" t="s">
-        <v>435</v>
-      </c>
+      <c r="H56" s="3"/>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>105</v>
+        <v>444</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>591</v>
+        <v>617</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>596</v>
+        <v>615</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H58" s="3" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="F59" s="1"/>
+      <c r="G59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="59" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
-        <v>56</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="C59" s="1" t="s">
+    <row r="60" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E60" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F60" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G59" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H59" s="3"/>
-    </row>
-    <row r="60" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
-        <v>57</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C60" s="1" t="s">
+      <c r="G60" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H60" s="3"/>
+    </row>
+    <row r="61" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>660</v>
-      </c>
-      <c r="F60" s="1"/>
-      <c r="G60" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" s="6" customFormat="1" ht="120" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>58</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>602</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H61" s="3" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" s="6" customFormat="1" ht="120" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="F62" s="1"/>
+      <c r="G62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
-        <v>59</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H62" s="3"/>
     </row>
     <row r="63" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>615</v>
+        <v>114</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>615</v>
+        <v>114</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>12</v>
@@ -4361,22 +4417,22 @@
     </row>
     <row r="64" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>114</v>
+        <v>615</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>114</v>
+        <v>615</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>12</v>
@@ -4385,116 +4441,116 @@
     </row>
     <row r="65" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>112</v>
+        <v>445</v>
       </c>
       <c r="C65" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H65" s="3"/>
+    </row>
+    <row r="66" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E66" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F66" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="G65" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H65" s="3"/>
-    </row>
-    <row r="66" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
-        <v>63</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C66" s="1" t="s">
+      <c r="G66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H66" s="3"/>
+    </row>
+    <row r="67" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H66" s="3"/>
-    </row>
-    <row r="67" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
-        <v>64</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="C67" s="1" t="s">
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H67" s="3"/>
+    </row>
+    <row r="68" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E68" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F68" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="G67" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H67" s="3" t="s">
+      <c r="G68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H68" s="3" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
-        <v>65</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H68" s="3"/>
     </row>
     <row r="69" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>582</v>
+        <v>114</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>582</v>
+        <v>114</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>12</v>
@@ -4503,40 +4559,40 @@
     </row>
     <row r="70" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C70" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H70" s="3"/>
+    </row>
+    <row r="71" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H70" s="3"/>
-    </row>
-    <row r="71" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
-        <v>72</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>695</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>114</v>
@@ -4545,94 +4601,94 @@
         <v>114</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H71" s="3"/>
     </row>
-    <row r="72" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>426</v>
+        <v>694</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>585</v>
+        <v>695</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>586</v>
+        <v>114</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>586</v>
+        <v>114</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H72" s="3"/>
     </row>
     <row r="73" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C73" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H73" s="3"/>
+    </row>
+    <row r="74" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D74" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="F74" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G73" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H73" s="3"/>
-    </row>
-    <row r="74" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
-        <v>70</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="F74" s="1"/>
       <c r="G74" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>404</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H74" s="3"/>
     </row>
     <row r="75" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>395</v>
@@ -4642,51 +4698,51 @@
         <v>8</v>
       </c>
       <c r="H75" s="3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F76" s="1"/>
+      <c r="G76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H76" s="3" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="76" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
-        <v>72</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="C76" s="1" t="s">
+    <row r="77" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D77" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F77" s="1" t="s">
         <v>693</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H76" s="3"/>
-    </row>
-    <row r="77" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
-        <v>72</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>12</v>
@@ -4695,92 +4751,92 @@
     </row>
     <row r="78" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F78" s="1"/>
+      <c r="F78" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="G78" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H78" s="3"/>
+    </row>
+    <row r="79" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="E79" s="1"/>
+        <v>698</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="F79" s="1"/>
       <c r="G79" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="80" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>388</v>
+        <v>691</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>390</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
       <c r="G80" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H80" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>701</v>
+      </c>
     </row>
     <row r="81" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>12</v>
@@ -4789,64 +4845,64 @@
     </row>
     <row r="82" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C82" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H82" s="3"/>
+    </row>
+    <row r="83" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D83" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E83" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="F82" s="1"/>
-      <c r="G82" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
-        <v>76</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="F83" s="1"/>
       <c r="G83" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
     </row>
     <row r="84" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>407</v>
@@ -4856,219 +4912,219 @@
         <v>8</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="85" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="C85" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="F85" s="1"/>
+      <c r="G85" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D86" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E86" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="F86" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G85" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H85" s="3"/>
-    </row>
-    <row r="86" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
-        <v>79</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="C86" s="1" t="s">
+      <c r="G86" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H86" s="3"/>
+    </row>
+    <row r="87" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E87" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="F86" s="1" t="s">
+      <c r="F87" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="G86" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H86" s="3"/>
-    </row>
-    <row r="87" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
-        <v>80</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C87" s="1" t="s">
+      <c r="G87" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H87" s="3"/>
+    </row>
+    <row r="88" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D88" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="F88" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G87" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H87" s="3"/>
-    </row>
-    <row r="88" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
-        <v>81</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="C88" s="1" t="s">
+      <c r="G88" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H88" s="3"/>
+    </row>
+    <row r="89" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D89" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E89" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="F88" s="1"/>
-      <c r="G88" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
-        <v>82</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>377</v>
       </c>
       <c r="F89" s="1"/>
       <c r="G89" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F90" s="1"/>
       <c r="G90" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H90" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="F91" s="1"/>
+      <c r="G91" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="91" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
-        <v>84</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="C91" s="1" t="s">
+    <row r="92" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D92" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E92" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="F92" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G91" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H91" s="3"/>
-    </row>
-    <row r="92" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
-        <v>85</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="C92" s="1" t="s">
+      <c r="G92" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H92" s="3"/>
+    </row>
+    <row r="93" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E93" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="F92" s="1" t="s">
+      <c r="F93" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H92" s="3"/>
-    </row>
-    <row r="93" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
-        <v>86</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>12</v>
@@ -5077,22 +5133,22 @@
     </row>
     <row r="94" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>380</v>
+        <v>114</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>380</v>
+        <v>114</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>12</v>
@@ -5101,46 +5157,46 @@
     </row>
     <row r="95" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C95" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H95" s="3"/>
+    </row>
+    <row r="96" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D96" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="E96" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F95" s="1" t="s">
+      <c r="F96" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H95" s="3"/>
-    </row>
-    <row r="96" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
-        <v>89</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>12</v>
@@ -5149,22 +5205,22 @@
     </row>
     <row r="97" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>384</v>
+        <v>271</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>385</v>
+        <v>272</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>385</v>
+        <v>272</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>12</v>
@@ -5173,168 +5229,168 @@
     </row>
     <row r="98" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C98" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H98" s="3"/>
+    </row>
+    <row r="99" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D99" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E99" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="F98" s="1" t="s">
+      <c r="F99" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="G98" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H98" s="3" t="s">
+      <c r="G99" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H99" s="3" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="99" spans="1:8" s="6" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
-        <v>92</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="C99" s="1" t="s">
+    <row r="100" spans="1:8" s="6" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="D100" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="E100" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="F99" s="1"/>
-      <c r="G99" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A100" s="1">
-        <v>93</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>342</v>
       </c>
       <c r="F100" s="1"/>
       <c r="G100" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H100" s="3" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="F101" s="1"/>
+      <c r="G101" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="101" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A101" s="1">
-        <v>94</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C101" s="1" t="s">
+    <row r="102" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D102" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E102" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F101" s="1" t="s">
+      <c r="F102" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G101" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H101" s="3"/>
-    </row>
-    <row r="102" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A102" s="1">
-        <v>95</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="C102" s="1" t="s">
+      <c r="G102" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H102" s="3"/>
+    </row>
+    <row r="103" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="D103" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E103" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="F102" s="1"/>
-      <c r="G102" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H102" s="3" t="s">
+      <c r="F103" s="1"/>
+      <c r="G103" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H103" s="3" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A103" s="1">
-        <v>96</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H103" s="3"/>
     </row>
     <row r="104" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>347</v>
+        <v>114</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>347</v>
+        <v>114</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>12</v>
@@ -5343,482 +5399,482 @@
     </row>
     <row r="105" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C105" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H105" s="3"/>
+    </row>
+    <row r="106" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D106" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E106" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F105" s="1" t="s">
+      <c r="F106" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G105" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H105" s="3"/>
-    </row>
-    <row r="106" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A106" s="1">
-        <v>99</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="C106" s="1" t="s">
+      <c r="G106" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H106" s="3"/>
+    </row>
+    <row r="107" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="D107" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="E106" s="1" t="s">
+      <c r="E107" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="F106" s="1"/>
-      <c r="G106" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A107" s="1">
-        <v>100</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>353</v>
       </c>
       <c r="F107" s="1"/>
       <c r="G107" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="108" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F108" s="1"/>
       <c r="G108" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>685</v>
+        <v>354</v>
       </c>
     </row>
     <row r="109" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F109" s="1"/>
       <c r="G109" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H109" s="3" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="F110" s="1"/>
+      <c r="G110" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H110" s="3" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="110" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="1">
-        <v>103</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="C110" s="1" t="s">
+    <row r="111" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="D111" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="E110" s="1" t="s">
+      <c r="E111" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="F110" s="1" t="s">
+      <c r="F111" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="G110" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H110" s="3" t="s">
+      <c r="G111" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H111" s="3" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="111" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A111" s="1">
-        <v>104</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F111" s="1"/>
-      <c r="G111" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H111" s="3"/>
     </row>
     <row r="112" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F112" s="1"/>
       <c r="G112" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H112" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H112" s="3"/>
+    </row>
+    <row r="113" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F113" s="1"/>
+      <c r="G113" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H113" s="3" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="113" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A113" s="1">
-        <v>106</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="C113" s="1" t="s">
+    <row r="114" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="D114" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="E114" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F113" s="1" t="s">
+      <c r="F114" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G113" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H113" s="3"/>
-    </row>
-    <row r="114" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A114" s="1">
-        <v>107</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="C114" s="1" t="s">
+      <c r="G114" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H114" s="3"/>
+    </row>
+    <row r="115" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="D115" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E115" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="F114" s="1" t="s">
+      <c r="F115" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="G114" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H114" s="3" t="s">
+      <c r="G115" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H115" s="3" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A115" s="1">
-        <v>108</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H115" s="3"/>
     </row>
     <row r="116" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>311</v>
+        <v>114</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>311</v>
+        <v>114</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H116" s="3" t="s">
-        <v>578</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H116" s="3"/>
     </row>
     <row r="117" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="C117" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="D118" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="E118" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F117" s="1" t="s">
+      <c r="F118" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G117" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H117" s="3"/>
-    </row>
-    <row r="118" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="1">
-        <v>111</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="C118" s="1" t="s">
+      <c r="G118" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H118" s="3"/>
+    </row>
+    <row r="119" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="D119" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="F118" s="1" t="s">
+      <c r="F119" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="G118" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H118" s="3"/>
-    </row>
-    <row r="119" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A119" s="1">
-        <v>112</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="C119" s="1" t="s">
+      <c r="G119" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H119" s="3"/>
+    </row>
+    <row r="120" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="D120" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="E119" s="1" t="s">
+      <c r="E120" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="F119" s="1" t="s">
+      <c r="F120" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G119" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H119" s="3" t="s">
+      <c r="G120" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H120" s="3" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A120" s="1">
-        <v>113</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H120" s="3"/>
     </row>
     <row r="121" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="F121" s="1"/>
+      <c r="F121" s="1" t="s">
+        <v>316</v>
+      </c>
       <c r="G121" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H121" s="3"/>
     </row>
-    <row r="122" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C122" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F122" s="1"/>
+      <c r="G122" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H122" s="3"/>
+    </row>
+    <row r="123" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D123" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="E122" s="1" t="s">
+      <c r="E123" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F122" s="1" t="s">
+      <c r="F123" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G122" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H122" s="3"/>
-    </row>
-    <row r="123" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A123" s="1">
-        <v>116</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="C123" s="1" t="s">
+      <c r="G123" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H123" s="3"/>
+    </row>
+    <row r="124" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="D124" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E123" s="1" t="s">
+      <c r="E124" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="F123" s="1" t="s">
+      <c r="F124" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H123" s="3"/>
-    </row>
-    <row r="124" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A124" s="1">
-        <v>117</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>12</v>
@@ -5827,22 +5883,22 @@
     </row>
     <row r="125" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>315</v>
+        <v>114</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>315</v>
+        <v>114</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>12</v>
@@ -5851,190 +5907,190 @@
     </row>
     <row r="126" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C126" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H126" s="3"/>
+    </row>
+    <row r="127" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="D127" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="E126" s="1" t="s">
+      <c r="E127" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F126" s="1" t="s">
+      <c r="F127" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G126" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H126" s="3">
+      <c r="G127" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H127" s="3">
         <v>702</v>
       </c>
     </row>
-    <row r="127" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A127" s="1">
-        <v>120</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="C127" s="1" t="s">
+    <row r="128" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D128" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="E127" s="1" t="s">
+      <c r="E128" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="F127" s="1" t="s">
+      <c r="F128" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="G127" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H127" s="3" t="s">
+      <c r="G128" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H128" s="3" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="128" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A128" s="1">
-        <v>121</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C128" s="1" t="s">
+    <row r="129" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="D129" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E128" s="1" t="s">
+      <c r="E129" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="F128" s="1"/>
-      <c r="G128" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H128" s="3" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A129" s="1">
-        <v>122</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>316</v>
       </c>
       <c r="F129" s="1"/>
       <c r="G129" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F130" s="1"/>
       <c r="G130" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H130" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F131" s="1"/>
+      <c r="G131" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H131" s="3" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="131" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="1">
-        <v>124</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="C131" s="1" t="s">
+    <row r="132" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="D132" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E131" s="1" t="s">
+      <c r="E132" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="F131" s="1" t="s">
+      <c r="F132" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="G131" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H131" s="3" t="s">
+      <c r="G132" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H132" s="3" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A132" s="1">
-        <v>125</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H132" s="3"/>
     </row>
     <row r="133" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>273</v>
@@ -6043,104 +6099,104 @@
         <v>273</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H133" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H133" s="3"/>
+    </row>
+    <row r="134" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H134" s="3" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="134" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A134" s="1">
-        <v>127</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C134" s="1" t="s">
+    <row r="135" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="D135" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E134" s="1" t="s">
+      <c r="E135" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F134" s="1" t="s">
+      <c r="F135" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G134" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H134" s="3"/>
-    </row>
-    <row r="135" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A135" s="1">
-        <v>128</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="C135" s="1" t="s">
+      <c r="G135" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H135" s="3"/>
+    </row>
+    <row r="136" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="D136" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="E135" s="1" t="s">
+      <c r="E136" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F135" s="1" t="s">
+      <c r="F136" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="G135" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H135" s="3" t="s">
+      <c r="G136" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H136" s="3" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="136" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A136" s="1">
-        <v>129</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G136" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H136" s="3"/>
     </row>
     <row r="137" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>276</v>
+        <v>114</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>276</v>
+        <v>114</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>12</v>
@@ -6149,139 +6205,139 @@
     </row>
     <row r="138" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="C138" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H138" s="3"/>
+    </row>
+    <row r="139" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C139" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="D139" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="E138" s="1" t="s">
+      <c r="E139" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F138" s="1" t="s">
+      <c r="F139" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G138" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H138" s="3"/>
-    </row>
-    <row r="139" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="1">
-        <v>132</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C139" s="1" t="s">
+      <c r="G139" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H139" s="3"/>
+    </row>
+    <row r="140" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C140" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="D140" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="E140" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="F139" s="1" t="s">
+      <c r="F140" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="G139" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H139" s="3"/>
-    </row>
-    <row r="140" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A140" s="1">
-        <v>133</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="F140" s="1"/>
       <c r="G140" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H140" s="3" t="s">
-        <v>362</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H140" s="3"/>
     </row>
     <row r="141" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>231</v>
+        <v>127</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F141" s="1"/>
       <c r="G141" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F142" s="1"/>
       <c r="G142" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
     </row>
     <row r="143" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F143" s="1"/>
       <c r="G143" s="2" t="s">
@@ -6291,21 +6347,21 @@
         <v>249</v>
       </c>
     </row>
-    <row r="144" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F144" s="1"/>
       <c r="G144" s="2" t="s">
@@ -6317,19 +6373,19 @@
     </row>
     <row r="145" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F145" s="1"/>
       <c r="G145" s="2" t="s">
@@ -6339,21 +6395,21 @@
         <v>249</v>
       </c>
     </row>
-    <row r="146" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F146" s="1"/>
       <c r="G146" s="2" t="s">
@@ -6365,19 +6421,19 @@
     </row>
     <row r="147" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="F147" s="1"/>
       <c r="G147" s="2" t="s">
@@ -6389,19 +6445,19 @@
     </row>
     <row r="148" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="F148" s="1"/>
       <c r="G148" s="2" t="s">
@@ -6411,25 +6467,23 @@
         <v>249</v>
       </c>
     </row>
-    <row r="149" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F149" s="1" t="s">
-        <v>254</v>
-      </c>
+      <c r="F149" s="1"/>
       <c r="G149" s="2" t="s">
         <v>13</v>
       </c>
@@ -6437,89 +6491,91 @@
         <v>249</v>
       </c>
     </row>
-    <row r="150" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H150" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H151" s="3" t="s">
         <v>364</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A151" s="1">
-        <v>144</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="F151" s="1"/>
-      <c r="G151" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H151" s="3" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="152" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="F152" s="1"/>
       <c r="G152" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H152" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="153" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>221</v>
@@ -6531,269 +6587,269 @@
         <v>114</v>
       </c>
       <c r="G153" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H153" s="3"/>
+    </row>
+    <row r="154" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G154" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H153" s="3" t="s">
+      <c r="H154" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="154" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="1">
-        <v>147</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="C154" s="1" t="s">
+    <row r="155" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C155" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D154" s="1" t="s">
+      <c r="D155" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E154" s="1" t="s">
+      <c r="E155" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F154" s="1" t="s">
+      <c r="F155" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="G154" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H154" s="3"/>
-    </row>
-    <row r="155" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A155" s="1">
-        <v>148</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="C155" s="1" t="s">
+      <c r="G155" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H155" s="3"/>
+    </row>
+    <row r="156" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C156" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D155" s="1" t="s">
+      <c r="D156" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E155" s="1" t="s">
+      <c r="E156" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F155" s="1"/>
-      <c r="G155" s="2" t="s">
+      <c r="F156" s="1"/>
+      <c r="G156" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H155" s="3" t="s">
+      <c r="H156" s="3" t="s">
         <v>212</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="1">
-        <v>149</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G156" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H156" s="3" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="157" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H157" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H157" s="3" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="158" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C158" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H158" s="3"/>
+    </row>
+    <row r="159" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C159" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D158" s="1" t="s">
+      <c r="D159" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E158" s="1"/>
-      <c r="F158" s="1"/>
-      <c r="G158" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H158" s="3" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A159" s="1">
-        <v>152</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>195</v>
-      </c>
+      <c r="E159" s="1"/>
       <c r="F159" s="1"/>
       <c r="G159" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F160" s="1"/>
       <c r="G160" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F161" s="1"/>
       <c r="G161" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F162" s="1"/>
       <c r="G162" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>537</v>
+        <v>575</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F163" s="1"/>
       <c r="G163" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H163" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="H163" s="3" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="164" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>538</v>
+        <v>576</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>203</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="F164" s="1"/>
       <c r="G164" s="2" t="s">
         <v>12</v>
       </c>
@@ -6801,16 +6857,16 @@
     </row>
     <row r="165" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>539</v>
+        <v>577</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>203</v>
@@ -6825,16 +6881,16 @@
     </row>
     <row r="166" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>540</v>
+        <v>646</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>203</v>
@@ -6847,273 +6903,297 @@
       </c>
       <c r="H166" s="3"/>
     </row>
-    <row r="167" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>541</v>
+        <v>647</v>
       </c>
       <c r="C167" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H167" s="3"/>
+    </row>
+    <row r="168" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C168" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D167" s="1" t="s">
+      <c r="D168" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E167" s="1" t="s">
+      <c r="E168" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="F167" s="1"/>
-      <c r="G167" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H167" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A168" s="1">
-        <v>161</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="F168" s="1"/>
       <c r="G168" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="169" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>575</v>
+        <v>649</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>114</v>
+        <v>188</v>
       </c>
       <c r="F169" s="1"/>
       <c r="G169" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H169" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F170" s="1"/>
+      <c r="G170" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H169" s="3"/>
-    </row>
-    <row r="170" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="1">
-        <v>163</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="C170" s="1" t="s">
+      <c r="H170" s="3"/>
+    </row>
+    <row r="171" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="C171" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D170" s="1" t="s">
+      <c r="D171" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E170" s="1" t="s">
+      <c r="E171" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F170" s="1" t="s">
+      <c r="F171" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="G170" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H170" s="3"/>
-    </row>
-    <row r="171" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A171" s="1">
-        <v>164</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="F171" s="1"/>
       <c r="G171" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H171" s="3" t="s">
-        <v>164</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H171" s="3"/>
     </row>
     <row r="172" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>646</v>
+        <v>707</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>88</v>
+        <v>161</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F172" s="1"/>
       <c r="G172" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>647</v>
+        <v>708</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>156</v>
+        <v>88</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F173" s="1"/>
       <c r="G173" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H173" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F174" s="1"/>
+      <c r="G174" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H174" s="3" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="174" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A174" s="1">
-        <v>167</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="C174" s="1" t="s">
+    <row r="175" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="C175" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D174" s="1" t="s">
+      <c r="D175" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E174" s="1" t="s">
+      <c r="E175" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F174" s="1" t="s">
+      <c r="F175" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G174" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H174" s="3" t="s">
+      <c r="G175" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H175" s="3" t="s">
         <v>674</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A175" s="1">
-        <v>168</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E175" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F175" s="1"/>
-      <c r="G175" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H175" s="3" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="176" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>668</v>
+        <v>711</v>
       </c>
       <c r="C176" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F176" s="1"/>
+      <c r="G176" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H176" s="3" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="C177" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D176" s="1" t="s">
+      <c r="D177" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="E176" s="1" t="s">
+      <c r="E177" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="F176" s="1" t="s">
+      <c r="F177" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="G176" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H176" s="3"/>
-    </row>
-    <row r="177" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A177" s="1">
-        <v>170</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="C177" s="1" t="s">
+      <c r="G177" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H177" s="3"/>
+    </row>
+    <row r="178" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C178" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="D177" s="1" t="s">
+      <c r="D178" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="E177" s="1" t="s">
+      <c r="E178" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="F177" s="1" t="s">
+      <c r="F178" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="G177" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H177" s="3"/>
+      <c r="G178" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H178" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G177">
+  <conditionalFormatting sqref="G2:G178">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>

--- a/App/TestCases_App/User_admin.xlsx
+++ b/App/TestCases_App/User_admin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C06543-226E-4700-B61B-4E74C79F49D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8566F17-5E34-46E6-AADD-5CA7DC69F18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2211,10 +2212,6 @@
   </si>
   <si>
     <t>Pte</t>
-  </si>
-  <si>
-    <t>No hay tickets
-15/05/26: El ticket practicamente no se ve, y ademas dice que el pago total de 13,80e está hecho con tarjeta, cuando parte esta hecho con tarjeta y parte con efectivo: HISTIC001.jpg</t>
   </si>
   <si>
     <t>1. The user writes a world in the box of the search</t>
@@ -2465,6 +2462,11 @@
   </si>
   <si>
     <t>USERADM177</t>
+  </si>
+  <si>
+    <t>No hay tickets
+15/05/26: El ticket practicamente no se ve, y ademas dice que el pago total de 13,80e está hecho con tarjeta, cuando parte esta hecho con tarjeta y parte con efectivo: HISTIC001.jpg
+05/06/25: Se muestran tickets, pero el formato de la fecha es erroneo:HISTIC002.jpg</t>
   </si>
 </sst>
 </file>
@@ -3082,7 +3084,7 @@
         <v>8</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -3096,17 +3098,17 @@
         <v>554</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3178,7 +3180,7 @@
         <v>8</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3261,20 +3263,20 @@
         <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>677</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3528,7 +3530,7 @@
         <v>64</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>65</v>
@@ -3538,7 +3540,7 @@
         <v>8</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -3552,7 +3554,7 @@
         <v>66</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>67</v>
@@ -3615,7 +3617,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="29" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -3632,10 +3634,10 @@
         <v>8</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -4000,20 +4002,20 @@
         <v>97</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -4024,10 +4026,10 @@
         <v>98</v>
       </c>
       <c r="C47" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>704</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>705</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>114</v>
@@ -4222,7 +4224,7 @@
         <v>8</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -4388,7 +4390,7 @@
         <v>8</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="63" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4474,7 +4476,7 @@
         <v>561</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>599</v>
@@ -4530,7 +4532,7 @@
         <v>8</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="69" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4613,10 +4615,10 @@
         <v>452</v>
       </c>
       <c r="C72" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>694</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>695</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>114</v>
@@ -4733,16 +4735,16 @@
         <v>457</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D77" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>693</v>
-      </c>
       <c r="F77" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>12</v>
@@ -4757,10 +4759,10 @@
         <v>458</v>
       </c>
       <c r="C78" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>694</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>695</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>114</v>
@@ -4781,10 +4783,10 @@
         <v>459</v>
       </c>
       <c r="C79" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>697</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>698</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>114</v>
@@ -4794,7 +4796,7 @@
         <v>8</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="80" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4805,10 +4807,10 @@
         <v>460</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
@@ -4816,7 +4818,7 @@
         <v>8</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="81" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5298,7 +5300,7 @@
         <v>8</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="101" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -5514,7 +5516,7 @@
         <v>8</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="110" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5784,7 +5786,7 @@
         <v>8</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="121" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6980,7 +6982,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>177</v>
@@ -7002,7 +7004,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>87</v>
@@ -7026,7 +7028,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>161</v>
@@ -7050,7 +7052,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>88</v>
@@ -7074,7 +7076,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>156</v>
@@ -7098,7 +7100,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>44</v>
@@ -7116,7 +7118,7 @@
         <v>8</v>
       </c>
       <c r="H175" s="3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="176" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -7124,7 +7126,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>48</v>
@@ -7140,7 +7142,7 @@
         <v>8</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="177" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -7148,19 +7150,19 @@
         <v>176</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>12</v>
@@ -7172,19 +7174,19 @@
         <v>177</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>12</v>
@@ -7208,5 +7210,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>